--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
@@ -6346,7 +6346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ63"/>
+  <dimension ref="A1:BQ64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10868,20 +10868,20 @@
       <c r="BP29" s="10" t="n"/>
       <c r="BQ29" s="11" t="n"/>
     </row>
-    <row r="30" ht="368" customHeight="1">
+    <row r="30" ht="450" customHeight="1">
       <c r="A30" s="44" t="n">
         <v>16</v>
       </c>
       <c r="B30" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-016</t>
+          <t>ACSMS-TC-011-015-2</t>
         </is>
       </c>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="46" t="inlineStr">
         <is>
-          <t>郵便番号 7桁チェック</t>
+          <t>購読者氏名 漢字・ひらがな・カタカナチェック（顧客要件 2026-07）</t>
         </is>
       </c>
       <c r="F30" s="10" t="n"/>
@@ -10916,7 +10916,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">郵便番号（yubin_no）に「123」（6桁未満）を入力し「承認・登録」ボタンを押下
+            <t xml:space="preserve">購読者氏名_氏（shimei_sei）に半角英数字「Yamada12」を入力し「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -10933,7 +10933,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">郵便番号（yubin_no）に「123-4567」（ハイフン入り）を入力し「承認・登録」ボタンを押下
+            <t xml:space="preserve">購読者氏名_氏（shimei_sei）に全角ひらがな「やまだ」を入力し「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -10950,7 +10950,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>郵便番号（yubin_no）に「1234567」（半角数字7桁）を入力し「承認・登録」ボタンを押下</t>
+            <t xml:space="preserve">購読者氏名_名（shimei_mei）に全角カタカナ「タロウ」を入力し「承認・登録」ボタンを押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>購読者氏名_氏（shimei_sei）に漢字「山田」を入力し「承認・登録」ボタンを押下</t>
           </r>
         </is>
       </c>
@@ -10976,7 +10993,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">形式エラーが表示されること（メッセージ `郵便番号は7桁で入力してください。`）
+            <t xml:space="preserve">形式エラーが表示されること（メッセージ `漢字・ひらがな・カタカナで入力してください。`）
 </t>
           </r>
           <r>
@@ -10993,7 +11010,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">形式エラーが表示されること（ハイフン入力不可、メッセージ `郵便番号は7桁で入力してください。`）
+            <t xml:space="preserve">形式エラーが表示されないこと（全角ひらがなが入力可能であること）
 </t>
           </r>
           <r>
@@ -11010,7 +11027,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">郵便番号の形式エラーが表示されないこと（半角数字7桁が入力可能であること）
+            <t xml:space="preserve">形式エラーが表示されないこと（全角カタカナが入力可能であること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">形式エラーが表示されないこと（漢字が入力可能であること）
 </t>
           </r>
           <r>
@@ -11027,15 +11061,31 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・郵便番号は半角数字7桁固定、ハイフン入力不可とすること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・桁数不正の場合 ACSMS-MSG-011-004 メッセージ `郵便番号は7桁で入力してください。` を表示すること</t>
+            <t xml:space="preserve">・顧客要件 2026-07：ひらがな/カタカナ表記の氏名の方に対応するため、氏名（漢字）は漢字のみから漢字・ひらがな・カタカナ許容に緩和
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・対象は 購読者氏名_氏/名（shimei_sei/shimei_mei）および配達先氏名_姓/名（haitatsu_shimei_sei/haitatsu_shimei_mei）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・半角カナ・英数字は引き続き不可。形式不正時は `漢字・ひらがな・カタカナで入力してください。` を表示すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・かな項目（shimei_kana_*）の全角ひらがな形式は変更なし（ACSMS-TC-011-015）</t>
           </r>
         </is>
       </c>
@@ -11089,20 +11139,20 @@
       <c r="BP30" s="10" t="n"/>
       <c r="BQ30" s="11" t="n"/>
     </row>
-    <row r="31" ht="400" customHeight="1">
+    <row r="31" ht="368" customHeight="1">
       <c r="A31" s="44" t="n">
         <v>17</v>
       </c>
       <c r="B31" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-017</t>
+          <t>ACSMS-TC-011-016</t>
         </is>
       </c>
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="46" t="inlineStr">
         <is>
-          <t>メールアドレス 形式チェック</t>
+          <t>郵便番号 7桁チェック</t>
         </is>
       </c>
       <c r="F31" s="10" t="n"/>
@@ -11137,7 +11187,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">メールアドレス（email）に「yamada」（@なし）を入力し「承認・登録」ボタンを押下
+            <t xml:space="preserve">郵便番号（yubin_no）に「123」（6桁未満）を入力し「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -11154,7 +11204,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">メールアドレス（email）に「yamada@」（ドメインなし）を入力し「承認・登録」ボタンを押下
+            <t xml:space="preserve">郵便番号（yubin_no）に「123-4567」（ハイフン入り）を入力し「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -11171,7 +11221,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>メールアドレス（email）に「yamada@example.com」（正しい形式）を入力し「承認・登録」ボタンを押下</t>
+            <t>郵便番号（yubin_no）に「1234567」（半角数字7桁）を入力し「承認・登録」ボタンを押下</t>
           </r>
         </is>
       </c>
@@ -11197,7 +11247,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">形式エラーが表示されること（メッセージ `正しいメールアドレスを入力してください。`）
+            <t xml:space="preserve">形式エラーが表示されること（メッセージ `郵便番号は7桁で入力してください。`）
 </t>
           </r>
           <r>
@@ -11214,7 +11264,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">形式エラーが表示されること（メッセージ `正しいメールアドレスを入力してください。`）
+            <t xml:space="preserve">形式エラーが表示されること（ハイフン入力不可、メッセージ `郵便番号は7桁で入力してください。`）
 </t>
           </r>
           <r>
@@ -11231,7 +11281,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">メールアドレスの形式エラーが表示されないこと
+            <t xml:space="preserve">郵便番号の形式エラーが表示されないこと（半角数字7桁が入力可能であること）
 </t>
           </r>
           <r>
@@ -11248,23 +11298,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・メールアドレスは RFC 5322 形式チェックを行うこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・形式不正の場合 ACSMS-MSG-011-005 メッセージ `正しいメールアドレスを入力してください。` を表示すること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・メールアドレス項目は `type="text"` を使用し、ブラウザ標準の英語ポップアップを使用しないこと</t>
+            <t xml:space="preserve">・郵便番号は半角数字7桁固定、ハイフン入力不可とすること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・桁数不正の場合 ACSMS-MSG-011-004 メッセージ `郵便番号は7桁で入力してください。` を表示すること</t>
           </r>
         </is>
       </c>
@@ -11318,20 +11360,20 @@
       <c r="BP31" s="10" t="n"/>
       <c r="BQ31" s="11" t="n"/>
     </row>
-    <row r="32" ht="384" customHeight="1">
+    <row r="32" ht="400" customHeight="1">
       <c r="A32" s="44" t="n">
         <v>18</v>
       </c>
       <c r="B32" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-018</t>
+          <t>ACSMS-TC-011-017</t>
         </is>
       </c>
       <c r="C32" s="10" t="n"/>
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="46" t="inlineStr">
         <is>
-          <t>メールアドレス 条件付き必須（電子版・併読）</t>
+          <t>メールアドレス 形式チェック</t>
         </is>
       </c>
       <c r="F32" s="10" t="n"/>
@@ -11366,7 +11408,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">購読種別（dokusya_shubetsu）で「電子版」を選択し、メールアドレス（email）を空欄のまま「承認・登録」ボタンを押下
+            <t xml:space="preserve">メールアドレス（email）に「yamada」（@なし）を入力し「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -11383,7 +11425,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">購読種別で「併読」を選択し、メールアドレスを空欄のまま「承認・登録」ボタンを押下
+            <t xml:space="preserve">メールアドレス（email）に「yamada@」（ドメインなし）を入力し「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -11400,7 +11442,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>購読種別で「紙版」を選択し、メールアドレスを空欄のまま他必須項目を入力して「承認・登録」ボタンを押下</t>
+            <t>メールアドレス（email）に「yamada@example.com」（正しい形式）を入力し「承認・登録」ボタンを押下</t>
           </r>
         </is>
       </c>
@@ -11426,7 +11468,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">メールアドレス（email）の下に必須入力エラーが表示されること（メッセージ `必須項目です。`）
+            <t xml:space="preserve">形式エラーが表示されること（メッセージ `正しいメールアドレスを入力してください。`）
 </t>
           </r>
           <r>
@@ -11443,7 +11485,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">メールアドレス（email）の下に必須入力エラーが表示されること（メッセージ `必須項目です。`）
+            <t xml:space="preserve">形式エラーが表示されること（メッセージ `正しいメールアドレスを入力してください。`）
 </t>
           </r>
           <r>
@@ -11460,7 +11502,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">メールアドレス（email）の必須入力エラーが表示されないこと（紙版の場合は任意であること）
+            <t xml:space="preserve">メールアドレスの形式エラーが表示されないこと
 </t>
           </r>
           <r>
@@ -11477,15 +11519,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・購読種別=電子版/併読時はメールアドレスを必須とすること（機能定義 §7.1）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・紙版の場合はメールアドレスは任意であること</t>
+            <t xml:space="preserve">・メールアドレスは RFC 5322 形式チェックを行うこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・形式不正の場合 ACSMS-MSG-011-005 メッセージ `正しいメールアドレスを入力してください。` を表示すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・メールアドレス項目は `type="text"` を使用し、ブラウザ標準の英語ポップアップを使用しないこと</t>
           </r>
         </is>
       </c>
@@ -11539,20 +11589,20 @@
       <c r="BP32" s="10" t="n"/>
       <c r="BQ32" s="11" t="n"/>
     </row>
-    <row r="33" ht="450" customHeight="1">
+    <row r="33" ht="384" customHeight="1">
       <c r="A33" s="44" t="n">
         <v>19</v>
       </c>
       <c r="B33" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-019</t>
+          <t>ACSMS-TC-011-018</t>
         </is>
       </c>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="46" t="inlineStr">
         <is>
-          <t>口座引落時の銀行クラスタ 条件付き必須</t>
+          <t>メールアドレス 条件付き必須（電子版・併読）</t>
         </is>
       </c>
       <c r="F33" s="10" t="n"/>
@@ -11562,8 +11612,7 @@
       <c r="J33" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・購読種別=紙版
-・支払方法（shiharai_hoho）で「口座引落」を選択した状態</t>
+・購読者情報登録画面（新規作成モード）を開いた状態</t>
         </is>
       </c>
       <c r="K33" s="10" t="n"/>
@@ -11588,7 +11637,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">引落口座支店（bank_shiten_id）・引落口座貯金種目（hikiotoshi_yokin_shubetsu）・引落口座番号（hikiotoshi_koza_no）・引落口座名義（hikiotoshi_koza_meigi）を空欄のまま「承認・登録」ボタンを押下
+            <t xml:space="preserve">購読種別（dokusya_shubetsu）で「電子版」を選択し、メールアドレス（email）を空欄のまま「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -11605,7 +11654,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">支払方法を「現金集金」に変更し、上記4項目を空欄のまま「承認・登録」ボタンを押下
+            <t xml:space="preserve">購読種別で「併読」を選択し、メールアドレスを空欄のまま「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -11622,7 +11671,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>引落口座支店プルダウンの選択肢を確認</t>
+            <t>購読種別で「紙版」を選択し、メールアドレスを空欄のまま他必須項目を入力して「承認・登録」ボタンを押下</t>
           </r>
         </is>
       </c>
@@ -11648,7 +11697,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">引落口座支店・引落口座貯金種目・引落口座番号・引落口座名義の下にエラーが表示されること（メッセージ `口座引落の場合、〇〇は必須です。`）
+            <t xml:space="preserve">メールアドレス（email）の下に必須入力エラーが表示されること（メッセージ `必須項目です。`）
 </t>
           </r>
           <r>
@@ -11665,7 +11714,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">上記4項目のエラーが表示されないこと（口座引落以外の支払方法では任意であること）
+            <t xml:space="preserve">メールアドレス（email）の下に必須入力エラーが表示されること（メッセージ `必須項目です。`）
 </t>
           </r>
           <r>
@@ -11682,7 +11731,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">金融機関支店フラグ（kinyu_shiten_flg=TRUE）の支店のみが選択肢に表示されること
+            <t xml:space="preserve">メールアドレス（email）の必須入力エラーが表示されないこと（紙版の場合は任意であること）
 </t>
           </r>
           <r>
@@ -11699,23 +11748,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・支払方法=口座引落（shiharai_hoho=1）の場合、引落口座クラスタ4項目を必須とすること（機能定義 §10.1）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・口座引落必須エラーは ACSMS-MSG-011-006 メッセージ `口座引落の場合、〇〇は必須です。` を表示すること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・引落口座支店プルダウンは `m_shiten.kinyu_shiten_flg=TRUE` のもののみ表示すること</t>
+            <t xml:space="preserve">・購読種別=電子版/併読時はメールアドレスを必須とすること（機能定義 §7.1）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・紙版の場合はメールアドレスは任意であること</t>
           </r>
         </is>
       </c>
@@ -11775,14 +11816,14 @@
       </c>
       <c r="B34" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-020</t>
+          <t>ACSMS-TC-011-019</t>
         </is>
       </c>
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="46" t="inlineStr">
         <is>
-          <t>配達先 条件付き必須（購読者情報と同じが未チェック）</t>
+          <t>口座引落時の銀行クラスタ 条件付き必須</t>
         </is>
       </c>
       <c r="F34" s="10" t="n"/>
@@ -11793,7 +11834,7 @@
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
 ・購読種別=紙版
-・「購読者情報と同じ」（haitatsu_same_flg）が未チェックの状態</t>
+・支払方法（shiharai_hoho）で「口座引落」を選択した状態</t>
         </is>
       </c>
       <c r="K34" s="10" t="n"/>
@@ -11818,7 +11859,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">配達先郵便番号（haitatsu_yubin_no）・配達先都道府県（haitatsu_todofuken_code）・配達先市町村郡（haitatsu_shikuchoson）・配達先丁目番地（haitatsu_chome_banchi）を空欄のまま「承認・登録」ボタンを押下
+            <t xml:space="preserve">引落口座支店（bank_shiten_id）・引落口座貯金種目（hikiotoshi_yokin_shubetsu）・引落口座番号（hikiotoshi_koza_no）・引落口座名義（hikiotoshi_koza_meigi）を空欄のまま「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -11835,7 +11876,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">配達先苗字漢字（haitatsu_shimei_sei）・配達先名前漢字（haitatsu_shimei_mei）・配達先苗字かな（haitatsu_shimei_kana_sei）・配達先名前かな（haitatsu_shimei_kana_mei）を空欄のまま「承認・登録」ボタンを押下
+            <t xml:space="preserve">支払方法を「現金集金」に変更し、上記4項目を空欄のまま「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -11852,7 +11893,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>「購読者情報と同じ」をチェックし、配達先項目を空欄のまま「承認・登録」ボタンを押下</t>
+            <t>引落口座支店プルダウンの選択肢を確認</t>
           </r>
         </is>
       </c>
@@ -11878,7 +11919,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">配達先郵便番号・配達先都道府県・配達先市町村郡・配達先丁目番地の下に必須入力エラーが表示されること（メッセージ `必須項目です。`）
+            <t xml:space="preserve">引落口座支店・引落口座貯金種目・引落口座番号・引落口座名義の下にエラーが表示されること（メッセージ `口座引落の場合、〇〇は必須です。`）
 </t>
           </r>
           <r>
@@ -11895,7 +11936,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">配達先苗字漢字・配達先名前漢字・配達先苗字かな・配達先名前かなの下に必須入力エラーが表示されること（メッセージ `必須項目です。`）
+            <t xml:space="preserve">上記4項目のエラーが表示されないこと（口座引落以外の支払方法では任意であること）
 </t>
           </r>
           <r>
@@ -11912,7 +11953,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">配達先項目の必須入力エラーが表示されないこと（チェック時は購読者情報をコピーするため必須スキップとなること）
+            <t xml:space="preserve">金融機関支店フラグ（kinyu_shiten_flg=TRUE）の支店のみが選択肢に表示されること
 </t>
           </r>
           <r>
@@ -11929,15 +11970,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・「購読者情報と同じ」未チェック時は配達先郵便番号〜丁目番地および配達先氏名（漢字・かな）を必須とすること（機能定義 §9.2）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・チェック時はDB保存時に購読者情報からコピーすること（機能定義 §9.1）</t>
+            <t xml:space="preserve">・支払方法=口座引落（shiharai_hoho=1）の場合、引落口座クラスタ4項目を必須とすること（機能定義 §10.1）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・口座引落必須エラーは ACSMS-MSG-011-006 メッセージ `口座引落の場合、〇〇は必須です。` を表示すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・引落口座支店プルダウンは `m_shiten.kinyu_shiten_flg=TRUE` のもののみ表示すること</t>
           </r>
         </is>
       </c>
@@ -11991,20 +12040,20 @@
       <c r="BP34" s="10" t="n"/>
       <c r="BQ34" s="11" t="n"/>
     </row>
-    <row r="35" ht="384" customHeight="1">
+    <row r="35" ht="450" customHeight="1">
       <c r="A35" s="44" t="n">
         <v>21</v>
       </c>
       <c r="B35" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-021</t>
+          <t>ACSMS-TC-011-020</t>
         </is>
       </c>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="46" t="inlineStr">
         <is>
-          <t>備考 最大文字数チェック・読者情報変更適用日 未来日チェック</t>
+          <t>配達先 条件付き必須（購読者情報と同じが未チェック）</t>
         </is>
       </c>
       <c r="F35" s="10" t="n"/>
@@ -12014,8 +12063,8 @@
       <c r="J35" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・購読者情報登録画面（新規作成モード）を開いた状態
-・当日: 2026-06-03</t>
+・購読種別=紙版
+・「購読者情報と同じ」（haitatsu_same_flg）が未チェックの状態</t>
         </is>
       </c>
       <c r="K35" s="10" t="n"/>
@@ -12040,7 +12089,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">備考（biko）に501文字を入力し「承認・登録」ボタンを押下
+            <t xml:space="preserve">配達先郵便番号（haitatsu_yubin_no）・配達先都道府県（haitatsu_todofuken_code）・配達先市町村郡（haitatsu_shikuchoson）・配達先丁目番地（haitatsu_chome_banchi）を空欄のまま「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -12057,7 +12106,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">備考（biko）に500文字を入力し「承認・登録」ボタンを押下
+            <t xml:space="preserve">配達先苗字漢字（haitatsu_shimei_sei）・配達先名前漢字（haitatsu_shimei_mei）・配達先苗字かな（haitatsu_shimei_kana_sei）・配達先名前かな（haitatsu_shimei_kana_mei）を空欄のまま「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -12074,7 +12123,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>読者情報変更適用日（joho_henko_tekiyo_date）に過去日（2026-06-02）を入力し「承認・登録」ボタンを押下</t>
+            <t>「購読者情報と同じ」をチェックし、配達先項目を空欄のまま「承認・登録」ボタンを押下</t>
           </r>
         </is>
       </c>
@@ -12100,7 +12149,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">桁数超過エラーが表示されること（メッセージ `備考は500文字以内で入力してください。`）
+            <t xml:space="preserve">配達先郵便番号・配達先都道府県・配達先市町村郡・配達先丁目番地の下に必須入力エラーが表示されること（メッセージ `必須項目です。`）
 </t>
           </r>
           <r>
@@ -12117,7 +12166,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">備考の桁数超過エラーが表示されないこと（500文字以内で登録できること）
+            <t xml:space="preserve">配達先苗字漢字・配達先名前漢字・配達先苗字かな・配達先名前かなの下に必須入力エラーが表示されること（メッセージ `必須項目です。`）
 </t>
           </r>
           <r>
@@ -12134,7 +12183,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">読者情報変更適用日の下にエラーが表示されること（未来日のみ入力可能であること）
+            <t xml:space="preserve">配達先項目の必須入力エラーが表示されないこと（チェック時は購読者情報をコピーするため必須スキップとなること）
 </t>
           </r>
           <r>
@@ -12151,15 +12200,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・備考は500文字以内とすること（ACSMS-MSG-011-010 メッセージ `備考は500文字以内で入力してください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・読者情報変更適用日（joho_henko_tekiyo_date）は入力時は未来日であることをチェックすること</t>
+            <t xml:space="preserve">・「購読者情報と同じ」未チェック時は配達先郵便番号〜丁目番地および配達先氏名（漢字・かな）を必須とすること（機能定義 §9.2）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・チェック時はDB保存時に購読者情報からコピーすること（機能定義 §9.1）</t>
           </r>
         </is>
       </c>
@@ -12213,20 +12262,20 @@
       <c r="BP35" s="10" t="n"/>
       <c r="BQ35" s="11" t="n"/>
     </row>
-    <row r="36" ht="368" customHeight="1">
+    <row r="36" ht="384" customHeight="1">
       <c r="A36" s="44" t="n">
         <v>22</v>
       </c>
       <c r="B36" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-022</t>
+          <t>ACSMS-TC-011-021</t>
         </is>
       </c>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="46" t="inlineStr">
         <is>
-          <t>農業者分類 条件付き必須（購読者層=農業者）</t>
+          <t>備考 最大文字数チェック・読者情報変更適用日 未来日チェック</t>
         </is>
       </c>
       <c r="F36" s="10" t="n"/>
@@ -12236,7 +12285,8 @@
       <c r="J36" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・購読者情報登録画面（新規作成モード）を開いた状態</t>
+・購読者情報登録画面（新規作成モード）を開いた状態
+・当日: 2026-06-03</t>
         </is>
       </c>
       <c r="K36" s="10" t="n"/>
@@ -12261,7 +12311,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">購読者層分類（dokusyaso_bunrui）で「農業者」をチェックし、農業者分類（nogyosya_bunrui）を空欄のまま「承認・登録」ボタンを押下
+            <t xml:space="preserve">備考（biko）に501文字を入力し「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -12278,7 +12328,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">農業者分類（nogyosya_bunrui）で「水稲」を選択し「承認・登録」ボタンを押下
+            <t xml:space="preserve">備考（biko）に500文字を入力し「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -12295,7 +12345,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>購読者層分類「農業者」のチェックを解除し、農業者分類を空欄のまま「承認・登録」ボタンを押下</t>
+            <t>読者情報変更適用日（joho_henko_tekiyo_date）に過去日（2026-06-02）を入力し「承認・登録」ボタンを押下</t>
           </r>
         </is>
       </c>
@@ -12321,7 +12371,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">農業者分類（nogyosya_bunrui）の下に必須入力エラーが表示されること（メッセージ `必須項目です。`）
+            <t xml:space="preserve">桁数超過エラーが表示されること（メッセージ `備考は500文字以内で入力してください。`）
 </t>
           </r>
           <r>
@@ -12338,7 +12388,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">農業者分類の必須入力エラーが表示されないこと
+            <t xml:space="preserve">備考の桁数超過エラーが表示されないこと（500文字以内で登録できること）
 </t>
           </r>
           <r>
@@ -12355,7 +12405,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">農業者分類の必須入力エラーが表示されないこと（農業者未選択時は任意であること）
+            <t xml:space="preserve">読者情報変更適用日の下にエラーが表示されること（未来日のみ入力可能であること）
 </t>
           </r>
           <r>
@@ -12372,15 +12422,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・購読者層分類で「農業者」を選択した場合、農業者分類（nogyosya_bunrui）を必須とすること（API リクエストパラメータ仕様）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・農業者を未選択の場合は農業者分類を任意とすること</t>
+            <t xml:space="preserve">・備考は500文字以内とすること（ACSMS-MSG-011-010 メッセージ `備考は500文字以内で入力してください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・読者情報変更適用日（joho_henko_tekiyo_date）は入力時は未来日であることをチェックすること</t>
           </r>
         </is>
       </c>
@@ -12426,12 +12476,7 @@
       <c r="BH36" s="45" t="inlineStr"/>
       <c r="BI36" s="10" t="n"/>
       <c r="BJ36" s="11" t="n"/>
-      <c r="BK36" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BK36" s="46" t="inlineStr"/>
       <c r="BL36" s="10" t="n"/>
       <c r="BM36" s="10" t="n"/>
       <c r="BN36" s="10" t="n"/>
@@ -12439,74 +12484,225 @@
       <c r="BP36" s="10" t="n"/>
       <c r="BQ36" s="11" t="n"/>
     </row>
-    <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="32" t="inlineStr">
-        <is>
-          <t>業務ロジック登録（Function — Create）</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n"/>
+    <row r="37" ht="368" customHeight="1">
+      <c r="A37" s="44" t="n">
+        <v>23</v>
+      </c>
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-022</t>
+        </is>
+      </c>
       <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="46" t="inlineStr">
+        <is>
+          <t>農業者分類 条件付き必須（購読者層=農業者）</t>
+        </is>
+      </c>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
       <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・購読者情報登録画面（新規作成モード）を開いた状態</t>
+        </is>
+      </c>
       <c r="K37" s="10" t="n"/>
       <c r="L37" s="10" t="n"/>
       <c r="M37" s="10" t="n"/>
       <c r="N37" s="10" t="n"/>
       <c r="O37" s="10" t="n"/>
-      <c r="P37" s="10" t="n"/>
-      <c r="Q37" s="10" t="n"/>
+      <c r="P37" s="11" t="n"/>
+      <c r="Q37" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読者層分類（dokusyaso_bunrui）で「農業者」をチェックし、農業者分類（nogyosya_bunrui）を空欄のまま「承認・登録」ボタンを押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">農業者分類（nogyosya_bunrui）で「水稲」を選択し「承認・登録」ボタンを押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>購読者層分類「農業者」のチェックを解除し、農業者分類を空欄のまま「承認・登録」ボタンを押下</t>
+          </r>
+        </is>
+      </c>
       <c r="R37" s="10" t="n"/>
       <c r="S37" s="10" t="n"/>
       <c r="T37" s="10" t="n"/>
       <c r="U37" s="10" t="n"/>
       <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n"/>
-      <c r="X37" s="10" t="n"/>
+      <c r="W37" s="11" t="n"/>
+      <c r="X37" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">農業者分類（nogyosya_bunrui）の下に必須入力エラーが表示されること（メッセージ `必須項目です。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">農業者分類の必須入力エラーが表示されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">農業者分類の必須入力エラーが表示されないこと（農業者未選択時は任意であること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・購読者層分類で「農業者」を選択した場合、農業者分類（nogyosya_bunrui）を必須とすること（API リクエストパラメータ仕様）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・農業者を未選択の場合は農業者分類を任意とすること</t>
+          </r>
+        </is>
+      </c>
       <c r="Y37" s="10" t="n"/>
       <c r="Z37" s="10" t="n"/>
       <c r="AA37" s="10" t="n"/>
       <c r="AB37" s="10" t="n"/>
       <c r="AC37" s="10" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="10" t="n"/>
-      <c r="AF37" s="10" t="n"/>
-      <c r="AG37" s="10" t="n"/>
+      <c r="AD37" s="11" t="n"/>
+      <c r="AE37" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF37" s="11" t="n"/>
+      <c r="AG37" s="45" t="inlineStr"/>
       <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="10" t="n"/>
+      <c r="AI37" s="11" t="n"/>
+      <c r="AJ37" s="45" t="inlineStr"/>
       <c r="AK37" s="10" t="n"/>
-      <c r="AL37" s="10" t="n"/>
-      <c r="AM37" s="10" t="n"/>
+      <c r="AL37" s="11" t="n"/>
+      <c r="AM37" s="45" t="inlineStr"/>
       <c r="AN37" s="10" t="n"/>
-      <c r="AO37" s="10" t="n"/>
-      <c r="AP37" s="10" t="n"/>
+      <c r="AO37" s="11" t="n"/>
+      <c r="AP37" s="45" t="inlineStr"/>
       <c r="AQ37" s="10" t="n"/>
-      <c r="AR37" s="10" t="n"/>
-      <c r="AS37" s="10" t="n"/>
+      <c r="AR37" s="11" t="n"/>
+      <c r="AS37" s="45" t="inlineStr"/>
       <c r="AT37" s="10" t="n"/>
-      <c r="AU37" s="10" t="n"/>
-      <c r="AV37" s="10" t="n"/>
+      <c r="AU37" s="11" t="n"/>
+      <c r="AV37" s="45" t="inlineStr"/>
       <c r="AW37" s="10" t="n"/>
-      <c r="AX37" s="10" t="n"/>
-      <c r="AY37" s="10" t="n"/>
+      <c r="AX37" s="11" t="n"/>
+      <c r="AY37" s="45" t="inlineStr"/>
       <c r="AZ37" s="10" t="n"/>
-      <c r="BA37" s="10" t="n"/>
-      <c r="BB37" s="10" t="n"/>
+      <c r="BA37" s="11" t="n"/>
+      <c r="BB37" s="45" t="inlineStr"/>
       <c r="BC37" s="10" t="n"/>
-      <c r="BD37" s="10" t="n"/>
-      <c r="BE37" s="10" t="n"/>
+      <c r="BD37" s="11" t="n"/>
+      <c r="BE37" s="45" t="inlineStr"/>
       <c r="BF37" s="10" t="n"/>
-      <c r="BG37" s="10" t="n"/>
-      <c r="BH37" s="10" t="n"/>
+      <c r="BG37" s="11" t="n"/>
+      <c r="BH37" s="45" t="inlineStr"/>
       <c r="BI37" s="10" t="n"/>
-      <c r="BJ37" s="10" t="n"/>
-      <c r="BK37" s="10" t="n"/>
+      <c r="BJ37" s="11" t="n"/>
+      <c r="BK37" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL37" s="10" t="n"/>
       <c r="BM37" s="10" t="n"/>
       <c r="BN37" s="10" t="n"/>
@@ -12514,382 +12710,74 @@
       <c r="BP37" s="10" t="n"/>
       <c r="BQ37" s="11" t="n"/>
     </row>
-    <row r="38" ht="450" customHeight="1">
-      <c r="A38" s="44" t="n">
-        <v>23</v>
-      </c>
-      <c r="B38" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-011-023</t>
-        </is>
-      </c>
+    <row r="38" ht="22.5" customHeight="1">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>業務ロジック登録（Function — Create）</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="46" t="inlineStr">
-        <is>
-          <t>新規登録 正常系（DB 永続化 + 履歴作成 + 監査ログ）</t>
-        </is>
-      </c>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
       <c r="F38" s="10" t="n"/>
       <c r="G38" s="10" t="n"/>
       <c r="H38" s="10" t="n"/>
-      <c r="I38" s="11" t="n"/>
-      <c r="J38" s="46" t="inlineStr">
-        <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・全必須項目に有効な値を入力済み（購読種別=紙版、手続種類=新規、支払方法=口座引落）</t>
-        </is>
-      </c>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
       <c r="K38" s="10" t="n"/>
       <c r="L38" s="10" t="n"/>
       <c r="M38" s="10" t="n"/>
       <c r="N38" s="10" t="n"/>
       <c r="O38" s="10" t="n"/>
-      <c r="P38" s="11" t="n"/>
-      <c r="Q38" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">全必須項目を入力し「承認・登録」ボタンを押下、確認ダイアログで「はい」を押下
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">画面遷移とメッセージを確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">DBで以下クエリを実行し、本体・履歴レコードを確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT dokusya_id, rireki_no, tetsuzuki_shurui, dokusya_busu
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_dokusya
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = :new_dokusya_id;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT rireki_no, saishin_data_flg, shinki_flg, kaiyaku_flg, zougen_hokoku_flg
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_dokusya_rireki
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = :new_dokusya_id;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">DBで以下クエリを実行し、監査ログを確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT operation, result_status, target_table, ja_id
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_log
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE target_table = 't_dokusya' AND target_id = :new_dokusya_id
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY log_datetime DESC
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">LIMIT 1;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>```</t>
-          </r>
-        </is>
-      </c>
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n"/>
       <c r="R38" s="10" t="n"/>
       <c r="S38" s="10" t="n"/>
       <c r="T38" s="10" t="n"/>
       <c r="U38" s="10" t="n"/>
       <c r="V38" s="10" t="n"/>
-      <c r="W38" s="11" t="n"/>
-      <c r="X38" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">確認ダイアログが表示され「はい」押下で登録処理が実行されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">HTTPステータスコード201が返却されること、登録完了メッセージ `登録しました。`（ACSMS-MSG-011-011）が表示されること、購読者明細検索画面へ遷移すること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">t_dokusya に新規レコードが登録されること、t_dokusya_rireki に履歴レコード（rireki_no=1, saishin_data_flg=true, shinki_flg=true, kaiyaku_flg=false, zougen_hokoku_flg=true）が登録されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">t_log に operation=`CREATE`, result_status=1, target_table=`t_dokusya`, ja_id=100 のレコードが記録されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・t_dokusya + t_dokusya_rireki を1トランザクションで作成すること（機能定義 §2.6）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・支払方法=口座引落の場合、bank_shiten_id から `m_shiten.jastem_toriatsukai_tenpo_code` / `jastem_tenpo_name` を逆引きし、`t_dokusya.bank_branch_code` / `bank_branch_name` へ非正規化保存すること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・登録（業務書き込み）と監査ログは単一トランザクションで実行されること</t>
-          </r>
-        </is>
-      </c>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="10" t="n"/>
       <c r="Y38" s="10" t="n"/>
       <c r="Z38" s="10" t="n"/>
       <c r="AA38" s="10" t="n"/>
       <c r="AB38" s="10" t="n"/>
       <c r="AC38" s="10" t="n"/>
-      <c r="AD38" s="11" t="n"/>
-      <c r="AE38" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF38" s="11" t="n"/>
-      <c r="AG38" s="45" t="inlineStr"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="10" t="n"/>
+      <c r="AF38" s="10" t="n"/>
+      <c r="AG38" s="10" t="n"/>
       <c r="AH38" s="10" t="n"/>
-      <c r="AI38" s="11" t="n"/>
-      <c r="AJ38" s="45" t="inlineStr"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
       <c r="AK38" s="10" t="n"/>
-      <c r="AL38" s="11" t="n"/>
-      <c r="AM38" s="45" t="inlineStr"/>
+      <c r="AL38" s="10" t="n"/>
+      <c r="AM38" s="10" t="n"/>
       <c r="AN38" s="10" t="n"/>
-      <c r="AO38" s="11" t="n"/>
-      <c r="AP38" s="45" t="inlineStr"/>
+      <c r="AO38" s="10" t="n"/>
+      <c r="AP38" s="10" t="n"/>
       <c r="AQ38" s="10" t="n"/>
-      <c r="AR38" s="11" t="n"/>
-      <c r="AS38" s="45" t="inlineStr"/>
+      <c r="AR38" s="10" t="n"/>
+      <c r="AS38" s="10" t="n"/>
       <c r="AT38" s="10" t="n"/>
-      <c r="AU38" s="11" t="n"/>
-      <c r="AV38" s="45" t="inlineStr"/>
+      <c r="AU38" s="10" t="n"/>
+      <c r="AV38" s="10" t="n"/>
       <c r="AW38" s="10" t="n"/>
-      <c r="AX38" s="11" t="n"/>
-      <c r="AY38" s="45" t="inlineStr"/>
+      <c r="AX38" s="10" t="n"/>
+      <c r="AY38" s="10" t="n"/>
       <c r="AZ38" s="10" t="n"/>
-      <c r="BA38" s="11" t="n"/>
-      <c r="BB38" s="45" t="inlineStr"/>
+      <c r="BA38" s="10" t="n"/>
+      <c r="BB38" s="10" t="n"/>
       <c r="BC38" s="10" t="n"/>
-      <c r="BD38" s="11" t="n"/>
-      <c r="BE38" s="45" t="inlineStr"/>
+      <c r="BD38" s="10" t="n"/>
+      <c r="BE38" s="10" t="n"/>
       <c r="BF38" s="10" t="n"/>
-      <c r="BG38" s="11" t="n"/>
-      <c r="BH38" s="45" t="inlineStr"/>
+      <c r="BG38" s="10" t="n"/>
+      <c r="BH38" s="10" t="n"/>
       <c r="BI38" s="10" t="n"/>
-      <c r="BJ38" s="11" t="n"/>
-      <c r="BK38" s="46" t="inlineStr"/>
+      <c r="BJ38" s="10" t="n"/>
+      <c r="BK38" s="10" t="n"/>
       <c r="BL38" s="10" t="n"/>
       <c r="BM38" s="10" t="n"/>
       <c r="BN38" s="10" t="n"/>
@@ -12897,20 +12785,20 @@
       <c r="BP38" s="10" t="n"/>
       <c r="BQ38" s="11" t="n"/>
     </row>
-    <row r="39" ht="336" customHeight="1">
+    <row r="39" ht="450" customHeight="1">
       <c r="A39" s="44" t="n">
         <v>24</v>
       </c>
       <c r="B39" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-024</t>
+          <t>ACSMS-TC-011-023</t>
         </is>
       </c>
       <c r="C39" s="10" t="n"/>
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="46" t="inlineStr">
         <is>
-          <t>新規登録 — 手続種類「解約」時の購読部数0強制</t>
+          <t>新規登録 正常系（DB 永続化 + 履歴作成 + 監査ログ）</t>
         </is>
       </c>
       <c r="F39" s="10" t="n"/>
@@ -12920,7 +12808,7 @@
       <c r="J39" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・手続種類（tetsuzuki_shurui）=解約 を選択</t>
+・全必須項目に有効な値を入力済み（購読種別=紙版、手続種類=新規、支払方法=口座引落）</t>
         </is>
       </c>
       <c r="K39" s="10" t="n"/>
@@ -12945,7 +12833,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">手続種類で「解約」を選択し、購読部数（dokusya_busu）に「5」を入力した状態で「承認・登録」ボタンを押下
+            <t xml:space="preserve">全必須項目を入力し「承認・登録」ボタンを押下、確認ダイアログで「はい」を押下
 </t>
           </r>
           <r>
@@ -12962,7 +12850,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DBで以下クエリを実行し、購読部数と解約フラグを確認
+            <t xml:space="preserve">画面遷移とメッセージを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DBで以下クエリを実行し、本体・履歴レコードを確認
 </t>
           </r>
           <r>
@@ -12978,15 +12883,31 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">SELECT dokusya_busu FROM t_dokusya WHERE dokusya_id = :new_dokusya_id;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT kaiyaku_flg, shinki_flg
+            <t xml:space="preserve">SELECT dokusya_id, rireki_no, tetsuzuki_shurui, dokusya_busu
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE dokusya_id = :new_dokusya_id;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT rireki_no, saishin_data_flg, shinki_flg, kaiyaku_flg, zougen_hokoku_flg
 </t>
           </r>
           <r>
@@ -13002,7 +12923,80 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = :new_dokusya_id AND saishin_data_flg = TRUE;
+            <t xml:space="preserve">WHERE dokusya_id = :new_dokusya_id;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DBで以下クエリを実行し、監査ログを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT operation, result_status, target_table, ja_id
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_log
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE target_table = 't_dokusya' AND target_id = :new_dokusya_id
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY log_datetime DESC
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">LIMIT 1;
 </t>
           </r>
           <r>
@@ -13036,7 +13030,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">登録処理が実行されること、登録完了メッセージ `登録しました。` が表示されること
+            <t xml:space="preserve">確認ダイアログが表示され「はい」押下で登録処理が実行されること
 </t>
           </r>
           <r>
@@ -13053,7 +13047,41 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">t_dokusya の dokusya_busu が0で保存されること、t_dokusya_rireki の kaiyaku_flg が TRUE、shinki_flg が FALSE で保存されること
+            <t xml:space="preserve">HTTPステータスコード201が返却されること、登録完了メッセージ `登録しました。`（ACSMS-MSG-011-011）が表示されること、購読者明細検索画面へ遷移すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">t_dokusya に新規レコードが登録されること、t_dokusya_rireki に履歴レコード（rireki_no=1, saishin_data_flg=true, shinki_flg=true, kaiyaku_flg=false, zougen_hokoku_flg=true）が登録されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">t_log に operation=`CREATE`, result_status=1, target_table=`t_dokusya`, ja_id=100 のレコードが記録されること
 </t>
           </r>
           <r>
@@ -13070,15 +13098,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・解約を選んで登録する場合は購読部数を0にし、kaiyaku_flg=TRUE に設定すること（機能定義 §8.1）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・二重請求防止のため購読部数は解約時に強制的に0となること</t>
+            <t xml:space="preserve">・t_dokusya + t_dokusya_rireki を1トランザクションで作成すること（機能定義 §2.6）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・bank_shiten_id が指定された場合、支払方法を問わず（口座引落以外も含む） `m_shiten.jastem_toriatsukai_tenpo_code` / `jastem_tenpo_name` を逆引きし、`t_dokusya.bank_branch_code` / `bank_branch_name` へ非正規化保存すること（顧客要件 2026-06）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・登録（業務書き込み）と監査ログは単一トランザクションで実行されること</t>
           </r>
         </is>
       </c>
@@ -13132,20 +13168,20 @@
       <c r="BP39" s="10" t="n"/>
       <c r="BQ39" s="11" t="n"/>
     </row>
-    <row r="40" ht="288" customHeight="1">
+    <row r="40" ht="336" customHeight="1">
       <c r="A40" s="44" t="n">
         <v>25</v>
       </c>
       <c r="B40" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-025</t>
+          <t>ACSMS-TC-011-024</t>
         </is>
       </c>
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="46" t="inlineStr">
         <is>
-          <t>新規登録 — 配達先「購読者情報と同じ」時のコピー保存</t>
+          <t>新規登録 — 手続種類「解約」時の購読部数0強制</t>
         </is>
       </c>
       <c r="F40" s="10" t="n"/>
@@ -13155,8 +13191,7 @@
       <c r="J40" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・購読種別=紙版
-・「購読者情報と同じ」（haitatsu_same_flg）をチェック</t>
+・手続種類（tetsuzuki_shurui）=解約 を選択</t>
         </is>
       </c>
       <c r="K40" s="10" t="n"/>
@@ -13181,7 +13216,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">購読者氏名・住所等を入力し、「購読者情報と同じ」をチェックして「承認・登録」ボタンを押下
+            <t xml:space="preserve">手続種類で「解約」を選択し、購読部数（dokusya_busu）に「5」を入力した状態で「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -13198,7 +13233,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DBで以下クエリを実行し、配達先情報を確認
+            <t xml:space="preserve">DBで以下クエリを実行し、購読部数と解約フラグを確認
 </t>
           </r>
           <r>
@@ -13214,15 +13249,31 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">SELECT haitatsu_same_flg, haitatsu_yubin_no, haitatsu_shimei_sei
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_dokusya WHERE dokusya_id = :new_dokusya_id;
+            <t xml:space="preserve">SELECT dokusya_busu FROM t_dokusya WHERE dokusya_id = :new_dokusya_id;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT kaiyaku_flg, shinki_flg
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya_rireki
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE dokusya_id = :new_dokusya_id AND saishin_data_flg = TRUE;
 </t>
           </r>
           <r>
@@ -13273,7 +13324,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">haitatsu_same_flg が true で保存されること、配達先項目（haitatsu_yubin_no・haitatsu_shimei_sei 等）に購読者情報からコピーされた値が保存されること
+            <t xml:space="preserve">t_dokusya の dokusya_busu が0で保存されること、t_dokusya_rireki の kaiyaku_flg が TRUE、shinki_flg が FALSE で保存されること
 </t>
           </r>
           <r>
@@ -13290,7 +13341,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・「購読者情報と同じ」チェック時はDB保存時に購読者情報からコピーすること（機能定義 §9.1）</t>
+            <t xml:space="preserve">・解約を選んで登録する場合は購読部数を0にし、kaiyaku_flg=TRUE に設定すること（機能定義 §8.1）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・二重請求防止のため購読部数は解約時に強制的に0となること</t>
           </r>
         </is>
       </c>
@@ -13344,20 +13403,20 @@
       <c r="BP40" s="10" t="n"/>
       <c r="BQ40" s="11" t="n"/>
     </row>
-    <row r="41" ht="400" customHeight="1">
+    <row r="41" ht="288" customHeight="1">
       <c r="A41" s="44" t="n">
         <v>26</v>
       </c>
       <c r="B41" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-026</t>
+          <t>ACSMS-TC-011-025</t>
         </is>
       </c>
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="46" t="inlineStr">
         <is>
-          <t>新規登録 — 全項目未入力時の統合バリデーション</t>
+          <t>新規登録 — 配達先「購読者情報と同じ」時のコピー保存</t>
         </is>
       </c>
       <c r="F41" s="10" t="n"/>
@@ -13367,7 +13426,8 @@
       <c r="J41" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・購読者情報登録画面（新規作成モード）を開いた状態</t>
+・購読種別=紙版
+・「購読者情報と同じ」（haitatsu_same_flg）をチェック</t>
         </is>
       </c>
       <c r="K41" s="10" t="n"/>
@@ -13392,7 +13452,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">全項目を空欄のまま「承認・登録」ボタンを押下
+            <t xml:space="preserve">購読者氏名・住所等を入力し、「購読者情報と同じ」をチェックして「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -13409,7 +13469,39 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DevTools の Network タブで POST `/api/v1/dokusya` のレスポンスを確認</t>
+            <t xml:space="preserve">DBで以下クエリを実行し、配達先情報を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT haitatsu_same_flg, haitatsu_yubin_no, haitatsu_shimei_sei
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya WHERE dokusya_id = :new_dokusya_id;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>```</t>
           </r>
         </is>
       </c>
@@ -13435,7 +13527,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">各必須項目の下に必須入力エラー `必須項目です。` が表示されること、登録処理が実行されないこと
+            <t xml:space="preserve">登録処理が実行されること、登録完了メッセージ `登録しました。` が表示されること
 </t>
           </r>
           <r>
@@ -13452,7 +13544,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、メッセージ `入力値が不正です。詳細はerrorsフィールドを確認してください。`、`errors` 配列に shimei_sei・yubin_no 等の項目別メッセージが含まれること）
+            <t xml:space="preserve">haitatsu_same_flg が true で保存されること、配達先項目（haitatsu_yubin_no・haitatsu_shimei_sei 等）に購読者情報からコピーされた値が保存されること
 </t>
           </r>
           <r>
@@ -13469,15 +13561,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・クライアント側のデータチェック（必須・フォーマット・相関）後、サーバー側でも再度バリデーションを行うこと（機能定義 §2.1, §2.5）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・バリデーションエラーは `errors` 配列で項目別に返却されること</t>
+            <t>・「購読者情報と同じ」チェック時はDB保存時に購読者情報からコピーすること（機能定義 §9.1）</t>
           </r>
         </is>
       </c>
@@ -13489,7 +13573,7 @@
       <c r="AD41" s="11" t="n"/>
       <c r="AE41" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF41" s="11" t="n"/>
@@ -13531,20 +13615,20 @@
       <c r="BP41" s="10" t="n"/>
       <c r="BQ41" s="11" t="n"/>
     </row>
-    <row r="42" ht="256" customHeight="1">
+    <row r="42" ht="400" customHeight="1">
       <c r="A42" s="44" t="n">
         <v>27</v>
       </c>
       <c r="B42" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-027</t>
+          <t>ACSMS-TC-011-026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="46" t="inlineStr">
         <is>
-          <t>新規登録 — 戻るボタンによるキャンセル</t>
+          <t>新規登録 — 全項目未入力時の統合バリデーション</t>
         </is>
       </c>
       <c r="F42" s="10" t="n"/>
@@ -13554,7 +13638,7 @@
       <c r="J42" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・購読者情報登録画面（新規作成モード）で一部項目を入力済み</t>
+・購読者情報登録画面（新規作成モード）を開いた状態</t>
         </is>
       </c>
       <c r="K42" s="10" t="n"/>
@@ -13579,7 +13663,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「前の画面に戻る」ボタンを押下
+            <t xml:space="preserve">全項目を空欄のまま「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -13596,7 +13680,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>遷移先画面と、入力したデータの保存有無を確認</t>
+            <t>DevTools の Network タブで POST `/api/v1/dokusya` のレスポンスを確認</t>
           </r>
         </is>
       </c>
@@ -13622,7 +13706,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">購読者明細検索画面へ遷移すること
+            <t xml:space="preserve">各必須項目の下に必須入力エラー `必須項目です。` が表示されること、登録処理が実行されないこと
 </t>
           </r>
           <r>
@@ -13639,7 +13723,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">入力したデータが保存されないこと（t_dokusya に新規データが登録されないこと）
+            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、メッセージ `入力値が不正です。詳細はerrorsフィールドを確認してください。`、`errors` 配列に shimei_sei・yubin_no 等の項目別メッセージが含まれること）
 </t>
           </r>
           <r>
@@ -13656,15 +13740,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・「前の画面に戻る」ボタンを押下すると購読者明細検索画面へ遷移すること（機能定義 §16）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・フォームに入力されたデータは保存されないこと</t>
+            <t xml:space="preserve">・クライアント側のデータチェック（必須・フォーマット・相関）後、サーバー側でも再度バリデーションを行うこと（機能定義 §2.1, §2.5）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・バリデーションエラーは `errors` 配列で項目別に返却されること</t>
           </r>
         </is>
       </c>
@@ -13676,7 +13760,7 @@
       <c r="AD42" s="11" t="n"/>
       <c r="AE42" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF42" s="11" t="n"/>
@@ -13710,12 +13794,7 @@
       <c r="BH42" s="45" t="inlineStr"/>
       <c r="BI42" s="10" t="n"/>
       <c r="BJ42" s="11" t="n"/>
-      <c r="BK42" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BK42" s="46" t="inlineStr"/>
       <c r="BL42" s="10" t="n"/>
       <c r="BM42" s="10" t="n"/>
       <c r="BN42" s="10" t="n"/>
@@ -13723,74 +13802,191 @@
       <c r="BP42" s="10" t="n"/>
       <c r="BQ42" s="11" t="n"/>
     </row>
-    <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="32" t="inlineStr">
-        <is>
-          <t>業務ロジック更新（編集・承認・否認）</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n"/>
+    <row r="43" ht="256" customHeight="1">
+      <c r="A43" s="44" t="n">
+        <v>28</v>
+      </c>
+      <c r="B43" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-027</t>
+        </is>
+      </c>
       <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="46" t="inlineStr">
+        <is>
+          <t>新規登録 — 戻るボタンによるキャンセル</t>
+        </is>
+      </c>
       <c r="F43" s="10" t="n"/>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="n"/>
-      <c r="J43" s="10" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・購読者情報登録画面（新規作成モード）で一部項目を入力済み</t>
+        </is>
+      </c>
       <c r="K43" s="10" t="n"/>
       <c r="L43" s="10" t="n"/>
       <c r="M43" s="10" t="n"/>
       <c r="N43" s="10" t="n"/>
       <c r="O43" s="10" t="n"/>
-      <c r="P43" s="10" t="n"/>
-      <c r="Q43" s="10" t="n"/>
+      <c r="P43" s="11" t="n"/>
+      <c r="Q43" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「前の画面に戻る」ボタンを押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>遷移先画面と、入力したデータの保存有無を確認</t>
+          </r>
+        </is>
+      </c>
       <c r="R43" s="10" t="n"/>
       <c r="S43" s="10" t="n"/>
       <c r="T43" s="10" t="n"/>
       <c r="U43" s="10" t="n"/>
       <c r="V43" s="10" t="n"/>
-      <c r="W43" s="10" t="n"/>
-      <c r="X43" s="10" t="n"/>
+      <c r="W43" s="11" t="n"/>
+      <c r="X43" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読者明細検索画面へ遷移すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">入力したデータが保存されないこと（t_dokusya に新規データが登録されないこと）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「前の画面に戻る」ボタンを押下すると購読者明細検索画面へ遷移すること（機能定義 §16）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・フォームに入力されたデータは保存されないこと</t>
+          </r>
+        </is>
+      </c>
       <c r="Y43" s="10" t="n"/>
       <c r="Z43" s="10" t="n"/>
       <c r="AA43" s="10" t="n"/>
       <c r="AB43" s="10" t="n"/>
       <c r="AC43" s="10" t="n"/>
-      <c r="AD43" s="10" t="n"/>
-      <c r="AE43" s="10" t="n"/>
-      <c r="AF43" s="10" t="n"/>
-      <c r="AG43" s="10" t="n"/>
+      <c r="AD43" s="11" t="n"/>
+      <c r="AE43" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF43" s="11" t="n"/>
+      <c r="AG43" s="45" t="inlineStr"/>
       <c r="AH43" s="10" t="n"/>
-      <c r="AI43" s="10" t="n"/>
-      <c r="AJ43" s="10" t="n"/>
+      <c r="AI43" s="11" t="n"/>
+      <c r="AJ43" s="45" t="inlineStr"/>
       <c r="AK43" s="10" t="n"/>
-      <c r="AL43" s="10" t="n"/>
-      <c r="AM43" s="10" t="n"/>
+      <c r="AL43" s="11" t="n"/>
+      <c r="AM43" s="45" t="inlineStr"/>
       <c r="AN43" s="10" t="n"/>
-      <c r="AO43" s="10" t="n"/>
-      <c r="AP43" s="10" t="n"/>
+      <c r="AO43" s="11" t="n"/>
+      <c r="AP43" s="45" t="inlineStr"/>
       <c r="AQ43" s="10" t="n"/>
-      <c r="AR43" s="10" t="n"/>
-      <c r="AS43" s="10" t="n"/>
+      <c r="AR43" s="11" t="n"/>
+      <c r="AS43" s="45" t="inlineStr"/>
       <c r="AT43" s="10" t="n"/>
-      <c r="AU43" s="10" t="n"/>
-      <c r="AV43" s="10" t="n"/>
+      <c r="AU43" s="11" t="n"/>
+      <c r="AV43" s="45" t="inlineStr"/>
       <c r="AW43" s="10" t="n"/>
-      <c r="AX43" s="10" t="n"/>
-      <c r="AY43" s="10" t="n"/>
+      <c r="AX43" s="11" t="n"/>
+      <c r="AY43" s="45" t="inlineStr"/>
       <c r="AZ43" s="10" t="n"/>
-      <c r="BA43" s="10" t="n"/>
-      <c r="BB43" s="10" t="n"/>
+      <c r="BA43" s="11" t="n"/>
+      <c r="BB43" s="45" t="inlineStr"/>
       <c r="BC43" s="10" t="n"/>
-      <c r="BD43" s="10" t="n"/>
-      <c r="BE43" s="10" t="n"/>
+      <c r="BD43" s="11" t="n"/>
+      <c r="BE43" s="45" t="inlineStr"/>
       <c r="BF43" s="10" t="n"/>
-      <c r="BG43" s="10" t="n"/>
-      <c r="BH43" s="10" t="n"/>
+      <c r="BG43" s="11" t="n"/>
+      <c r="BH43" s="45" t="inlineStr"/>
       <c r="BI43" s="10" t="n"/>
-      <c r="BJ43" s="10" t="n"/>
-      <c r="BK43" s="10" t="n"/>
+      <c r="BJ43" s="11" t="n"/>
+      <c r="BK43" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL43" s="10" t="n"/>
       <c r="BM43" s="10" t="n"/>
       <c r="BN43" s="10" t="n"/>
@@ -13798,228 +13994,74 @@
       <c r="BP43" s="10" t="n"/>
       <c r="BQ43" s="11" t="n"/>
     </row>
-    <row r="44" ht="450" customHeight="1">
-      <c r="A44" s="44" t="n">
-        <v>28</v>
-      </c>
-      <c r="B44" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-011-028</t>
-        </is>
-      </c>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>業務ロジック更新（編集・承認・否認）</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
       <c r="C44" s="10" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="46" t="inlineStr">
-        <is>
-          <t>編集モード フォームロード（既存データ反映）</t>
-        </is>
-      </c>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
       <c r="F44" s="10" t="n"/>
       <c r="G44" s="10" t="n"/>
       <c r="H44" s="10" t="n"/>
-      <c r="I44" s="11" t="n"/>
-      <c r="J44" s="46" t="inlineStr">
-        <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・購読種別=紙版 の購読者（dokusya_id=100）が存在</t>
-        </is>
-      </c>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
       <c r="K44" s="10" t="n"/>
       <c r="L44" s="10" t="n"/>
       <c r="M44" s="10" t="n"/>
       <c r="N44" s="10" t="n"/>
       <c r="O44" s="10" t="n"/>
-      <c r="P44" s="11" t="n"/>
-      <c r="Q44" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">購読者明細検索画面の一覧から対象購読者の行を押下し、編集モードで購読者情報登録画面を開く
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">DevTools の Network タブで GET `/api/v1/dokusya/100` のレスポンスを確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>フォーム各項目の値と、購読者ID（dokusya_id）・履歴No（rireki_no）の表示を確認</t>
-          </r>
-        </is>
-      </c>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n"/>
       <c r="R44" s="10" t="n"/>
       <c r="S44" s="10" t="n"/>
       <c r="T44" s="10" t="n"/>
       <c r="U44" s="10" t="n"/>
       <c r="V44" s="10" t="n"/>
-      <c r="W44" s="11" t="n"/>
-      <c r="X44" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">編集モードで購読者情報登録画面が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること（対象購読者の全項目が `data` に含まれること、bank_shiten_id がプルダウン再ハイドレーション用に返却されること）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">フォーム各項目に既存データが反映されること、購読者ID（dokusya_id）が変更不可で表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・編集モードでは IDで購読者のデータを取得し、フォームに反映すること（機能定義 §15.1）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・購読者IDは変更不可とすること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・データ取得失敗の場合は ACSMS-MSG-011-016 `購読者ID #{id} が見つかりません。` を表示すること</t>
-          </r>
-        </is>
-      </c>
+      <c r="W44" s="10" t="n"/>
+      <c r="X44" s="10" t="n"/>
       <c r="Y44" s="10" t="n"/>
       <c r="Z44" s="10" t="n"/>
       <c r="AA44" s="10" t="n"/>
       <c r="AB44" s="10" t="n"/>
       <c r="AC44" s="10" t="n"/>
-      <c r="AD44" s="11" t="n"/>
-      <c r="AE44" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF44" s="11" t="n"/>
-      <c r="AG44" s="45" t="inlineStr"/>
+      <c r="AD44" s="10" t="n"/>
+      <c r="AE44" s="10" t="n"/>
+      <c r="AF44" s="10" t="n"/>
+      <c r="AG44" s="10" t="n"/>
       <c r="AH44" s="10" t="n"/>
-      <c r="AI44" s="11" t="n"/>
-      <c r="AJ44" s="45" t="inlineStr"/>
+      <c r="AI44" s="10" t="n"/>
+      <c r="AJ44" s="10" t="n"/>
       <c r="AK44" s="10" t="n"/>
-      <c r="AL44" s="11" t="n"/>
-      <c r="AM44" s="45" t="inlineStr"/>
+      <c r="AL44" s="10" t="n"/>
+      <c r="AM44" s="10" t="n"/>
       <c r="AN44" s="10" t="n"/>
-      <c r="AO44" s="11" t="n"/>
-      <c r="AP44" s="45" t="inlineStr"/>
+      <c r="AO44" s="10" t="n"/>
+      <c r="AP44" s="10" t="n"/>
       <c r="AQ44" s="10" t="n"/>
-      <c r="AR44" s="11" t="n"/>
-      <c r="AS44" s="45" t="inlineStr"/>
+      <c r="AR44" s="10" t="n"/>
+      <c r="AS44" s="10" t="n"/>
       <c r="AT44" s="10" t="n"/>
-      <c r="AU44" s="11" t="n"/>
-      <c r="AV44" s="45" t="inlineStr"/>
+      <c r="AU44" s="10" t="n"/>
+      <c r="AV44" s="10" t="n"/>
       <c r="AW44" s="10" t="n"/>
-      <c r="AX44" s="11" t="n"/>
-      <c r="AY44" s="45" t="inlineStr"/>
+      <c r="AX44" s="10" t="n"/>
+      <c r="AY44" s="10" t="n"/>
       <c r="AZ44" s="10" t="n"/>
-      <c r="BA44" s="11" t="n"/>
-      <c r="BB44" s="45" t="inlineStr"/>
+      <c r="BA44" s="10" t="n"/>
+      <c r="BB44" s="10" t="n"/>
       <c r="BC44" s="10" t="n"/>
-      <c r="BD44" s="11" t="n"/>
-      <c r="BE44" s="45" t="inlineStr"/>
+      <c r="BD44" s="10" t="n"/>
+      <c r="BE44" s="10" t="n"/>
       <c r="BF44" s="10" t="n"/>
-      <c r="BG44" s="11" t="n"/>
-      <c r="BH44" s="45" t="inlineStr"/>
+      <c r="BG44" s="10" t="n"/>
+      <c r="BH44" s="10" t="n"/>
       <c r="BI44" s="10" t="n"/>
-      <c r="BJ44" s="11" t="n"/>
-      <c r="BK44" s="46" t="inlineStr"/>
+      <c r="BJ44" s="10" t="n"/>
+      <c r="BK44" s="10" t="n"/>
       <c r="BL44" s="10" t="n"/>
       <c r="BM44" s="10" t="n"/>
       <c r="BN44" s="10" t="n"/>
@@ -14033,14 +14075,14 @@
       </c>
       <c r="B45" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-029</t>
+          <t>ACSMS-TC-011-028</t>
         </is>
       </c>
       <c r="C45" s="10" t="n"/>
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="46" t="inlineStr">
         <is>
-          <t>更新 正常系（履歴追記方式 + 監査ログ）</t>
+          <t>編集モード フォームロード（既存データ反映）</t>
         </is>
       </c>
       <c r="F45" s="10" t="n"/>
@@ -14050,7 +14092,7 @@
       <c r="J45" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・購読種別=紙版 の購読者（dokusya_id=100, 現 rireki_no=1）が存在</t>
+・購読種別=紙版 の購読者（dokusya_id=100）が存在</t>
         </is>
       </c>
       <c r="K45" s="10" t="n"/>
@@ -14075,7 +14117,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">編集モードで購読者情報登録画面を開き、購読部数（dokusya_busu）を1から2へ変更して「承認・登録」ボタンを押下
+            <t xml:space="preserve">購読者明細検索画面の一覧から対象購読者の行を押下し、編集モードで購読者情報登録画面を開く
 </t>
           </r>
           <r>
@@ -14092,7 +14134,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">画面遷移とメッセージを確認
+            <t xml:space="preserve">DevTools の Network タブで GET `/api/v1/dokusya/100` のレスポンスを確認
 </t>
           </r>
           <r>
@@ -14109,136 +14151,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DBで以下クエリを実行し、本体・履歴レコードを確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT rireki_no, dokusya_busu FROM t_dokusya WHERE dokusya_id = 100;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT rireki_no, saishin_data_flg, zougen_hokoku_flg
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_dokusya_rireki
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = 100
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY rireki_no DESC;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">DBで以下クエリを実行し、監査ログを確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT operation, result_status, before_value, after_value
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_log
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE target_table = 't_dokusya' AND target_id = 100
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY log_datetime DESC
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">LIMIT 1;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>```</t>
+            <t>フォーム各項目の値と、購読者ID（dokusya_id）・履歴No（rireki_no）の表示を確認</t>
           </r>
         </is>
       </c>
@@ -14264,7 +14177,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">更新処理が実行されること
+            <t xml:space="preserve">編集モードで購読者情報登録画面が表示されること
 </t>
           </r>
           <r>
@@ -14281,7 +14194,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること、更新完了メッセージ `更新しました。`（ACSMS-MSG-011-015）が表示されること、購読者明細検索画面へ戻ること
+            <t xml:space="preserve">HTTPステータスコード200が返却されること（対象購読者の全項目が `data` に含まれること、bank_shiten_id がプルダウン再ハイドレーション用に返却されること）
 </t>
           </r>
           <r>
@@ -14298,24 +14211,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">t_dokusya の rireki_no が2に更新され dokusya_busu が2となること、t_dokusya_rireki に新履歴（rireki_no=2, saishin_data_flg=true, zougen_hokoku_flg=true）が追記され、旧履歴（rireki_no=1）の saishin_data_flg が false に更新されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">t_log に operation=`UPDATE`, result_status=1 のレコードが記録され、before_value に更新前データ、after_value に更新後データが格納されること
+            <t xml:space="preserve">フォーム各項目に既存データが反映されること、購読者ID（dokusya_id）が変更不可で表示されること
 </t>
           </r>
           <r>
@@ -14332,23 +14228,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・更新は既存レコードの物理更新ではなく、新しい履歴番号でのレコード追記を行うこと（機能定義 §15.3）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・旧履歴の最新データフラグを false に更新し、新履歴の最新データフラグを true とすること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・更新（業務書き込み）と監査ログは単一トランザクションで実行されること</t>
+            <t xml:space="preserve">・編集モードでは IDで購読者のデータを取得し、フォームに反映すること（機能定義 §15.1）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・購読者IDは変更不可とすること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・データ取得失敗の場合は ACSMS-MSG-011-016 `購読者ID #{id} が見つかりません。` を表示すること</t>
           </r>
         </is>
       </c>
@@ -14402,20 +14298,20 @@
       <c r="BP45" s="10" t="n"/>
       <c r="BQ45" s="11" t="n"/>
     </row>
-    <row r="46" ht="448" customHeight="1">
+    <row r="46" ht="450" customHeight="1">
       <c r="A46" s="44" t="n">
         <v>30</v>
       </c>
       <c r="B46" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-030</t>
+          <t>ACSMS-TC-011-029</t>
         </is>
       </c>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="46" t="inlineStr">
         <is>
-          <t>純電子版（クレカ決済）・併読読者の読み取り専用制御</t>
+          <t>更新 正常系（履歴追記方式 + 監査ログ）</t>
         </is>
       </c>
       <c r="F46" s="10" t="n"/>
@@ -14425,7 +14321,7 @@
       <c r="J46" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・購読種別=電子版（クレカ決済）の購読者（dokusya_id=300）が存在</t>
+・購読種別=紙版 の購読者（dokusya_id=100, 現 rireki_no=1）が存在</t>
         </is>
       </c>
       <c r="K46" s="10" t="n"/>
@@ -14450,7 +14346,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">購読者明細検索画面の一覧から電子版クレカ決済者の行を押下し、編集モードで画面を開く
+            <t xml:space="preserve">編集モードで購読者情報登録画面を開き、購読部数（dokusya_busu）を1から2へ変更して「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -14467,7 +14363,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">フォーム各項目の入力可否を確認
+            <t xml:space="preserve">画面遷移とメッセージを確認
 </t>
           </r>
           <r>
@@ -14484,7 +14380,136 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DevTools の Network タブで PUT `/api/v1/dokusya/300` に編集内容を含めて直接送信</t>
+            <t xml:space="preserve">DBで以下クエリを実行し、本体・履歴レコードを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT rireki_no, dokusya_busu FROM t_dokusya WHERE dokusya_id = 100;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT rireki_no, saishin_data_flg, zougen_hokoku_flg
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya_rireki
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE dokusya_id = 100
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY rireki_no DESC;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DBで以下クエリを実行し、監査ログを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT operation, result_status, before_value, after_value
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_log
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE target_table = 't_dokusya' AND target_id = 100
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY log_datetime DESC
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">LIMIT 1;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>```</t>
           </r>
         </is>
       </c>
@@ -14510,7 +14535,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">編集モードで購読者情報登録画面が参照モードで表示されること
+            <t xml:space="preserve">更新処理が実行されること
 </t>
           </r>
           <r>
@@ -14527,7 +14552,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">購読開始日（dokusya_kaishi_date）・購読中止日（dokusya_chushi_date）等が読み取り専用で表示されること（電子版読者管理システムからの連携データ）
+            <t xml:space="preserve">HTTPステータスコード200が返却されること、更新完了メッセージ `更新しました。`（ACSMS-MSG-011-015）が表示されること、購読者明細検索画面へ戻ること
 </t>
           </r>
           <r>
@@ -14544,7 +14569,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">バックエンド側で電子版クレカ決済者の編集が拒否されること（業務ルールにより編集不可）
+            <t xml:space="preserve">t_dokusya の rireki_no が2に更新され dokusya_busu が2となること、t_dokusya_rireki に新履歴（rireki_no=2, saishin_data_flg=true, zougen_hokoku_flg=true）が追記され、旧履歴（rireki_no=1）の saishin_data_flg が false に更新されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">t_log に operation=`UPDATE`, result_status=1 のレコードが記録され、before_value に更新前データ、after_value に更新後データが格納されること
 </t>
           </r>
           <r>
@@ -14561,15 +14603,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・純粋な電子版（クレカ決済）読者は読者管理が外部Webシステム側で主導されるため、本画面では参照のみ（読み取り専用）とすること（機能定義 §15.1）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・電子版クレカ決済者・併読者は編集・削除不可（業務ルール、機能定義 §1.2）</t>
+            <t xml:space="preserve">・更新は既存レコードの物理更新ではなく、新しい履歴番号でのレコード追記を行うこと（機能定義 §15.3）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・旧履歴の最新データフラグを false に更新し、新履歴の最新データフラグを true とすること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・更新（業務書き込み）と監査ログは単一トランザクションで実行されること</t>
           </r>
         </is>
       </c>
@@ -14581,7 +14631,7 @@
       <c r="AD46" s="11" t="n"/>
       <c r="AE46" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF46" s="11" t="n"/>
@@ -14623,20 +14673,20 @@
       <c r="BP46" s="10" t="n"/>
       <c r="BQ46" s="11" t="n"/>
     </row>
-    <row r="47" ht="400" customHeight="1">
+    <row r="47" ht="448" customHeight="1">
       <c r="A47" s="44" t="n">
         <v>31</v>
       </c>
       <c r="B47" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-031</t>
+          <t>ACSMS-TC-011-030</t>
         </is>
       </c>
       <c r="C47" s="10" t="n"/>
       <c r="D47" s="11" t="n"/>
       <c r="E47" s="46" t="inlineStr">
         <is>
-          <t>同時編集競合（楽観ロック）</t>
+          <t>純電子版（クレカ決済）・併読読者の読み取り専用制御</t>
         </is>
       </c>
       <c r="F47" s="10" t="n"/>
@@ -14646,7 +14696,7 @@
       <c r="J47" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・購読者（dokusya_id=100）を2つのブラウザタブで編集モードで開いた状態</t>
+・購読種別=電子版（クレカ決済）の購読者（dokusya_id=300）が存在</t>
         </is>
       </c>
       <c r="K47" s="10" t="n"/>
@@ -14671,7 +14721,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">タブAで購読部数（dokusya_busu）を変更し「承認・登録」ボタンを押下（更新成功）
+            <t xml:space="preserve">購読者明細検索画面の一覧から電子版クレカ決済者の行を押下し、編集モードで画面を開く
 </t>
           </r>
           <r>
@@ -14688,7 +14738,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">タブBで（タブA更新前のデータのまま）市町村郡（shikuchoson）を変更し「承認・登録」ボタンを押下
+            <t xml:space="preserve">フォーム各項目の入力可否を確認
 </t>
           </r>
           <r>
@@ -14705,47 +14755,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DBで以下クエリを実行し、最新履歴の内容を確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT rireki_no, dokusya_busu, shikuchoson
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_dokusya_rireki
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = 100 AND saishin_data_flg = TRUE;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>```</t>
+            <t>DevTools の Network タブで PUT `/api/v1/dokusya/300` に編集内容を含めて直接送信</t>
           </r>
         </is>
       </c>
@@ -14771,7 +14781,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">タブAの更新処理が実行されること、更新完了メッセージ `更新しました。` が表示されること
+            <t xml:space="preserve">編集モードで購読者情報登録画面が参照モードで表示されること
 </t>
           </r>
           <r>
@@ -14788,7 +14798,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">タブBの更新時に競合が検知されること（後勝ち更新の場合はタブAの変更が失われないこと）
+            <t xml:space="preserve">購読開始日（dokusya_kaishi_date）・購読中止日（dokusya_chushi_date）等が読み取り専用で表示されること（電子版読者管理システムからの連携データ）
 </t>
           </r>
           <r>
@@ -14805,7 +14815,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">データ整合性が保たれること、saishin_data_flg=TRUE の履歴が1件のみであること
+            <t xml:space="preserve">バックエンド側で電子版クレカ決済者の編集が拒否されること（業務ルールにより編集不可）
 </t>
           </r>
           <r>
@@ -14822,15 +14832,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・履歴テーブルは追記専用であり、最新データフラグ（saishin_data_flg）が TRUE のレコードは購読者IDごとに1件のみとすること（機能定義 §14.2）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・楽観ロックの実装有無は設計仕様に従い、未実装の場合は別途バグチケットを起票すること</t>
+            <t xml:space="preserve">・純粋な電子版（クレカ決済）読者は読者管理が外部Webシステム側で主導されるため、本画面では参照のみ（読み取り専用）とすること（機能定義 §15.1）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・電子版クレカ決済者・併読者は編集・削除不可（業務ルール、機能定義 §1.2）</t>
           </r>
         </is>
       </c>
@@ -14876,11 +14886,7 @@
       <c r="BH47" s="45" t="inlineStr"/>
       <c r="BI47" s="10" t="n"/>
       <c r="BJ47" s="11" t="n"/>
-      <c r="BK47" s="46" t="inlineStr">
-        <is>
-          <t>楽観ロック競合時の専用メッセージは設計仕様に未定義のため、本TCではHTTPコードとデータ整合性のみ検証する（メッセージは仕様確認待ち）。</t>
-        </is>
-      </c>
+      <c r="BK47" s="46" t="inlineStr"/>
       <c r="BL47" s="10" t="n"/>
       <c r="BM47" s="10" t="n"/>
       <c r="BN47" s="10" t="n"/>
@@ -14888,20 +14894,20 @@
       <c r="BP47" s="10" t="n"/>
       <c r="BQ47" s="11" t="n"/>
     </row>
-    <row r="48" ht="450" customHeight="1">
+    <row r="48" ht="400" customHeight="1">
       <c r="A48" s="44" t="n">
         <v>32</v>
       </c>
       <c r="B48" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-032</t>
+          <t>ACSMS-TC-011-031</t>
         </is>
       </c>
       <c r="C48" s="10" t="n"/>
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="46" t="inlineStr">
         <is>
-          <t>電子版承認 正常系（denshi_shonin_status 0→1）</t>
+          <t>同時編集競合（楽観ロック）</t>
         </is>
       </c>
       <c r="F48" s="10" t="n"/>
@@ -14910,8 +14916,8 @@
       <c r="I48" s="11" t="n"/>
       <c r="J48" s="46" t="inlineStr">
         <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属、電子版取扱フラグあり）
-・購読種別=電子版 かつ denshi_shonin_status=0（承認待ち）の購読者（dokusya_id=200, 現 rireki_no=1）が存在</t>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・購読者（dokusya_id=100）を2つのブラウザタブで編集モードで開いた状態</t>
         </is>
       </c>
       <c r="K48" s="10" t="n"/>
@@ -14936,7 +14942,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">承認待ちの購読者を編集モードで開き、「承認・登録」ボタンを押下
+            <t xml:space="preserve">タブAで購読部数（dokusya_busu）を変更し「承認・登録」ボタンを押下（更新成功）
 </t>
           </r>
           <r>
@@ -14953,7 +14959,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">画面遷移とメッセージを確認
+            <t xml:space="preserve">タブBで（タブA更新前のデータのまま）市町村郡（shikuchoson）を変更し「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -14970,7 +14976,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DBで以下クエリを実行し、ステータスと履歴を確認
+            <t xml:space="preserve">DBで以下クエリを実行し、最新履歴の内容を確認
 </t>
           </r>
           <r>
@@ -14986,15 +14992,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">SELECT denshi_shonin_status, rireki_no FROM t_dokusya WHERE dokusya_id = 200;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT rireki_no, denshi_shonin_status, saishin_data_flg, henko_riyu
+            <t xml:space="preserve">SELECT rireki_no, dokusya_busu, shikuchoson
 </t>
           </r>
           <r>
@@ -15010,15 +15008,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = 200
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY rireki_no DESC;
+            <t xml:space="preserve">WHERE dokusya_id = 100 AND saishin_data_flg = TRUE;
 </t>
           </r>
           <r>
@@ -15052,7 +15042,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">承認処理が実行されること
+            <t xml:space="preserve">タブAの更新処理が実行されること、更新完了メッセージ `更新しました。` が表示されること
 </t>
           </r>
           <r>
@@ -15069,7 +15059,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること（`data.denshi_shonin_status = 1`）、メッセージ `承認しました。` が表示されること
+            <t xml:space="preserve">タブBの更新時に競合が検知されること（後勝ち更新の場合はタブAの変更が失われないこと）
 </t>
           </r>
           <r>
@@ -15086,7 +15076,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">t_dokusya の denshi_shonin_status が1に更新されること、t_dokusya_rireki に新履歴（denshi_shonin_status=1, saishin_data_flg=true, henko_riyu=`電子版承認`）が追記されること
+            <t xml:space="preserve">データ整合性が保たれること、saishin_data_flg=TRUE の履歴が1件のみであること
 </t>
           </r>
           <r>
@@ -15103,23 +15093,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・「承認」ボタン押下で APIが denshi_shonin_status=1（承認済み）に設定し、新規履歴レコードを作成すること（機能定義 §3.3）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・PUT `/api/v1/dokusya/{dokusya_id}/approve` を呼び出すこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・承認（業務書き込み）と監査ログは単一トランザクションで実行されること</t>
+            <t xml:space="preserve">・履歴テーブルは追記専用であり、最新データフラグ（saishin_data_flg）が TRUE のレコードは購読者IDごとに1件のみとすること（機能定義 §14.2）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・楽観ロックの実装有無は設計仕様に従い、未実装の場合は別途バグチケットを起票すること</t>
           </r>
         </is>
       </c>
@@ -15131,7 +15113,7 @@
       <c r="AD48" s="11" t="n"/>
       <c r="AE48" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF48" s="11" t="n"/>
@@ -15165,7 +15147,11 @@
       <c r="BH48" s="45" t="inlineStr"/>
       <c r="BI48" s="10" t="n"/>
       <c r="BJ48" s="11" t="n"/>
-      <c r="BK48" s="46" t="inlineStr"/>
+      <c r="BK48" s="46" t="inlineStr">
+        <is>
+          <t>楽観ロック競合時の専用メッセージは設計仕様に未定義のため、本TCではHTTPコードとデータ整合性のみ検証する（メッセージは仕様確認待ち）。</t>
+        </is>
+      </c>
       <c r="BL48" s="10" t="n"/>
       <c r="BM48" s="10" t="n"/>
       <c r="BN48" s="10" t="n"/>
@@ -15179,14 +15165,14 @@
       </c>
       <c r="B49" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-033</t>
+          <t>ACSMS-TC-011-032</t>
         </is>
       </c>
       <c r="C49" s="10" t="n"/>
       <c r="D49" s="11" t="n"/>
       <c r="E49" s="46" t="inlineStr">
         <is>
-          <t>電子版否認 正常系（否認確認 + denshi_shonin_status 0→2）</t>
+          <t>電子版承認 正常系（denshi_shonin_status 0→1）</t>
         </is>
       </c>
       <c r="F49" s="10" t="n"/>
@@ -15196,7 +15182,7 @@
       <c r="J49" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属、電子版取扱フラグあり）
-・購読種別=電子版 かつ denshi_shonin_status=0（承認待ち）の購読者（dokusya_id=201）が存在</t>
+・購読種別=電子版 かつ denshi_shonin_status=0（承認待ち）の購読者（dokusya_id=200, 現 rireki_no=1）が存在</t>
         </is>
       </c>
       <c r="K49" s="10" t="n"/>
@@ -15221,7 +15207,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">承認待ちの購読者を編集モードで開き、「承認しない」ボタンの表示を確認
+            <t xml:space="preserve">承認待ちの購読者を編集モードで開き、「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -15238,7 +15224,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「承認しない」ボタンを押下し、否認確認ダイアログで「はい」を押下
+            <t xml:space="preserve">画面遷移とメッセージを確認
 </t>
           </r>
           <r>
@@ -15255,23 +15241,6 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">画面遷移とメッセージを確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
             <t xml:space="preserve">DBで以下クエリを実行し、ステータスと履歴を確認
 </t>
           </r>
@@ -15288,15 +15257,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">SELECT denshi_shonin_status FROM t_dokusya WHERE dokusya_id = 201;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT denshi_shonin_status, henko_riyu
+            <t xml:space="preserve">SELECT denshi_shonin_status, rireki_no FROM t_dokusya WHERE dokusya_id = 200;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT rireki_no, denshi_shonin_status, saishin_data_flg, henko_riyu
 </t>
           </r>
           <r>
@@ -15312,7 +15281,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = 201 AND saishin_data_flg = TRUE;
+            <t xml:space="preserve">WHERE dokusya_id = 200
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY rireki_no DESC;
 </t>
           </r>
           <r>
@@ -15346,7 +15323,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">denshi_shonin_status=0（承認待ち）のため「承認しない」ボタンが表示されること
+            <t xml:space="preserve">承認処理が実行されること
 </t>
           </r>
           <r>
@@ -15363,7 +15340,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">否認確認ダイアログが表示されること（メッセージ `電子版読者の登録を否認します。よろしいですか？`）、「はい」押下で否認処理が実行されること
+            <t xml:space="preserve">HTTPステータスコード200が返却されること（`data.denshi_shonin_status = 1`）、メッセージ `承認しました。` が表示されること
 </t>
           </r>
           <r>
@@ -15380,24 +15357,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること（`data.denshi_shonin_status = 2`）、メッセージ `否認しました。` が表示されること、購読者明細検索画面へ遷移すること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">t_dokusya の denshi_shonin_status が2に更新されること、t_dokusya_rireki の最新履歴に denshi_shonin_status=2, henko_riyu=`電子版否認` が記録されること
+            <t xml:space="preserve">t_dokusya の denshi_shonin_status が1に更新されること、t_dokusya_rireki に新履歴（denshi_shonin_status=1, saishin_data_flg=true, henko_riyu=`電子版承認`）が追記されること
 </t>
           </r>
           <r>
@@ -15414,23 +15374,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・denshi_shonin_status=0 の場合のみ「承認しない」ボタンを表示すること（機能定義 §4.1）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・「承認しない」押下で否認確認ダイアログ（ACSMS-MSG-011-014 `電子版読者の登録を否認します。よろしいですか？`）を表示すること（機能定義 §4.2）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・「はい」押下で PUT `/api/v1/dokusya/{dokusya_id}/reject` を呼び出し denshi_shonin_status=2 に設定すること（機能定義 §4.3）</t>
+            <t xml:space="preserve">・「承認」ボタン押下で APIが denshi_shonin_status=1（承認済み）に設定し、新規履歴レコードを作成すること（機能定義 §3.3）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・PUT `/api/v1/dokusya/{dokusya_id}/approve` を呼び出すこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・承認（業務書き込み）と監査ログは単一トランザクションで実行されること</t>
           </r>
         </is>
       </c>
@@ -15484,20 +15444,20 @@
       <c r="BP49" s="10" t="n"/>
       <c r="BQ49" s="11" t="n"/>
     </row>
-    <row r="50" ht="288" customHeight="1">
+    <row r="50" ht="450" customHeight="1">
       <c r="A50" s="44" t="n">
         <v>34</v>
       </c>
       <c r="B50" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-034</t>
+          <t>ACSMS-TC-011-033</t>
         </is>
       </c>
       <c r="C50" s="10" t="n"/>
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="46" t="inlineStr">
         <is>
-          <t>否認確認ダイアログ「いいえ」押下時の処理中断</t>
+          <t>電子版否認 正常系（否認確認 + denshi_shonin_status 0→2）</t>
         </is>
       </c>
       <c r="F50" s="10" t="n"/>
@@ -15507,7 +15467,7 @@
       <c r="J50" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属、電子版取扱フラグあり）
-・denshi_shonin_status=0（承認待ち）の購読者（dokusya_id=202）が存在</t>
+・購読種別=電子版 かつ denshi_shonin_status=0（承認待ち）の購読者（dokusya_id=201）が存在</t>
         </is>
       </c>
       <c r="K50" s="10" t="n"/>
@@ -15532,7 +15492,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">承認待ちの購読者を編集モードで開き、「承認しない」ボタンを押下
+            <t xml:space="preserve">承認待ちの購読者を編集モードで開き、「承認しない」ボタンの表示を確認
 </t>
           </r>
           <r>
@@ -15549,7 +15509,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">否認確認ダイアログで「いいえ」を押下
+            <t xml:space="preserve">「承認しない」ボタンを押下し、否認確認ダイアログで「はい」を押下
 </t>
           </r>
           <r>
@@ -15566,7 +15526,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DBで以下クエリを実行し、ステータスを確認
+            <t xml:space="preserve">画面遷移とメッセージを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DBで以下クエリを実行し、ステータスと履歴を確認
 </t>
           </r>
           <r>
@@ -15582,7 +15559,31 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">SELECT denshi_shonin_status FROM t_dokusya WHERE dokusya_id = 202;
+            <t xml:space="preserve">SELECT denshi_shonin_status FROM t_dokusya WHERE dokusya_id = 201;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT denshi_shonin_status, henko_riyu
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya_rireki
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE dokusya_id = 201 AND saishin_data_flg = TRUE;
 </t>
           </r>
           <r>
@@ -15616,7 +15617,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">否認確認ダイアログが表示されること
+            <t xml:space="preserve">denshi_shonin_status=0（承認待ち）のため「承認しない」ボタンが表示されること
 </t>
           </r>
           <r>
@@ -15633,7 +15634,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">否認処理が実行されないこと、現在の画面が維持されること
+            <t xml:space="preserve">否認確認ダイアログが表示されること（メッセージ `電子版読者の登録を否認します。よろしいですか？`）、「はい」押下で否認処理が実行されること
 </t>
           </r>
           <r>
@@ -15650,7 +15651,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">t_dokusya の denshi_shonin_status が0（承認待ち）のまま変更されないこと
+            <t xml:space="preserve">HTTPステータスコード200が返却されること（`data.denshi_shonin_status = 2`）、メッセージ `否認しました。` が表示されること、購読者明細検索画面へ遷移すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">t_dokusya の denshi_shonin_status が2に更新されること、t_dokusya_rireki の最新履歴に denshi_shonin_status=2, henko_riyu=`電子版否認` が記録されること
 </t>
           </r>
           <r>
@@ -15667,7 +15685,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・否認確認ダイアログで「いいえ」を押下する場合、何も行わず現在の画面を維持すること（機能定義 §4.4）</t>
+            <t xml:space="preserve">・denshi_shonin_status=0 の場合のみ「承認しない」ボタンを表示すること（機能定義 §4.1）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「承認しない」押下で否認確認ダイアログ（ACSMS-MSG-011-014 `電子版読者の登録を否認します。よろしいですか？`）を表示すること（機能定義 §4.2）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・「はい」押下で PUT `/api/v1/dokusya/{dokusya_id}/reject` を呼び出し denshi_shonin_status=2 に設定すること（機能定義 §4.3）</t>
           </r>
         </is>
       </c>
@@ -15721,20 +15755,20 @@
       <c r="BP50" s="10" t="n"/>
       <c r="BQ50" s="11" t="n"/>
     </row>
-    <row r="51" ht="450" customHeight="1">
+    <row r="51" ht="288" customHeight="1">
       <c r="A51" s="44" t="n">
         <v>35</v>
       </c>
       <c r="B51" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-035</t>
+          <t>ACSMS-TC-011-034</t>
         </is>
       </c>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="11" t="n"/>
       <c r="E51" s="46" t="inlineStr">
         <is>
-          <t>変更履歴一覧の取得・表示</t>
+          <t>否認確認ダイアログ「いいえ」押下時の処理中断</t>
         </is>
       </c>
       <c r="F51" s="10" t="n"/>
@@ -15743,8 +15777,8 @@
       <c r="I51" s="11" t="n"/>
       <c r="J51" s="46" t="inlineStr">
         <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・購読者（dokusya_id=100）に2件以上の履歴（rireki_no=1, 2）が存在</t>
+          <t>・role: JA_HONTEN（ja_id=100 所属、電子版取扱フラグあり）
+・denshi_shonin_status=0（承認待ち）の購読者（dokusya_id=202）が存在</t>
         </is>
       </c>
       <c r="K51" s="10" t="n"/>
@@ -15769,7 +15803,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">編集モードで購読者情報登録画面を開き、「履歴表示」ボタンを押下
+            <t xml:space="preserve">承認待ちの購読者を編集モードで開き、「承認しない」ボタンを押下
 </t>
           </r>
           <r>
@@ -15786,7 +15820,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevTools の Network タブで GET `/api/v1/dokusya/100/history` のレスポンスを確認
+            <t xml:space="preserve">否認確認ダイアログで「いいえ」を押下
 </t>
           </r>
           <r>
@@ -15803,7 +15837,31 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>履歴一覧の並び順と各行の項目（rireki_no・tetsuzuki_shurui_label・henko_riyu・saishin_data_flg）を確認</t>
+            <t xml:space="preserve">DBで以下クエリを実行し、ステータスを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT denshi_shonin_status FROM t_dokusya WHERE dokusya_id = 202;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>```</t>
           </r>
         </is>
       </c>
@@ -15829,7 +15887,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">購読者履歴情報画面（変更履歴一覧）が表示されること
+            <t xml:space="preserve">否認確認ダイアログが表示されること
 </t>
           </r>
           <r>
@@ -15846,7 +15904,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること（`data` 配列に履歴レコードが含まれること）
+            <t xml:space="preserve">否認処理が実行されないこと、現在の画面が維持されること
 </t>
           </r>
           <r>
@@ -15863,7 +15921,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">履歴一覧が rireki_no の降順で表示されること、各行に手続種類ラベル（tetsuzuki_shurui_label）・変更理由（henko_riyu）・最新データフラグ（saishin_data_flg）が表示されること
+            <t xml:space="preserve">t_dokusya の denshi_shonin_status が0（承認待ち）のまま変更されないこと
 </t>
           </r>
           <r>
@@ -15880,23 +15938,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・「履歴表示」ボタン押下で購読者履歴情報画面（ACSMS-SCR-013）へ遷移すること（機能定義 §5.1）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・履歴一覧は rireki_no 降順で取得すること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・tetsuzuki_shurui 値はラベル（m_code.code_category='TETSUZUKI_SHURUI'）にマッピングすること</t>
+            <t>・否認確認ダイアログで「いいえ」を押下する場合、何も行わず現在の画面を維持すること（機能定義 §4.4）</t>
           </r>
         </is>
       </c>
@@ -15942,12 +15984,7 @@
       <c r="BH51" s="45" t="inlineStr"/>
       <c r="BI51" s="10" t="n"/>
       <c r="BJ51" s="11" t="n"/>
-      <c r="BK51" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BK51" s="46" t="inlineStr"/>
       <c r="BL51" s="10" t="n"/>
       <c r="BM51" s="10" t="n"/>
       <c r="BN51" s="10" t="n"/>
@@ -15955,74 +15992,233 @@
       <c r="BP51" s="10" t="n"/>
       <c r="BQ51" s="11" t="n"/>
     </row>
-    <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="32" t="inlineStr">
-        <is>
-          <t>共通エラーハンドリング（Common Error Handling）</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="n"/>
+    <row r="52" ht="450" customHeight="1">
+      <c r="A52" s="44" t="n">
+        <v>36</v>
+      </c>
+      <c r="B52" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-035</t>
+        </is>
+      </c>
       <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="46" t="inlineStr">
+        <is>
+          <t>変更履歴一覧の取得・表示</t>
+        </is>
+      </c>
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
       <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
-      <c r="J52" s="10" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・購読者（dokusya_id=100）に2件以上の履歴（rireki_no=1, 2）が存在</t>
+        </is>
+      </c>
       <c r="K52" s="10" t="n"/>
       <c r="L52" s="10" t="n"/>
       <c r="M52" s="10" t="n"/>
       <c r="N52" s="10" t="n"/>
       <c r="O52" s="10" t="n"/>
-      <c r="P52" s="10" t="n"/>
-      <c r="Q52" s="10" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">編集モードで購読者情報登録画面を開き、「履歴表示」ボタンを押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DevTools の Network タブで GET `/api/v1/dokusya/100/history` のレスポンスを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>履歴一覧の並び順と各行の項目（rireki_no・tetsuzuki_shurui_label・henko_riyu・saishin_data_flg）を確認</t>
+          </r>
+        </is>
+      </c>
       <c r="R52" s="10" t="n"/>
       <c r="S52" s="10" t="n"/>
       <c r="T52" s="10" t="n"/>
       <c r="U52" s="10" t="n"/>
       <c r="V52" s="10" t="n"/>
-      <c r="W52" s="10" t="n"/>
-      <c r="X52" s="10" t="n"/>
+      <c r="W52" s="11" t="n"/>
+      <c r="X52" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読者履歴情報画面（変更履歴一覧）が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード200が返却されること（`data` 配列に履歴レコードが含まれること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">履歴一覧が rireki_no の降順で表示されること、各行に手続種類ラベル（tetsuzuki_shurui_label）・変更理由（henko_riyu）・最新データフラグ（saishin_data_flg）が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「履歴表示」ボタン押下で購読者履歴情報画面（ACSMS-SCR-013）へ遷移すること（機能定義 §5.1）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・履歴一覧は rireki_no 降順で取得すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・tetsuzuki_shurui 値はラベル（m_code.code_category='TETSUZUKI_SHURUI'）にマッピングすること</t>
+          </r>
+        </is>
+      </c>
       <c r="Y52" s="10" t="n"/>
       <c r="Z52" s="10" t="n"/>
       <c r="AA52" s="10" t="n"/>
       <c r="AB52" s="10" t="n"/>
       <c r="AC52" s="10" t="n"/>
-      <c r="AD52" s="10" t="n"/>
-      <c r="AE52" s="10" t="n"/>
-      <c r="AF52" s="10" t="n"/>
-      <c r="AG52" s="10" t="n"/>
+      <c r="AD52" s="11" t="n"/>
+      <c r="AE52" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF52" s="11" t="n"/>
+      <c r="AG52" s="45" t="inlineStr"/>
       <c r="AH52" s="10" t="n"/>
-      <c r="AI52" s="10" t="n"/>
-      <c r="AJ52" s="10" t="n"/>
+      <c r="AI52" s="11" t="n"/>
+      <c r="AJ52" s="45" t="inlineStr"/>
       <c r="AK52" s="10" t="n"/>
-      <c r="AL52" s="10" t="n"/>
-      <c r="AM52" s="10" t="n"/>
+      <c r="AL52" s="11" t="n"/>
+      <c r="AM52" s="45" t="inlineStr"/>
       <c r="AN52" s="10" t="n"/>
-      <c r="AO52" s="10" t="n"/>
-      <c r="AP52" s="10" t="n"/>
+      <c r="AO52" s="11" t="n"/>
+      <c r="AP52" s="45" t="inlineStr"/>
       <c r="AQ52" s="10" t="n"/>
-      <c r="AR52" s="10" t="n"/>
-      <c r="AS52" s="10" t="n"/>
+      <c r="AR52" s="11" t="n"/>
+      <c r="AS52" s="45" t="inlineStr"/>
       <c r="AT52" s="10" t="n"/>
-      <c r="AU52" s="10" t="n"/>
-      <c r="AV52" s="10" t="n"/>
+      <c r="AU52" s="11" t="n"/>
+      <c r="AV52" s="45" t="inlineStr"/>
       <c r="AW52" s="10" t="n"/>
-      <c r="AX52" s="10" t="n"/>
-      <c r="AY52" s="10" t="n"/>
+      <c r="AX52" s="11" t="n"/>
+      <c r="AY52" s="45" t="inlineStr"/>
       <c r="AZ52" s="10" t="n"/>
-      <c r="BA52" s="10" t="n"/>
-      <c r="BB52" s="10" t="n"/>
+      <c r="BA52" s="11" t="n"/>
+      <c r="BB52" s="45" t="inlineStr"/>
       <c r="BC52" s="10" t="n"/>
-      <c r="BD52" s="10" t="n"/>
-      <c r="BE52" s="10" t="n"/>
+      <c r="BD52" s="11" t="n"/>
+      <c r="BE52" s="45" t="inlineStr"/>
       <c r="BF52" s="10" t="n"/>
-      <c r="BG52" s="10" t="n"/>
-      <c r="BH52" s="10" t="n"/>
+      <c r="BG52" s="11" t="n"/>
+      <c r="BH52" s="45" t="inlineStr"/>
       <c r="BI52" s="10" t="n"/>
-      <c r="BJ52" s="10" t="n"/>
-      <c r="BK52" s="10" t="n"/>
+      <c r="BJ52" s="11" t="n"/>
+      <c r="BK52" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL52" s="10" t="n"/>
       <c r="BM52" s="10" t="n"/>
       <c r="BN52" s="10" t="n"/>
@@ -16030,179 +16226,74 @@
       <c r="BP52" s="10" t="n"/>
       <c r="BQ52" s="11" t="n"/>
     </row>
-    <row r="53" ht="304" customHeight="1">
-      <c r="A53" s="44" t="n">
-        <v>36</v>
-      </c>
-      <c r="B53" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-011-036</t>
-        </is>
-      </c>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t>共通エラーハンドリング（Common Error Handling）</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="n"/>
       <c r="C53" s="10" t="n"/>
-      <c r="D53" s="11" t="n"/>
-      <c r="E53" s="46" t="inlineStr">
-        <is>
-          <t>共通エラー — UNAUTHORIZED — セッション切れ時の処理</t>
-        </is>
-      </c>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
       <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="10" t="n"/>
-      <c r="I53" s="11" t="n"/>
-      <c r="J53" s="46" t="inlineStr">
-        <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・購読者情報登録画面を表示中
-・最終操作から24時間以上経過し、Redis セッション TTL 失効済</t>
-        </is>
-      </c>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="10" t="n"/>
       <c r="K53" s="10" t="n"/>
       <c r="L53" s="10" t="n"/>
       <c r="M53" s="10" t="n"/>
       <c r="N53" s="10" t="n"/>
       <c r="O53" s="10" t="n"/>
-      <c r="P53" s="11" t="n"/>
-      <c r="Q53" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">購読者情報登録画面で「承認・登録」ボタンを押下し、POST `/api/v1/dokusya` リクエストを送信
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>レスポンス内容と画面遷移を確認</t>
-          </r>
-        </is>
-      </c>
+      <c r="P53" s="10" t="n"/>
+      <c r="Q53" s="10" t="n"/>
       <c r="R53" s="10" t="n"/>
       <c r="S53" s="10" t="n"/>
       <c r="T53" s="10" t="n"/>
       <c r="U53" s="10" t="n"/>
       <c r="V53" s="10" t="n"/>
-      <c r="W53" s="11" t="n"/>
-      <c r="X53" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">HTTPステータスコード401が返却されること（`error_code: UNAUTHORIZED`、メッセージ `セッションが切れました。再度ログインしてください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">フロントエンド側で Pinia auth store の user 状態がクリアされ、`/login?redirect=...` へ自動遷移すること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・セッション失効時はバックエンド側の SessionAuthGuard が401を返却し、フロントエンド側 axios インターセプタで一律ログイン画面へ誘導すること</t>
-          </r>
-        </is>
-      </c>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="10" t="n"/>
       <c r="Y53" s="10" t="n"/>
       <c r="Z53" s="10" t="n"/>
       <c r="AA53" s="10" t="n"/>
       <c r="AB53" s="10" t="n"/>
       <c r="AC53" s="10" t="n"/>
-      <c r="AD53" s="11" t="n"/>
-      <c r="AE53" s="45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AF53" s="11" t="n"/>
-      <c r="AG53" s="45" t="inlineStr"/>
+      <c r="AD53" s="10" t="n"/>
+      <c r="AE53" s="10" t="n"/>
+      <c r="AF53" s="10" t="n"/>
+      <c r="AG53" s="10" t="n"/>
       <c r="AH53" s="10" t="n"/>
-      <c r="AI53" s="11" t="n"/>
-      <c r="AJ53" s="45" t="inlineStr"/>
+      <c r="AI53" s="10" t="n"/>
+      <c r="AJ53" s="10" t="n"/>
       <c r="AK53" s="10" t="n"/>
-      <c r="AL53" s="11" t="n"/>
-      <c r="AM53" s="45" t="inlineStr"/>
+      <c r="AL53" s="10" t="n"/>
+      <c r="AM53" s="10" t="n"/>
       <c r="AN53" s="10" t="n"/>
-      <c r="AO53" s="11" t="n"/>
-      <c r="AP53" s="45" t="inlineStr"/>
+      <c r="AO53" s="10" t="n"/>
+      <c r="AP53" s="10" t="n"/>
       <c r="AQ53" s="10" t="n"/>
-      <c r="AR53" s="11" t="n"/>
-      <c r="AS53" s="45" t="inlineStr"/>
+      <c r="AR53" s="10" t="n"/>
+      <c r="AS53" s="10" t="n"/>
       <c r="AT53" s="10" t="n"/>
-      <c r="AU53" s="11" t="n"/>
-      <c r="AV53" s="45" t="inlineStr"/>
+      <c r="AU53" s="10" t="n"/>
+      <c r="AV53" s="10" t="n"/>
       <c r="AW53" s="10" t="n"/>
-      <c r="AX53" s="11" t="n"/>
-      <c r="AY53" s="45" t="inlineStr"/>
+      <c r="AX53" s="10" t="n"/>
+      <c r="AY53" s="10" t="n"/>
       <c r="AZ53" s="10" t="n"/>
-      <c r="BA53" s="11" t="n"/>
-      <c r="BB53" s="45" t="inlineStr"/>
+      <c r="BA53" s="10" t="n"/>
+      <c r="BB53" s="10" t="n"/>
       <c r="BC53" s="10" t="n"/>
-      <c r="BD53" s="11" t="n"/>
-      <c r="BE53" s="45" t="inlineStr"/>
+      <c r="BD53" s="10" t="n"/>
+      <c r="BE53" s="10" t="n"/>
       <c r="BF53" s="10" t="n"/>
-      <c r="BG53" s="11" t="n"/>
-      <c r="BH53" s="45" t="inlineStr"/>
+      <c r="BG53" s="10" t="n"/>
+      <c r="BH53" s="10" t="n"/>
       <c r="BI53" s="10" t="n"/>
-      <c r="BJ53" s="11" t="n"/>
-      <c r="BK53" s="46" t="inlineStr"/>
+      <c r="BJ53" s="10" t="n"/>
+      <c r="BK53" s="10" t="n"/>
       <c r="BL53" s="10" t="n"/>
       <c r="BM53" s="10" t="n"/>
       <c r="BN53" s="10" t="n"/>
@@ -16210,20 +16301,20 @@
       <c r="BP53" s="10" t="n"/>
       <c r="BQ53" s="11" t="n"/>
     </row>
-    <row r="54" ht="256" customHeight="1">
+    <row r="54" ht="304" customHeight="1">
       <c r="A54" s="44" t="n">
         <v>37</v>
       </c>
       <c r="B54" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-037</t>
+          <t>ACSMS-TC-011-036</t>
         </is>
       </c>
       <c r="C54" s="10" t="n"/>
       <c r="D54" s="11" t="n"/>
       <c r="E54" s="46" t="inlineStr">
         <is>
-          <t>共通エラー — FORBIDDEN — 権限なしでの登録API直接呼び出し</t>
+          <t>共通エラー — UNAUTHORIZED — セッション切れ時の処理</t>
         </is>
       </c>
       <c r="F54" s="10" t="n"/>
@@ -16232,8 +16323,9 @@
       <c r="I54" s="11" t="n"/>
       <c r="J54" s="46" t="inlineStr">
         <is>
-          <t>・role: NICHINO_ADMIN
-・権限「dokusya.create」を持たない</t>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・購読者情報登録画面を表示中
+・最終操作から24時間以上経過し、Redis セッション TTL 失効済</t>
         </is>
       </c>
       <c r="K54" s="10" t="n"/>
@@ -16258,7 +16350,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevTools の Console から `fetch('/api/v1/dokusya', { method: 'POST', credentials: 'include', headers: { 'Content-Type': 'application/json' }, body: '{}' })` を実行
+            <t xml:space="preserve">購読者情報登録画面で「承認・登録」ボタンを押下し、POST `/api/v1/dokusya` リクエストを送信
 </t>
           </r>
           <r>
@@ -16275,7 +16367,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>レスポンスの HTTP ステータスと error_code を確認</t>
+            <t>レスポンス内容と画面遷移を確認</t>
           </r>
         </is>
       </c>
@@ -16301,7 +16393,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">リクエストがバックエンド側の権限チェックで拒否されること
+            <t xml:space="preserve">HTTPステータスコード401が返却されること（`error_code: UNAUTHORIZED`、メッセージ `セッションが切れました。再度ログインしてください。`）
 </t>
           </r>
           <r>
@@ -16318,7 +16410,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード403が返却されること（`error_code: FORBIDDEN`、メッセージ `この画面へのアクセス権限がありません。`）
+            <t xml:space="preserve">フロントエンド側で Pinia auth store の user 状態がクリアされ、`/login?redirect=...` へ自動遷移すること
 </t>
           </r>
           <r>
@@ -16335,7 +16427,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・`dokusya.create` 権限を持たないロールが登録APIを直接呼び出してもバックエンド側で403を返却すること</t>
+            <t>・セッション失効時はバックエンド側の SessionAuthGuard が401を返却し、フロントエンド側 axios インターセプタで一律ログイン画面へ誘導すること</t>
           </r>
         </is>
       </c>
@@ -16389,20 +16481,20 @@
       <c r="BP54" s="10" t="n"/>
       <c r="BQ54" s="11" t="n"/>
     </row>
-    <row r="55" ht="400" customHeight="1">
+    <row r="55" ht="256" customHeight="1">
       <c r="A55" s="44" t="n">
         <v>38</v>
       </c>
       <c r="B55" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-038</t>
+          <t>ACSMS-TC-011-037</t>
         </is>
       </c>
       <c r="C55" s="10" t="n"/>
       <c r="D55" s="11" t="n"/>
       <c r="E55" s="46" t="inlineStr">
         <is>
-          <t>共通エラー — DATA_SCOPE_VIOLATION — 他JAスコープでの登録試行</t>
+          <t>共通エラー — FORBIDDEN — 権限なしでの登録API直接呼び出し</t>
         </is>
       </c>
       <c r="F55" s="10" t="n"/>
@@ -16411,8 +16503,8 @@
       <c r="I55" s="11" t="n"/>
       <c r="J55" s="46" t="inlineStr">
         <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・他JA（ja_id=200）の管理支店ID・販売店IDを保持</t>
+          <t>・role: NICHINO_ADMIN
+・権限「dokusya.create」を持たない</t>
         </is>
       </c>
       <c r="K55" s="10" t="n"/>
@@ -16437,7 +16529,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevTools の Console から POST `/api/v1/dokusya` を実行し、リクエストボディに他JA（ja_id=200）配下の kanri_shiten_id・hanbaiten_id を指定して送信
+            <t xml:space="preserve">DevTools の Console から `fetch('/api/v1/dokusya', { method: 'POST', credentials: 'include', headers: { 'Content-Type': 'application/json' }, body: '{}' })` を実行
 </t>
           </r>
           <r>
@@ -16480,7 +16572,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">リクエストがバックエンド側の DataScope チェックで拒否されること
+            <t xml:space="preserve">リクエストがバックエンド側の権限チェックで拒否されること
 </t>
           </r>
           <r>
@@ -16497,7 +16589,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード403が返却されること（`error_code: DATA_SCOPE_VIOLATION`、メッセージ `このデータへのアクセス権限がありません。`）
+            <t xml:space="preserve">HTTPステータスコード403が返却されること（`error_code: FORBIDDEN`、メッセージ `この画面へのアクセス権限がありません。`）
 </t>
           </r>
           <r>
@@ -16514,23 +16606,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・登録時の ja_id はサーバ側で自動設定し、リクエストボディの ja_id は信頼しないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・他JA配下のFK参照（管理支店・販売店）を指定した登録は DATA_SCOPE_VIOLATION（403）で拒否されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・参照系（詳細・履歴取得）の DataScope 違反は404で存在隠蔽されるが、登録・更新系は403でアクセス拒否を明示すること</t>
+            <t>・`dokusya.create` 権限を持たないロールが登録APIを直接呼び出してもバックエンド側で403を返却すること</t>
           </r>
         </is>
       </c>
@@ -16584,20 +16660,20 @@
       <c r="BP55" s="10" t="n"/>
       <c r="BQ55" s="11" t="n"/>
     </row>
-    <row r="56" ht="352" customHeight="1">
+    <row r="56" ht="400" customHeight="1">
       <c r="A56" s="44" t="n">
         <v>39</v>
       </c>
       <c r="B56" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-039</t>
+          <t>ACSMS-TC-011-038</t>
         </is>
       </c>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="11" t="n"/>
       <c r="E56" s="46" t="inlineStr">
         <is>
-          <t>共通エラー — VALIDATION_ERROR — 不正値統合送信</t>
+          <t>共通エラー — DATA_SCOPE_VIOLATION — 他JAスコープでの登録試行</t>
         </is>
       </c>
       <c r="F56" s="10" t="n"/>
@@ -16607,7 +16683,7 @@
       <c r="J56" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・ブラウザ DevTools の Network タブを開いている</t>
+・他JA（ja_id=200）の管理支店ID・販売店IDを保持</t>
         </is>
       </c>
       <c r="K56" s="10" t="n"/>
@@ -16632,7 +16708,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevTools の Console から POST `/api/v1/dokusya` を実行し、shimei_sei を空・yubin_no を「123」（不正桁数）として送信
+            <t xml:space="preserve">DevTools の Console から POST `/api/v1/dokusya` を実行し、リクエストボディに他JA（ja_id=200）配下の kanri_shiten_id・hanbaiten_id を指定して送信
 </t>
           </r>
           <r>
@@ -16649,7 +16725,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>レスポンスの HTTP ステータス・error_code・errors 配列を確認</t>
+            <t>レスポンスの HTTP ステータスと error_code を確認</t>
           </r>
         </is>
       </c>
@@ -16675,7 +16751,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">リクエストがバックエンド側のバリデーションで拒否されること
+            <t xml:space="preserve">リクエストがバックエンド側の DataScope チェックで拒否されること
 </t>
           </r>
           <r>
@@ -16692,7 +16768,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、メッセージ `入力値が不正です。詳細はerrorsフィールドを確認してください。`、`errors` 配列に shimei_sei・yubin_no の項目別メッセージが含まれること）
+            <t xml:space="preserve">HTTPステータスコード403が返却されること（`error_code: DATA_SCOPE_VIOLATION`、メッセージ `このデータへのアクセス権限がありません。`）
 </t>
           </r>
           <r>
@@ -16709,15 +16785,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・バリデーションエラーは `errors` 配列（field + message）形式で返却されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・項目別メッセージはフロントエンド側で各項目下に表示されること</t>
+            <t xml:space="preserve">・登録時の ja_id はサーバ側で自動設定し、リクエストボディの ja_id は信頼しないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・他JA配下のFK参照（管理支店・販売店）を指定した登録は DATA_SCOPE_VIOLATION（403）で拒否されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・参照系（詳細・履歴取得）の DataScope 違反は404で存在隠蔽されるが、登録・更新系は403でアクセス拒否を明示すること</t>
           </r>
         </is>
       </c>
@@ -16771,20 +16855,20 @@
       <c r="BP56" s="10" t="n"/>
       <c r="BQ56" s="11" t="n"/>
     </row>
-    <row r="57" ht="384" customHeight="1">
+    <row r="57" ht="352" customHeight="1">
       <c r="A57" s="44" t="n">
         <v>40</v>
       </c>
       <c r="B57" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-040</t>
+          <t>ACSMS-TC-011-039</t>
         </is>
       </c>
       <c r="C57" s="10" t="n"/>
       <c r="D57" s="11" t="n"/>
       <c r="E57" s="46" t="inlineStr">
         <is>
-          <t>共通エラー — NOT_FOUND — 削除済／存在しない購読者の取得</t>
+          <t>共通エラー — VALIDATION_ERROR — 不正値統合送信</t>
         </is>
       </c>
       <c r="F57" s="10" t="n"/>
@@ -16794,7 +16878,7 @@
       <c r="J57" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・存在しない購読者ID（dokusya_id=999999）</t>
+・ブラウザ DevTools の Network タブを開いている</t>
         </is>
       </c>
       <c r="K57" s="10" t="n"/>
@@ -16819,7 +16903,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ブラウザのアドレスバーに `/dokusya/999999` を入力し、編集モードで直接アクセス
+            <t xml:space="preserve">DevTools の Console から POST `/api/v1/dokusya` を実行し、shimei_sei を空・yubin_no を「123」（不正桁数）として送信
 </t>
           </r>
           <r>
@@ -16836,24 +16920,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevTools の Network タブで GET `/api/v1/dokusya/999999` のレスポンスを確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>画面側のメッセージ表示を確認</t>
+            <t>レスポンスの HTTP ステータス・error_code・errors 配列を確認</t>
           </r>
         </is>
       </c>
@@ -16879,7 +16946,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">編集モードの購読者情報登録画面が開くこと
+            <t xml:space="preserve">リクエストがバックエンド側のバリデーションで拒否されること
 </t>
           </r>
           <r>
@@ -16896,24 +16963,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード404が返却されること（`error_code: NOT_FOUND`、メッセージ `指定された購読者が見つかりません。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">データ取得失敗のメッセージ ACSMS-MSG-011-016 `購読者ID #{id} が見つかりません。` が表示されること
+            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、メッセージ `入力値が不正です。詳細はerrorsフィールドを確認してください。`、`errors` 配列に shimei_sei・yubin_no の項目別メッセージが含まれること）
 </t>
           </r>
           <r>
@@ -16930,15 +16980,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・存在しない購読者IDの取得は404（NOT_FOUND）を返却すること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・データ取得失敗時はフロントエンド側で ACSMS-MSG-011-016 を表示すること</t>
+            <t xml:space="preserve">・バリデーションエラーは `errors` 配列（field + message）形式で返却されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・項目別メッセージはフロントエンド側で各項目下に表示されること</t>
           </r>
         </is>
       </c>
@@ -16992,20 +17042,20 @@
       <c r="BP57" s="10" t="n"/>
       <c r="BQ57" s="11" t="n"/>
     </row>
-    <row r="58" ht="400" customHeight="1">
+    <row r="58" ht="384" customHeight="1">
       <c r="A58" s="44" t="n">
         <v>41</v>
       </c>
       <c r="B58" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-041</t>
+          <t>ACSMS-TC-011-040</t>
         </is>
       </c>
       <c r="C58" s="10" t="n"/>
       <c r="D58" s="11" t="n"/>
       <c r="E58" s="46" t="inlineStr">
         <is>
-          <t>共通エラー — DUPLICATE_EMAIL — メールアドレス重複</t>
+          <t>共通エラー — NOT_FOUND — 削除済／存在しない購読者の取得</t>
         </is>
       </c>
       <c r="F58" s="10" t="n"/>
@@ -17015,7 +17065,7 @@
       <c r="J58" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・自JA内に email=`existing@example.com` の購読者が既に存在</t>
+・存在しない購読者ID（dokusya_id=999999）</t>
         </is>
       </c>
       <c r="K58" s="10" t="n"/>
@@ -17040,7 +17090,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">新規作成モードで購読種別=電子版を選択し、メールアドレス（email）に `existing@example.com` を入力して全必須項目を入力後「承認・登録」ボタンを押下
+            <t xml:space="preserve">ブラウザのアドレスバーに `/dokusya/999999` を入力し、編集モードで直接アクセス
 </t>
           </r>
           <r>
@@ -17057,7 +17107,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">レスポンスの HTTP ステータスと error_code を確認
+            <t xml:space="preserve">DevTools の Network タブで GET `/api/v1/dokusya/999999` のレスポンスを確認
 </t>
           </r>
           <r>
@@ -17100,7 +17150,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">登録処理が拒否されること
+            <t xml:space="preserve">編集モードの購読者情報登録画面が開くこと
 </t>
           </r>
           <r>
@@ -17117,7 +17167,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: DUPLICATE_EMAIL`、メッセージ `このメールアドレスは既に登録されています。`）
+            <t xml:space="preserve">HTTPステータスコード404が返却されること（`error_code: NOT_FOUND`、メッセージ `指定された購読者が見つかりません。`）
 </t>
           </r>
           <r>
@@ -17134,7 +17184,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">メッセージ `このメールアドレスは既に登録されています。`（ACSMS-MSG-011-009）が表示されること、重複データが登録されないこと
+            <t xml:space="preserve">データ取得失敗のメッセージ ACSMS-MSG-011-016 `購読者ID #{id} が見つかりません。` が表示されること
 </t>
           </r>
           <r>
@@ -17151,15 +17201,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・メールアドレスが入力されている場合、自JA内（`ja_id = :ja_id`、空文字除く）で重複チェックを行うこと（機能定義 §2.5）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・重複の場合は DUPLICATE_EMAIL（400）を返却すること</t>
+            <t xml:space="preserve">・存在しない購読者IDの取得は404（NOT_FOUND）を返却すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・データ取得失敗時はフロントエンド側で ACSMS-MSG-011-016 を表示すること</t>
           </r>
         </is>
       </c>
@@ -17213,20 +17263,20 @@
       <c r="BP58" s="10" t="n"/>
       <c r="BQ58" s="11" t="n"/>
     </row>
-    <row r="59" ht="368" customHeight="1">
+    <row r="59" ht="400" customHeight="1">
       <c r="A59" s="44" t="n">
         <v>42</v>
       </c>
       <c r="B59" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-042</t>
+          <t>ACSMS-TC-011-041</t>
         </is>
       </c>
       <c r="C59" s="10" t="n"/>
       <c r="D59" s="11" t="n"/>
       <c r="E59" s="46" t="inlineStr">
         <is>
-          <t>共通エラー — INVALID_STATUS — 承認待ち以外の読者への承認試行</t>
+          <t>共通エラー — DUPLICATE_EMAIL — メールアドレス重複</t>
         </is>
       </c>
       <c r="F59" s="10" t="n"/>
@@ -17235,8 +17285,8 @@
       <c r="I59" s="11" t="n"/>
       <c r="J59" s="46" t="inlineStr">
         <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属、電子版取扱フラグあり）
-・denshi_shonin_status=1（承認済み）の購読者（dokusya_id=210）が存在</t>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・自JA内に email=`existing@example.com` の購読者が既に存在</t>
         </is>
       </c>
       <c r="K59" s="10" t="n"/>
@@ -17261,7 +17311,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevTools の Console から PUT `/api/v1/dokusya/210/approve` を実行
+            <t xml:space="preserve">新規作成モードで購読種別=電子版を選択し、メールアドレス（email）に `existing@example.com` を入力して全必須項目を入力後「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -17295,7 +17345,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DevTools の Console から PUT `/api/v1/dokusya/210/reject` を実行し、レスポンスを確認</t>
+            <t>画面側のメッセージ表示を確認</t>
           </r>
         </is>
       </c>
@@ -17321,7 +17371,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">承認処理が拒否されること
+            <t xml:space="preserve">登録処理が拒否されること
 </t>
           </r>
           <r>
@@ -17338,7 +17388,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: INVALID_STATUS`、メッセージ `承認待ちの読者ではありません。`）
+            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: DUPLICATE_EMAIL`、メッセージ `このメールアドレスは既に登録されています。`）
 </t>
           </r>
           <r>
@@ -17355,7 +17405,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: INVALID_STATUS`、メッセージ `承認待ちの読者ではありません。`）
+            <t xml:space="preserve">メッセージ `このメールアドレスは既に登録されています。`（ACSMS-MSG-011-009）が表示されること、重複データが登録されないこと
 </t>
           </r>
           <r>
@@ -17372,7 +17422,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・denshi_shonin_status が0でない場合、承認・否認API は INVALID_STATUS（400）を返却すること（機能定義 §3.1, §4.1）</t>
+            <t xml:space="preserve">・メールアドレスが入力されている場合、自JA内（`ja_id = :ja_id`、空文字除く）で重複チェックを行うこと（機能定義 §2.5）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・重複の場合は DUPLICATE_EMAIL（400）を返却すること</t>
           </r>
         </is>
       </c>
@@ -17426,20 +17484,20 @@
       <c r="BP59" s="10" t="n"/>
       <c r="BQ59" s="11" t="n"/>
     </row>
-    <row r="60" ht="272" customHeight="1">
+    <row r="60" ht="368" customHeight="1">
       <c r="A60" s="44" t="n">
         <v>43</v>
       </c>
       <c r="B60" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-043</t>
+          <t>ACSMS-TC-011-042</t>
         </is>
       </c>
       <c r="C60" s="10" t="n"/>
       <c r="D60" s="11" t="n"/>
       <c r="E60" s="46" t="inlineStr">
         <is>
-          <t>共通エラー — BAD_REQUEST — 不正リクエストパラメータ</t>
+          <t>共通エラー — INVALID_STATUS — 承認待ち以外の読者への承認試行</t>
         </is>
       </c>
       <c r="F60" s="10" t="n"/>
@@ -17448,8 +17506,8 @@
       <c r="I60" s="11" t="n"/>
       <c r="J60" s="46" t="inlineStr">
         <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・ブラウザ DevTools の Network タブを開いている</t>
+          <t>・role: JA_HONTEN（ja_id=100 所属、電子版取扱フラグあり）
+・denshi_shonin_status=1（承認済み）の購読者（dokusya_id=210）が存在</t>
         </is>
       </c>
       <c r="K60" s="10" t="n"/>
@@ -17474,7 +17532,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevTools の Console から `fetch('/api/v1/dokusya/abc', { credentials: 'include' })` を実行（dokusya_id に数値以外を指定）
+            <t xml:space="preserve">DevTools の Console から PUT `/api/v1/dokusya/210/approve` を実行
 </t>
           </r>
           <r>
@@ -17491,7 +17549,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>レスポンスの HTTP ステータスと error_code を確認</t>
+            <t xml:space="preserve">レスポンスの HTTP ステータスと error_code を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DevTools の Console から PUT `/api/v1/dokusya/210/reject` を実行し、レスポンスを確認</t>
           </r>
         </is>
       </c>
@@ -17517,7 +17592,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">リクエストがバックエンド側のバリデーションで拒否されること
+            <t xml:space="preserve">承認処理が拒否されること
 </t>
           </r>
           <r>
@@ -17534,7 +17609,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: BAD_REQUEST`、メッセージ `リクエストパラメータが不正です。`）
+            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: INVALID_STATUS`、メッセージ `承認待ちの読者ではありません。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: INVALID_STATUS`、メッセージ `承認待ちの読者ではありません。`）
 </t>
           </r>
           <r>
@@ -17551,7 +17643,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・dokusya_id パスパラメータは数値型の検証が行われ、不正値の場合 BAD_REQUEST にマップされること</t>
+            <t>・denshi_shonin_status が0でない場合、承認・否認API は INVALID_STATUS（400）を返却すること（機能定義 §3.1, §4.1）</t>
           </r>
         </is>
       </c>
@@ -17605,20 +17697,20 @@
       <c r="BP60" s="10" t="n"/>
       <c r="BQ60" s="11" t="n"/>
     </row>
-    <row r="61" ht="416" customHeight="1">
+    <row r="61" ht="272" customHeight="1">
       <c r="A61" s="44" t="n">
         <v>44</v>
       </c>
       <c r="B61" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-044</t>
+          <t>ACSMS-TC-011-043</t>
         </is>
       </c>
       <c r="C61" s="10" t="n"/>
       <c r="D61" s="11" t="n"/>
       <c r="E61" s="46" t="inlineStr">
         <is>
-          <t>共通エラー — TOO_MANY_REQUESTS — レート制限超過</t>
+          <t>共通エラー — BAD_REQUEST — 不正リクエストパラメータ</t>
         </is>
       </c>
       <c r="F61" s="10" t="n"/>
@@ -17628,7 +17720,7 @@
       <c r="J61" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・テスト用スクリプトで `/api/v1/dokusya/1` GET を1分間に上限超で送信</t>
+・ブラウザ DevTools の Network タブを開いている</t>
         </is>
       </c>
       <c r="K61" s="10" t="n"/>
@@ -17653,7 +17745,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">スクリプトを起動、購読者取得APIへ高頻度リクエスト送信
+            <t xml:space="preserve">DevTools の Console から `fetch('/api/v1/dokusya/abc', { credentials: 'include' })` を実行（dokusya_id に数値以外を指定）
 </t>
           </r>
           <r>
@@ -17670,24 +17762,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">レスポンスの HTTP ステータスと error_code を確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>画面側のトースト表示を確認</t>
+            <t>レスポンスの HTTP ステータスと error_code を確認</t>
           </r>
         </is>
       </c>
@@ -17713,7 +17788,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">上限件数までは正常応答、それ以降は429を返却すること
+            <t xml:space="preserve">リクエストがバックエンド側のバリデーションで拒否されること
 </t>
           </r>
           <r>
@@ -17730,24 +17805,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード429が返却されること（`error_code: TOO_MANY_REQUESTS`、メッセージ `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">トースト `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。` が表示されること
+            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: BAD_REQUEST`、メッセージ `リクエストパラメータが不正です。`）
 </t>
           </r>
           <r>
@@ -17764,15 +17822,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・NestJS @Throttle デコレータ + AWS WAF レート制限がインフラ／アプリ両層でブロックすること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・観点 VP-A-08「レート制限・Throttling」準拠（testcase-viewpoints.md v1.1）</t>
+            <t>・dokusya_id パスパラメータは数値型の検証が行われ、不正値の場合 BAD_REQUEST にマップされること</t>
           </r>
         </is>
       </c>
@@ -17826,20 +17876,20 @@
       <c r="BP61" s="10" t="n"/>
       <c r="BQ61" s="11" t="n"/>
     </row>
-    <row r="62" ht="450" customHeight="1">
+    <row r="62" ht="416" customHeight="1">
       <c r="A62" s="44" t="n">
         <v>45</v>
       </c>
       <c r="B62" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-045</t>
+          <t>ACSMS-TC-011-044</t>
         </is>
       </c>
       <c r="C62" s="10" t="n"/>
       <c r="D62" s="11" t="n"/>
       <c r="E62" s="46" t="inlineStr">
         <is>
-          <t>共通エラー — INTERNAL_SERVER_ERROR — サーバーエラー</t>
+          <t>共通エラー — TOO_MANY_REQUESTS — レート制限超過</t>
         </is>
       </c>
       <c r="F62" s="10" t="n"/>
@@ -17849,7 +17899,7 @@
       <c r="J62" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・DB接続エラー等のサーバー障害を模擬できる状態</t>
+・テスト用スクリプトで `/api/v1/dokusya/1` GET を1分間に上限超で送信</t>
         </is>
       </c>
       <c r="K62" s="10" t="n"/>
@@ -17874,7 +17924,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">サーバー障害（DB接続エラー等）を模擬した状態で「承認・登録」ボタンを押下
+            <t xml:space="preserve">スクリプトを起動、購読者取得APIへ高頻度リクエスト送信
 </t>
           </r>
           <r>
@@ -17891,7 +17941,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">POST `/api/v1/dokusya` のレスポンスの HTTP ステータスと error_code を確認
+            <t xml:space="preserve">レスポンスの HTTP ステータスと error_code を確認
 </t>
           </r>
           <r>
@@ -17908,7 +17958,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>画面側のメッセージ表示と、エラーログの記録を確認</t>
+            <t>画面側のトースト表示を確認</t>
           </r>
         </is>
       </c>
@@ -17934,7 +17984,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">登録処理が失敗すること
+            <t xml:space="preserve">上限件数までは正常応答、それ以降は429を返却すること
 </t>
           </r>
           <r>
@@ -17951,7 +18001,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード500が返却されること（`error_code: INTERNAL_SERVER_ERROR`、メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`）
+            <t xml:space="preserve">HTTPステータスコード429が返却されること（`error_code: TOO_MANY_REQUESTS`、メッセージ `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`）
 </t>
           </r>
           <r>
@@ -17968,7 +18018,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`（ACSMS-MSG-011-012）が表示されること、t_log にエラーログ（log_type=3, result_status=2）が記録されること、スタックトレースが利用者へ表示されないこと
+            <t xml:space="preserve">トースト `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。` が表示されること
 </t>
           </r>
           <r>
@@ -17985,15 +18035,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・DB接続エラー等のサーバー障害は INTERNAL_SERVER_ERROR にマップされること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・エラー発生時はエラーログ（log_type=3）をトランザクション外で記録すること（業務書き込みはロールバックされること）</t>
+            <t xml:space="preserve">・NestJS @Throttle デコレータ + AWS WAF レート制限がインフラ／アプリ両層でブロックすること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・観点 VP-A-08「レート制限・Throttling」準拠（testcase-viewpoints.md v1.1）</t>
           </r>
         </is>
       </c>
@@ -18047,20 +18097,20 @@
       <c r="BP62" s="10" t="n"/>
       <c r="BQ62" s="11" t="n"/>
     </row>
-    <row r="63" ht="352" customHeight="1">
+    <row r="63" ht="450" customHeight="1">
       <c r="A63" s="44" t="n">
         <v>46</v>
       </c>
       <c r="B63" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-046</t>
+          <t>ACSMS-TC-011-045</t>
         </is>
       </c>
       <c r="C63" s="10" t="n"/>
       <c r="D63" s="11" t="n"/>
       <c r="E63" s="46" t="inlineStr">
         <is>
-          <t>共通エラー — ネットワーク切断時の処理</t>
+          <t>共通エラー — INTERNAL_SERVER_ERROR — サーバーエラー</t>
         </is>
       </c>
       <c r="F63" s="10" t="n"/>
@@ -18070,7 +18120,7 @@
       <c r="J63" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・ブラウザ DevTools の Network タブを開いている</t>
+・DB接続エラー等のサーバー障害を模擬できる状態</t>
         </is>
       </c>
       <c r="K63" s="10" t="n"/>
@@ -18095,7 +18145,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevTools の Network タブでネットワーク切断（offline）を設定
+            <t xml:space="preserve">サーバー障害（DB接続エラー等）を模擬した状態で「承認・登録」ボタンを押下
 </t>
           </r>
           <r>
@@ -18112,7 +18162,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「承認・登録」ボタンを押下し、POST `/api/v1/dokusya` を送信
+            <t xml:space="preserve">POST `/api/v1/dokusya` のレスポンスの HTTP ステータスと error_code を確認
 </t>
           </r>
           <r>
@@ -18129,7 +18179,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>画面側のトースト表示を確認</t>
+            <t>画面側のメッセージ表示と、エラーログの記録を確認</t>
           </r>
         </is>
       </c>
@@ -18155,7 +18205,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ネットワーク切断状態となること
+            <t xml:space="preserve">登録処理が失敗すること
 </t>
           </r>
           <r>
@@ -18172,7 +18222,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">APIリクエストがネットワークエラーとなること
+            <t xml:space="preserve">HTTPステータスコード500が返却されること（`error_code: INTERNAL_SERVER_ERROR`、メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`）
 </t>
           </r>
           <r>
@@ -18189,7 +18239,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">トースト `ネットワークエラーが発生しました。しばらくしてから再度お試しください。` が表示されること、入力内容が保存されること
+            <t xml:space="preserve">メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`（ACSMS-MSG-011-012）が表示されること、t_log にエラーログ（log_type=3, result_status=2）が記録されること、スタックトレースが利用者へ表示されないこと
 </t>
           </r>
           <r>
@@ -18206,15 +18256,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・ネットワーク切断時はフロントエンド側 axios インターセプタでネットワークエラーのトーストを表示すること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・想定外エラーが発生しないこと、入力内容が消えないこと</t>
+            <t xml:space="preserve">・DB接続エラー等のサーバー障害は INTERNAL_SERVER_ERROR にマップされること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・エラー発生時はエラーログ（log_type=3）をトランザクション外で記録すること（業務書き込みはロールバックされること）</t>
           </r>
         </is>
       </c>
@@ -18260,12 +18310,7 @@
       <c r="BH63" s="45" t="inlineStr"/>
       <c r="BI63" s="10" t="n"/>
       <c r="BJ63" s="11" t="n"/>
-      <c r="BK63" s="46" t="inlineStr">
-        <is>
-          <t>ネットワークエラーのトースト文言はフロントエンド側 axios インターセプタの実装に準拠。
----</t>
-        </is>
-      </c>
+      <c r="BK63" s="46" t="inlineStr"/>
       <c r="BL63" s="10" t="n"/>
       <c r="BM63" s="10" t="n"/>
       <c r="BN63" s="10" t="n"/>
@@ -18273,8 +18318,234 @@
       <c r="BP63" s="10" t="n"/>
       <c r="BQ63" s="11" t="n"/>
     </row>
+    <row r="64" ht="352" customHeight="1">
+      <c r="A64" s="44" t="n">
+        <v>47</v>
+      </c>
+      <c r="B64" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-046</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="46" t="inlineStr">
+        <is>
+          <t>共通エラー — ネットワーク切断時の処理</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・ブラウザ DevTools の Network タブを開いている</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="11" t="n"/>
+      <c r="Q64" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DevTools の Network タブでネットワーク切断（offline）を設定
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「承認・登録」ボタンを押下し、POST `/api/v1/dokusya` を送信
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>画面側のトースト表示を確認</t>
+          </r>
+        </is>
+      </c>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="11" t="n"/>
+      <c r="X64" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ネットワーク切断状態となること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">APIリクエストがネットワークエラーとなること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">トースト `ネットワークエラーが発生しました。しばらくしてから再度お試しください。` が表示されること、入力内容が保存されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ネットワーク切断時はフロントエンド側 axios インターセプタでネットワークエラーのトーストを表示すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・想定外エラーが発生しないこと、入力内容が消えないこと</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="11" t="n"/>
+      <c r="AE64" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF64" s="11" t="n"/>
+      <c r="AG64" s="45" t="inlineStr"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="11" t="n"/>
+      <c r="AJ64" s="45" t="inlineStr"/>
+      <c r="AK64" s="10" t="n"/>
+      <c r="AL64" s="11" t="n"/>
+      <c r="AM64" s="45" t="inlineStr"/>
+      <c r="AN64" s="10" t="n"/>
+      <c r="AO64" s="11" t="n"/>
+      <c r="AP64" s="45" t="inlineStr"/>
+      <c r="AQ64" s="10" t="n"/>
+      <c r="AR64" s="11" t="n"/>
+      <c r="AS64" s="45" t="inlineStr"/>
+      <c r="AT64" s="10" t="n"/>
+      <c r="AU64" s="11" t="n"/>
+      <c r="AV64" s="45" t="inlineStr"/>
+      <c r="AW64" s="10" t="n"/>
+      <c r="AX64" s="11" t="n"/>
+      <c r="AY64" s="45" t="inlineStr"/>
+      <c r="AZ64" s="10" t="n"/>
+      <c r="BA64" s="11" t="n"/>
+      <c r="BB64" s="45" t="inlineStr"/>
+      <c r="BC64" s="10" t="n"/>
+      <c r="BD64" s="11" t="n"/>
+      <c r="BE64" s="45" t="inlineStr"/>
+      <c r="BF64" s="10" t="n"/>
+      <c r="BG64" s="11" t="n"/>
+      <c r="BH64" s="45" t="inlineStr"/>
+      <c r="BI64" s="10" t="n"/>
+      <c r="BJ64" s="11" t="n"/>
+      <c r="BK64" s="46" t="inlineStr">
+        <is>
+          <t>ネットワークエラーのトースト文言はフロントエンド側 axios インターセプタの実装に準拠。
+---</t>
+        </is>
+      </c>
+      <c r="BL64" s="10" t="n"/>
+      <c r="BM64" s="10" t="n"/>
+      <c r="BN64" s="10" t="n"/>
+      <c r="BO64" s="10" t="n"/>
+      <c r="BP64" s="10" t="n"/>
+      <c r="BQ64" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="854">
+  <mergeCells count="871">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -18285,21 +18556,25 @@
     <mergeCell ref="BH33:BJ33"/>
     <mergeCell ref="BK50:BQ50"/>
     <mergeCell ref="AE41:AF41"/>
+    <mergeCell ref="E52:I52"/>
     <mergeCell ref="AV57:AX57"/>
-    <mergeCell ref="B53:D53"/>
     <mergeCell ref="AP60:AR60"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
     <mergeCell ref="AS61:AU61"/>
     <mergeCell ref="W7:Y7"/>
+    <mergeCell ref="AM64:AO64"/>
     <mergeCell ref="AS48:AU48"/>
     <mergeCell ref="J62:P62"/>
     <mergeCell ref="BK16:BQ16"/>
     <mergeCell ref="AE56:AF56"/>
+    <mergeCell ref="AE43:AF43"/>
     <mergeCell ref="AM30:AO30"/>
     <mergeCell ref="AP45:AR45"/>
+    <mergeCell ref="J64:P64"/>
     <mergeCell ref="BE13:BG13"/>
     <mergeCell ref="W8:Y8"/>
+    <mergeCell ref="Q37:W37"/>
     <mergeCell ref="AJ20:AL20"/>
     <mergeCell ref="AM21:AO21"/>
     <mergeCell ref="AG24:AI24"/>
@@ -18312,7 +18587,6 @@
     <mergeCell ref="AG26:AI26"/>
     <mergeCell ref="AP13:AR13"/>
     <mergeCell ref="BK42:BQ42"/>
-    <mergeCell ref="Q38:W38"/>
     <mergeCell ref="AE34:AF34"/>
     <mergeCell ref="AJ51:AL51"/>
     <mergeCell ref="BK47:BQ47"/>
@@ -18326,11 +18600,11 @@
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="BH21:BJ21"/>
     <mergeCell ref="AM34:AO34"/>
-    <mergeCell ref="AJ38:AL38"/>
     <mergeCell ref="BE35:BG35"/>
     <mergeCell ref="BK48:BQ48"/>
     <mergeCell ref="AM49:AO49"/>
     <mergeCell ref="AE50:AF50"/>
+    <mergeCell ref="AG52:AI52"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="BB26:BD26"/>
@@ -18340,6 +18614,7 @@
     <mergeCell ref="AY29:BA29"/>
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="AJ33:AL33"/>
+    <mergeCell ref="AG37:AI37"/>
     <mergeCell ref="J39:P39"/>
     <mergeCell ref="X21:AD21"/>
     <mergeCell ref="AE62:AF62"/>
@@ -18347,26 +18622,27 @@
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="AJ35:AL35"/>
+    <mergeCell ref="BK37:BQ37"/>
     <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
-    <mergeCell ref="BE38:BG38"/>
+    <mergeCell ref="AE64:AF64"/>
     <mergeCell ref="AS62:AU62"/>
     <mergeCell ref="AV63:AX63"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
-    <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="X16:AD16"/>
     <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="AE57:AF57"/>
-    <mergeCell ref="BK53:BQ53"/>
     <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
+    <mergeCell ref="AS64:AU64"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
     <mergeCell ref="BE33:BG33"/>
+    <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="B21:D21"/>
@@ -18380,7 +18656,6 @@
     <mergeCell ref="AM24:AO24"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="AM60:AO60"/>
-    <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
     <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
@@ -18394,10 +18669,9 @@
     <mergeCell ref="BH29:BJ29"/>
     <mergeCell ref="Q41:W41"/>
     <mergeCell ref="E35:I35"/>
-    <mergeCell ref="AY44:BA44"/>
-    <mergeCell ref="AV53:AX53"/>
-    <mergeCell ref="BH44:BJ44"/>
     <mergeCell ref="Q56:W56"/>
+    <mergeCell ref="AE52:AF52"/>
+    <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
     <mergeCell ref="AE39:AF39"/>
     <mergeCell ref="B51:D51"/>
@@ -18412,15 +18686,13 @@
     <mergeCell ref="AJ41:AL41"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="BK10:BQ11"/>
-    <mergeCell ref="J53:P53"/>
     <mergeCell ref="AS14:AU14"/>
-    <mergeCell ref="AE53:AF53"/>
     <mergeCell ref="AG55:AI55"/>
     <mergeCell ref="AP18:AR18"/>
     <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="BH26:BJ26"/>
-    <mergeCell ref="AG38:AI38"/>
     <mergeCell ref="BE30:BG30"/>
+    <mergeCell ref="AJ43:AL43"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="J55:P55"/>
@@ -18432,6 +18704,8 @@
     <mergeCell ref="Q34:W34"/>
     <mergeCell ref="AG40:AI40"/>
     <mergeCell ref="X24:AD24"/>
+    <mergeCell ref="BB43:BD43"/>
+    <mergeCell ref="A44:BQ44"/>
     <mergeCell ref="AY47:BA47"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="BH50:BJ50"/>
@@ -18442,10 +18716,10 @@
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
-    <mergeCell ref="AP44:AR44"/>
     <mergeCell ref="E23:I23"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="BE56:BG56"/>
+    <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
     <mergeCell ref="BB59:BD59"/>
@@ -18460,6 +18734,7 @@
     <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="BB48:BD48"/>
+    <mergeCell ref="AG43:AI43"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E49:I49"/>
@@ -18467,9 +18742,12 @@
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
     <mergeCell ref="E36:I36"/>
+    <mergeCell ref="Q64:W64"/>
     <mergeCell ref="Q51:W51"/>
+    <mergeCell ref="X37:AD37"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
+    <mergeCell ref="A53:BQ53"/>
     <mergeCell ref="AP24:AR24"/>
     <mergeCell ref="BH32:BJ32"/>
     <mergeCell ref="BK18:BQ18"/>
@@ -18483,11 +18761,9 @@
     <mergeCell ref="AY42:BA42"/>
     <mergeCell ref="AE55:AF55"/>
     <mergeCell ref="AG21:AI21"/>
-    <mergeCell ref="X38:AD38"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="BH46:BJ46"/>
     <mergeCell ref="BE50:BG50"/>
-    <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AJ57:AL57"/>
     <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="BE31:BG31"/>
@@ -18495,46 +18771,45 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AG48:AI48"/>
     <mergeCell ref="Q17:W17"/>
-    <mergeCell ref="B44:D44"/>
     <mergeCell ref="BB34:BD34"/>
     <mergeCell ref="E29:I29"/>
     <mergeCell ref="J23:P23"/>
     <mergeCell ref="AV34:AX34"/>
+    <mergeCell ref="B37:D37"/>
     <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="AV28:AX28"/>
-    <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="BB49:BD49"/>
     <mergeCell ref="AG62:AI62"/>
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
-    <mergeCell ref="A37:BQ37"/>
     <mergeCell ref="X40:AD40"/>
     <mergeCell ref="E31:I31"/>
     <mergeCell ref="AV36:AX36"/>
     <mergeCell ref="T6:V6"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="AV30:AX30"/>
+    <mergeCell ref="Q52:W52"/>
     <mergeCell ref="Q39:W39"/>
     <mergeCell ref="AS33:AU33"/>
     <mergeCell ref="AM36:AO36"/>
     <mergeCell ref="F1:Q1"/>
+    <mergeCell ref="AP37:AR37"/>
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="E26:I26"/>
+    <mergeCell ref="AY37:BA37"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
     <mergeCell ref="J36:P36"/>
-    <mergeCell ref="A43:BQ43"/>
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
     <mergeCell ref="AV21:AX21"/>
-    <mergeCell ref="AY53:BA53"/>
     <mergeCell ref="BK24:BQ24"/>
     <mergeCell ref="X45:AD45"/>
     <mergeCell ref="E50:I50"/>
     <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="BH53:BJ53"/>
+    <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="AV29:AX29"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="AV23:AX23"/>
@@ -18544,7 +18819,6 @@
     <mergeCell ref="AY55:BA55"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
-    <mergeCell ref="E44:I44"/>
     <mergeCell ref="X46:AD46"/>
     <mergeCell ref="AE21:AF21"/>
     <mergeCell ref="BH48:BJ48"/>
@@ -18564,9 +18838,9 @@
     <mergeCell ref="BB11:BD11"/>
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
-    <mergeCell ref="BE53:BG53"/>
     <mergeCell ref="AJ60:AL60"/>
     <mergeCell ref="AM32:AO32"/>
+    <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
     <mergeCell ref="J24:P24"/>
@@ -18578,10 +18852,11 @@
     <mergeCell ref="E57:I57"/>
     <mergeCell ref="AV50:AX50"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="Q60:W60"/>
+    <mergeCell ref="A38:BQ38"/>
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q60:W60"/>
     <mergeCell ref="AS41:AU41"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
@@ -18590,16 +18865,17 @@
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
     <mergeCell ref="B48:D48"/>
+    <mergeCell ref="AV52:AX52"/>
     <mergeCell ref="AP55:AR55"/>
     <mergeCell ref="AS56:AU56"/>
-    <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
+    <mergeCell ref="AS43:AU43"/>
     <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
-    <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
     <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AM52:AO52"/>
     <mergeCell ref="BH61:BJ61"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
@@ -18611,9 +18887,11 @@
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="X36:AD36"/>
-    <mergeCell ref="J44:P44"/>
+    <mergeCell ref="J52:P52"/>
     <mergeCell ref="Q25:W25"/>
+    <mergeCell ref="AV37:AX37"/>
     <mergeCell ref="E60:I60"/>
+    <mergeCell ref="J37:P37"/>
     <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
     <mergeCell ref="X61:AD61"/>
@@ -18629,18 +18907,18 @@
     <mergeCell ref="AS29:AU29"/>
     <mergeCell ref="AM42:AO42"/>
     <mergeCell ref="X62:AD62"/>
+    <mergeCell ref="AE37:AF37"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="AM29:AO29"/>
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
-    <mergeCell ref="AS44:AU44"/>
     <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="X64:AD64"/>
     <mergeCell ref="BH18:BJ18"/>
     <mergeCell ref="J32:P32"/>
     <mergeCell ref="J63:P63"/>
     <mergeCell ref="AE26:AF26"/>
-    <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="BB58:BD58"/>
     <mergeCell ref="B61:D61"/>
@@ -18667,8 +18945,8 @@
     <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
     <mergeCell ref="AP48:AR48"/>
+    <mergeCell ref="B64:D64"/>
     <mergeCell ref="A27:BQ27"/>
-    <mergeCell ref="AE44:AF44"/>
     <mergeCell ref="X57:AD57"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
@@ -18680,7 +18958,7 @@
     <mergeCell ref="AP56:AR56"/>
     <mergeCell ref="AG20:AI20"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="AM53:AO53"/>
+    <mergeCell ref="AP43:AR43"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="J45:P45"/>
@@ -18689,10 +18967,9 @@
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="AJ23:AL23"/>
-    <mergeCell ref="E53:I53"/>
     <mergeCell ref="AM48:AO48"/>
     <mergeCell ref="Q49:W49"/>
-    <mergeCell ref="AM44:AO44"/>
+    <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="E55:I55"/>
@@ -18727,7 +19004,6 @@
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
     <mergeCell ref="BK61:BQ61"/>
-    <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
     <mergeCell ref="BE18:BG18"/>
     <mergeCell ref="AJ31:AL31"/>
@@ -18750,15 +19026,18 @@
     <mergeCell ref="BK56:BQ56"/>
     <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="BE36:BG36"/>
+    <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="X58:AD58"/>
     <mergeCell ref="AS60:AU60"/>
     <mergeCell ref="AV61:AX61"/>
+    <mergeCell ref="AP64:AR64"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
     <mergeCell ref="AG59:AI59"/>
+    <mergeCell ref="BK64:BQ64"/>
     <mergeCell ref="BK51:BQ51"/>
     <mergeCell ref="X60:AD60"/>
     <mergeCell ref="AM61:AO61"/>
@@ -18786,26 +19065,27 @@
     <mergeCell ref="Q42:W42"/>
     <mergeCell ref="A12:BQ12"/>
     <mergeCell ref="AY15:BA15"/>
-    <mergeCell ref="AS53:AU53"/>
     <mergeCell ref="AG23:AI23"/>
     <mergeCell ref="BH40:BJ40"/>
     <mergeCell ref="X13:AD13"/>
     <mergeCell ref="AS15:AU15"/>
     <mergeCell ref="AE48:AF48"/>
     <mergeCell ref="AS55:AU55"/>
+    <mergeCell ref="BE37:BG37"/>
     <mergeCell ref="AJ50:AL50"/>
     <mergeCell ref="BH20:BJ20"/>
     <mergeCell ref="AG54:AI54"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="BE24:BG24"/>
     <mergeCell ref="BH25:BJ25"/>
-    <mergeCell ref="AM38:AO38"/>
     <mergeCell ref="BB28:BD28"/>
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="BH35:BJ35"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
+    <mergeCell ref="AJ52:AL52"/>
     <mergeCell ref="BH22:BJ22"/>
+    <mergeCell ref="BK52:BQ52"/>
     <mergeCell ref="AG56:AI56"/>
     <mergeCell ref="BE26:BG26"/>
     <mergeCell ref="J16:P16"/>
@@ -18831,13 +19111,14 @@
     <mergeCell ref="Q32:W32"/>
     <mergeCell ref="AY35:BA35"/>
     <mergeCell ref="X22:AD22"/>
-    <mergeCell ref="BH38:BJ38"/>
     <mergeCell ref="BE42:BG42"/>
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
+    <mergeCell ref="BE52:BG52"/>
     <mergeCell ref="BK21:BQ21"/>
     <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AE61:AF61"/>
+    <mergeCell ref="AV64:AX64"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
@@ -18858,6 +19139,7 @@
     <mergeCell ref="AY41:BA41"/>
     <mergeCell ref="X15:AD15"/>
     <mergeCell ref="AV18:AX18"/>
+    <mergeCell ref="E37:I37"/>
     <mergeCell ref="X33:AD33"/>
     <mergeCell ref="AV17:AX17"/>
     <mergeCell ref="AY56:BA56"/>
@@ -18865,6 +19147,7 @@
     <mergeCell ref="AV11:AX11"/>
     <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AS21:AU21"/>
+    <mergeCell ref="AY43:BA43"/>
     <mergeCell ref="BE32:BG32"/>
     <mergeCell ref="BE63:BG63"/>
     <mergeCell ref="BK14:BQ14"/>
@@ -18872,27 +19155,25 @@
     <mergeCell ref="AG32:AI32"/>
     <mergeCell ref="X35:AD35"/>
     <mergeCell ref="AE10:AF11"/>
+    <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
     <mergeCell ref="BK60:BQ60"/>
-    <mergeCell ref="B38:D38"/>
     <mergeCell ref="J18:P18"/>
     <mergeCell ref="AE18:AF18"/>
     <mergeCell ref="BE40:BG40"/>
     <mergeCell ref="AP15:AR15"/>
     <mergeCell ref="AS16:AU16"/>
-    <mergeCell ref="BB44:BD44"/>
-    <mergeCell ref="AJ53:AL53"/>
+    <mergeCell ref="AM54:AO54"/>
+    <mergeCell ref="AG57:AI57"/>
     <mergeCell ref="AV10:BJ10"/>
     <mergeCell ref="BH28:BJ28"/>
     <mergeCell ref="J17:P17"/>
-    <mergeCell ref="AM54:AO54"/>
-    <mergeCell ref="AV44:AX44"/>
+    <mergeCell ref="AJ45:AL45"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="AJ45:AL45"/>
-    <mergeCell ref="AG57:AI57"/>
     <mergeCell ref="E63:I63"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="BB52:BD52"/>
     <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="AY34:BA34"/>
     <mergeCell ref="B33:D33"/>
@@ -18936,13 +19217,13 @@
     <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="AY64:BA64"/>
     <mergeCell ref="AS23:AU23"/>
-    <mergeCell ref="E38:I38"/>
     <mergeCell ref="AY51:BA51"/>
-    <mergeCell ref="Q53:W53"/>
     <mergeCell ref="X56:AD56"/>
     <mergeCell ref="BK22:BQ22"/>
     <mergeCell ref="E13:I13"/>
+    <mergeCell ref="X43:AD43"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="E40:I40"/>
     <mergeCell ref="BK15:BQ15"/>
@@ -18963,8 +19244,6 @@
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="AG25:AI25"/>
     <mergeCell ref="AY33:BA33"/>
-    <mergeCell ref="A52:BQ52"/>
-    <mergeCell ref="BB53:BD53"/>
     <mergeCell ref="T5:AH5"/>
     <mergeCell ref="AM22:AO22"/>
     <mergeCell ref="AP23:AR23"/>
@@ -18972,6 +19251,7 @@
     <mergeCell ref="J20:P20"/>
     <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
+    <mergeCell ref="B43:D43"/>
     <mergeCell ref="BE51:BG51"/>
     <mergeCell ref="AY50:BA50"/>
     <mergeCell ref="BB55:BD55"/>
@@ -18979,12 +19259,11 @@
     <mergeCell ref="A5:S5"/>
     <mergeCell ref="J22:P22"/>
     <mergeCell ref="BH62:BJ62"/>
-    <mergeCell ref="AV38:AX38"/>
+    <mergeCell ref="AY52:BA52"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="BK35:BQ35"/>
     <mergeCell ref="AY39:BA39"/>
-    <mergeCell ref="AG53:AI53"/>
-    <mergeCell ref="X44:AD44"/>
+    <mergeCell ref="AS52:AU52"/>
     <mergeCell ref="AP34:AR34"/>
     <mergeCell ref="AM11:AO11"/>
     <mergeCell ref="X31:AD31"/>
@@ -18997,9 +19276,9 @@
     <mergeCell ref="AV33:AX33"/>
     <mergeCell ref="BE61:BG61"/>
     <mergeCell ref="AP36:AR36"/>
+    <mergeCell ref="AS37:AU37"/>
+    <mergeCell ref="AE14:AF14"/>
     <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="AE14:AF14"/>
-    <mergeCell ref="J38:P38"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="Q28:W28"/>
@@ -19022,6 +19301,7 @@
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="X49:AD49"/>
     <mergeCell ref="E54:I54"/>
+    <mergeCell ref="BE64:BG64"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
     <mergeCell ref="AS63:AU63"/>
@@ -19033,6 +19313,7 @@
     <mergeCell ref="E56:I56"/>
     <mergeCell ref="AP29:AR29"/>
     <mergeCell ref="AV51:AX51"/>
+    <mergeCell ref="E43:I43"/>
     <mergeCell ref="X63:AD63"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BE16:BG16"/>
@@ -19042,11 +19323,13 @@
     <mergeCell ref="BK29:BQ29"/>
     <mergeCell ref="AS40:AU40"/>
     <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="AE35:AF35"/>
     <mergeCell ref="BH14:BJ14"/>
     <mergeCell ref="BK54:BQ54"/>
     <mergeCell ref="AJ62:AL62"/>
+    <mergeCell ref="AJ37:AL37"/>
     <mergeCell ref="AY49:BA49"/>
     <mergeCell ref="BE11:BG11"/>
     <mergeCell ref="AY20:BA20"/>
@@ -19054,14 +19337,16 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
+    <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
+    <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="Q18:W18"/>
     <mergeCell ref="BK49:BQ49"/>
     <mergeCell ref="B63:D63"/>
-    <mergeCell ref="AE38:AF38"/>
+    <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AV54:AX54"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="AP57:AR57"/>
@@ -19071,10 +19356,8 @@
     <mergeCell ref="AS45:AU45"/>
     <mergeCell ref="BK57:BQ57"/>
     <mergeCell ref="AE40:AF40"/>
-    <mergeCell ref="X53:AD53"/>
     <mergeCell ref="X47:AD47"/>
     <mergeCell ref="BH63:BJ63"/>
-    <mergeCell ref="AS38:AU38"/>
     <mergeCell ref="AM14:AO14"/>
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AP42:AR42"/>
@@ -19082,19 +19365,23 @@
     <mergeCell ref="AP58:AR58"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
+    <mergeCell ref="AP52:AR52"/>
     <mergeCell ref="X55:AD55"/>
-    <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="AJ17:AL17"/>
     <mergeCell ref="AM56:AO56"/>
+    <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="J54:P54"/>
+    <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
-    <mergeCell ref="Q44:W44"/>
+    <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
     <mergeCell ref="AY58:BA58"/>
+    <mergeCell ref="J43:P43"/>
     <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="E64:I64"/>
     <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
@@ -19106,6 +19393,7 @@
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
+    <mergeCell ref="BH64:BJ64"/>
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AM33:AO33"/>
     <mergeCell ref="BK26:BQ26"/>
@@ -19119,25 +19407,25 @@
     <mergeCell ref="AE30:AF30"/>
     <mergeCell ref="Q26:W26"/>
     <mergeCell ref="AG10:AU10"/>
-    <mergeCell ref="AG44:AI44"/>
     <mergeCell ref="AV62:AX62"/>
     <mergeCell ref="AM28:AO28"/>
     <mergeCell ref="BE14:BG14"/>
     <mergeCell ref="BB24:BD24"/>
     <mergeCell ref="BB18:BD18"/>
     <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="B52:D52"/>
     <mergeCell ref="AV56:AX56"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE36 AE38:AE42 AE44:AE51 AE53:AE63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE37 AE39:AE43 AE45:AE52 AE54:AE64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG36 AG38:AG42 AG44:AG51 AG53:AG63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG37 AG39:AG43 AG45:AG52 AG54:AG64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV36 AV38:AV42 AV44:AV51 AV53:AV63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV37 AV39:AV43 AV45:AV52 AV54:AV64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
@@ -1539,7 +1539,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -1555,7 +1555,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -2078,7 +2078,7 @@
       <c r="F4" s="11" t="n"/>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="H4" s="10" t="n"/>
@@ -2851,7 +2851,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -2867,7 +2867,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -6484,7 +6484,7 @@
       <c r="E2" s="11" t="n"/>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -10993,7 +10993,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">形式エラーが表示されること（メッセージ `漢字・ひらがな・カタカナで入力してください。`）
+            <t xml:space="preserve">形式エラーが表示されること（メッセージ `漢字・ひらがな・カタカナ・アルファベットで入力してください。`）
 </t>
           </r>
           <r>
@@ -11061,7 +11061,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・顧客要件 2026-07：ひらがな/カタカナ表記の氏名の方に対応するため、氏名（漢字）は漢字のみから漢字・ひらがな・カタカナ許容に緩和
+            <t xml:space="preserve">・顧客要件 2026-07：ひらがな/カタカナ表記の氏名の方に対応するため、氏名（漢字）は漢字・ひらがな・カタカナに加えアルファベットも許容
 </t>
           </r>
           <r>
@@ -11077,7 +11077,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・半角カナ・英数字は引き続き不可。形式不正時は `漢字・ひらがな・カタカナで入力してください。` を表示すること
+            <t xml:space="preserve">・半角カナ・数字は引き続き不可（アルファベットは許容）。形式不正時は `漢字・ひらがな・カタカナ・アルファベットで入力してください。` を表示すること
 </t>
           </r>
           <r>

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
@@ -1539,7 +1539,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -1555,7 +1555,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -2078,7 +2078,7 @@
       <c r="F4" s="11" t="n"/>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="H4" s="10" t="n"/>
@@ -2851,7 +2851,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -2867,7 +2867,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -6484,7 +6484,7 @@
       <c r="E2" s="11" t="n"/>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -15265,7 +15265,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">SELECT rireki_no, denshi_shonin_status, saishin_data_flg, henko_riyu
+            <t xml:space="preserve">SELECT rireki_no, denshi_shonin_status, saishin_data_flg
 </t>
           </r>
           <r>
@@ -15357,7 +15357,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">t_dokusya の denshi_shonin_status が1に更新されること、t_dokusya_rireki に新履歴（denshi_shonin_status=1, saishin_data_flg=true, henko_riyu=`電子版承認`）が追記されること
+            <t xml:space="preserve">t_dokusya の denshi_shonin_status が1に更新されること、t_dokusya_rireki に新履歴（denshi_shonin_status=1, saishin_data_flg=true）が追記されること
 </t>
           </r>
           <r>
@@ -15567,7 +15567,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">SELECT denshi_shonin_status, henko_riyu
+            <t xml:space="preserve">SELECT denshi_shonin_status
 </t>
           </r>
           <r>
@@ -15668,7 +15668,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">t_dokusya の denshi_shonin_status が2に更新されること、t_dokusya_rireki の最新履歴に denshi_shonin_status=2, henko_riyu=`電子版否認` が記録されること
+            <t xml:space="preserve">t_dokusya の denshi_shonin_status が2に更新されること、t_dokusya_rireki の最新履歴に denshi_shonin_status=2 が記録されること
 </t>
           </r>
           <r>
@@ -15992,7 +15992,7 @@
       <c r="BP51" s="10" t="n"/>
       <c r="BQ51" s="11" t="n"/>
     </row>
-    <row r="52" ht="450" customHeight="1">
+    <row r="52" ht="448" customHeight="1">
       <c r="A52" s="44" t="n">
         <v>36</v>
       </c>
@@ -16074,7 +16074,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>履歴一覧の並び順と各行の項目（rireki_no・tetsuzuki_shurui_label・henko_riyu・saishin_data_flg）を確認</t>
+            <t>履歴一覧の並び順と各行の項目（rireki_no・tetsuzuki_shurui_label・saishin_data_flg）を確認</t>
           </r>
         </is>
       </c>
@@ -16134,7 +16134,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">履歴一覧が rireki_no の降順で表示されること、各行に手続種類ラベル（tetsuzuki_shurui_label）・変更理由（henko_riyu）・最新データフラグ（saishin_data_flg）が表示されること
+            <t xml:space="preserve">履歴一覧が rireki_no の降順で表示されること、各行に手続種類ラベル（tetsuzuki_shurui_label）・最新データフラグ（saishin_data_flg）が表示されること
 </t>
           </r>
           <r>

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
@@ -6346,7 +6346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ64"/>
+  <dimension ref="A1:BQ65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -18544,8 +18544,277 @@
       <c r="BP64" s="10" t="n"/>
       <c r="BQ64" s="11" t="n"/>
     </row>
+    <row r="65" ht="450" customHeight="1">
+      <c r="A65" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-047</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>純電子版の編集導線（参照モードで開く・予約変更は非活性）</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属・`dokusya.update` 権限あり）
+・購読種別=電子版（クレカ決済**以外**・承認ステータス=1 承認済）の購読者（dokusya_id=301）が存在
+・購読種別=紙版の購読者（dokusya_id=100）が存在（比較用）</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読者明細検索画面の一覧から電子版（dokusya_id=301）の行を押下し、編集モードで画面を開く
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">モードバーの「当日変更」「予約変更」ボタンの状態を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「当日変更」を押下し、何も入力を変更せずに「更新」を押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>比較のため紙版（dokusya_id=100）を編集モードで開き、「予約変更」ボタンの状態を確認</t>
+          </r>
+        </is>
+      </c>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="11" t="n"/>
+      <c r="X65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">紙版と同じく**参照モード**（全項目 read-only）で表示され、モードバーが表示されること。更新ボタンは表示されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「当日変更」は押下可能、「予約変更」は**非活性（グレーアウト）**で表示されること。ボタン自体は**非表示にならない**こと。あわせて「電子版は当日変更のみです（予約変更は使用できません）。」の補足が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">当日変更モードに切り替わり、情報変更適用日が本日になること。業務項目を変更していないため ACSMS-MSG-011-018（変更がありません。）が表示され、更新（PUT）・履歴（t_dokusya_rireki）が発生しないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">紙版では「予約変更」が押下可能であること（制限は電子版のみ）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・従来は電子版のみモードバーを表示せず、開いた瞬間から編集可能（当日変更固定）だった。同じ編集画面が購読種別によって参照/編集で開き分かれ、誤操作で保存しやすかったため、導線を紙版と統一した（機能定義 §15.0）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「予約変更」を非表示ではなく非活性にするのは、隠すと「この画面に予約変更機能が無い」と誤読され、紙版との違いが画面から伝わらないため
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・非活性はUIの制御に過ぎないため、FEは selectMode 側でも予約変更への遷移を弾き、BEも `change_mode='reserved'` を VALIDATION_ERROR で拒否する（三重の防御）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="11" t="n"/>
+      <c r="AE65" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF65" s="11" t="n"/>
+      <c r="AG65" s="45" t="inlineStr"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="11" t="n"/>
+      <c r="AJ65" s="45" t="inlineStr"/>
+      <c r="AK65" s="10" t="n"/>
+      <c r="AL65" s="11" t="n"/>
+      <c r="AM65" s="45" t="inlineStr"/>
+      <c r="AN65" s="10" t="n"/>
+      <c r="AO65" s="11" t="n"/>
+      <c r="AP65" s="45" t="inlineStr"/>
+      <c r="AQ65" s="10" t="n"/>
+      <c r="AR65" s="11" t="n"/>
+      <c r="AS65" s="45" t="inlineStr"/>
+      <c r="AT65" s="10" t="n"/>
+      <c r="AU65" s="11" t="n"/>
+      <c r="AV65" s="45" t="inlineStr"/>
+      <c r="AW65" s="10" t="n"/>
+      <c r="AX65" s="11" t="n"/>
+      <c r="AY65" s="45" t="inlineStr"/>
+      <c r="AZ65" s="10" t="n"/>
+      <c r="BA65" s="11" t="n"/>
+      <c r="BB65" s="45" t="inlineStr"/>
+      <c r="BC65" s="10" t="n"/>
+      <c r="BD65" s="11" t="n"/>
+      <c r="BE65" s="45" t="inlineStr"/>
+      <c r="BF65" s="10" t="n"/>
+      <c r="BG65" s="11" t="n"/>
+      <c r="BH65" s="45" t="inlineStr"/>
+      <c r="BI65" s="10" t="n"/>
+      <c r="BJ65" s="11" t="n"/>
+      <c r="BK65" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL65" s="10" t="n"/>
+      <c r="BM65" s="10" t="n"/>
+      <c r="BN65" s="10" t="n"/>
+      <c r="BO65" s="10" t="n"/>
+      <c r="BP65" s="10" t="n"/>
+      <c r="BQ65" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="871">
+  <mergeCells count="888">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -18577,6 +18846,7 @@
     <mergeCell ref="Q37:W37"/>
     <mergeCell ref="AJ20:AL20"/>
     <mergeCell ref="AM21:AO21"/>
+    <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
     <mergeCell ref="J57:P57"/>
@@ -18639,6 +18909,7 @@
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
     <mergeCell ref="AS64:AU64"/>
+    <mergeCell ref="J65:P65"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
     <mergeCell ref="BE33:BG33"/>
@@ -18745,6 +19016,7 @@
     <mergeCell ref="Q64:W64"/>
     <mergeCell ref="Q51:W51"/>
     <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="A53:BQ53"/>
@@ -18798,6 +19070,7 @@
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="E26:I26"/>
     <mergeCell ref="AY37:BA37"/>
+    <mergeCell ref="BE65:BG65"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
     <mergeCell ref="J36:P36"/>
@@ -18812,6 +19085,7 @@
     <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="AV29:AX29"/>
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="Q65:W65"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
     <mergeCell ref="AP63:AR63"/>
@@ -18824,6 +19098,7 @@
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
+    <mergeCell ref="AJ65:AL65"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AS28:AU28"/>
     <mergeCell ref="AM31:AO31"/>
@@ -18861,6 +19136,7 @@
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="AG65:AI65"/>
     <mergeCell ref="AV55:AX55"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
@@ -18890,6 +19166,7 @@
     <mergeCell ref="J52:P52"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
+    <mergeCell ref="BB65:BD65"/>
     <mergeCell ref="E60:I60"/>
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="AV60:AX60"/>
@@ -19005,6 +19282,7 @@
     <mergeCell ref="X17:AD17"/>
     <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="BE18:BG18"/>
     <mergeCell ref="AJ31:AL31"/>
     <mergeCell ref="B62:D62"/>
@@ -19051,6 +19329,7 @@
     <mergeCell ref="BB35:BD35"/>
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="J61:P61"/>
@@ -19115,6 +19394,7 @@
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
     <mergeCell ref="BE52:BG52"/>
+    <mergeCell ref="BK65:BQ65"/>
     <mergeCell ref="BK21:BQ21"/>
     <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AE61:AF61"/>
@@ -19199,6 +19479,7 @@
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
+    <mergeCell ref="BH65:BJ65"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -19240,6 +19521,7 @@
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="AS26:AU26"/>
     <mergeCell ref="B54:D54"/>
+    <mergeCell ref="AE65:AF65"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="AG25:AI25"/>
@@ -19292,6 +19574,7 @@
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
+    <mergeCell ref="AY65:BA65"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="AY21:BA21"/>
@@ -19307,6 +19590,7 @@
     <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
+    <mergeCell ref="X65:AD65"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F3:Q3"/>
@@ -19337,6 +19621,7 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
+    <mergeCell ref="B65:D65"/>
     <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
@@ -19390,6 +19675,7 @@
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
+    <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
@@ -19419,13 +19705,13 @@
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE37 AE39:AE43 AE45:AE52 AE54:AE64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE37 AE39:AE43 AE45:AE52 AE54:AE65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG37 AG39:AG43 AG45:AG52 AG54:AG64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG37 AG39:AG43 AG45:AG52 AG54:AG65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV37 AV39:AV43 AV45:AV52 AV54:AV64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV37 AV39:AV43 AV45:AV52 AV54:AV65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
@@ -6346,7 +6346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ65"/>
+  <dimension ref="A1:BQ66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -18813,8 +18813,285 @@
       <c r="BP65" s="10" t="n"/>
       <c r="BQ65" s="11" t="n"/>
     </row>
+    <row r="66" ht="450" customHeight="1">
+      <c r="A66" s="44" t="n">
+        <v>49</v>
+      </c>
+      <c r="B66" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-048</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="46" t="inlineStr">
+        <is>
+          <t>販売店ドロップダウンの購読種別連動（ダミー販売店の絞込）</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属・`dokusya.create` / `dokusya.update` 権限あり）
+・ja_id=100 に販売店が3件存在：`1000000001`（営業中）、`1000000002`（営業中）、`9999999999`（電子版ダミー・営業中）
+・購読種別=電子版の購読者（dokusya_id=301・販売店=`9999999999`）が存在</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="11" t="n"/>
+      <c r="Q66" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読者情報登録画面（新規）を開き、購読種別=1:紙版（既定）の状態で販売店コードのドロップダウンを開く
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">販売店コード=`1000000001` を選択したうえで、購読種別を 2:電子版 へ切り替え、販売店コードの表示と候補を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読種別を 3:併読 へ切り替え、販売店コードの候補を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>電子版の購読者（dokusya_id=301）を編集モードで開き、販売店コードの表示と候補を確認</t>
+          </r>
+        </is>
+      </c>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="11" t="n"/>
+      <c r="X66" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`1000000001` と `1000000002` のみが候補に並び、ダミー販売店 `9999999999` は候補に**現れない**こと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">販売店コードの選択が**解除**され（空欄になり）、候補が `9999999999` の**1件のみ**に入れ替わること。切替前に選んでいた `1000000001` は候補に残らないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">候補が `1000000001` / `1000000002` に戻り、`9999999999` は現れないこと。購読種別を切り替えたため選択は再び解除されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読種別は編集で不変のため、候補は `9999999999` の1件のみで、現在の選択 `9999999999` がそのまま表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・電子版は紙を配達しないため実在の販売店に紐づかないが、`t_dokusya.hanbaiten_id` は NOT NULL。そのため JA ごとに `hanbaiten_code = 9999999999` のダミー販売店を受け皿として用意し、電子版はそこへ紐づける（顧客要件 2026-08）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・絞込は BE（`GET /api/v1/hanbaiten/dropdown` の `dummy=only` / `dummy=exclude`）の SQL 側で行い、FE はどちら側かを送るだけ。FE で候補配列を後から filter すると、ページング時に「絞込後0件」のページが返り無限スクロールが止まる
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・切替時に選択を解除するのは、残すと画面には候補に無いコードが表示され、そのまま更新すると BE が別種別の販売店を受け付けてしまうため
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・営業中フィルタ（`active_only`）とは独立。編集で既に廃店の販売店へ紐づく購読者は従来どおり `include_id` ピンで現在の選択を復元する</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="11" t="n"/>
+      <c r="AE66" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF66" s="11" t="n"/>
+      <c r="AG66" s="45" t="inlineStr"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="11" t="n"/>
+      <c r="AJ66" s="45" t="inlineStr"/>
+      <c r="AK66" s="10" t="n"/>
+      <c r="AL66" s="11" t="n"/>
+      <c r="AM66" s="45" t="inlineStr"/>
+      <c r="AN66" s="10" t="n"/>
+      <c r="AO66" s="11" t="n"/>
+      <c r="AP66" s="45" t="inlineStr"/>
+      <c r="AQ66" s="10" t="n"/>
+      <c r="AR66" s="11" t="n"/>
+      <c r="AS66" s="45" t="inlineStr"/>
+      <c r="AT66" s="10" t="n"/>
+      <c r="AU66" s="11" t="n"/>
+      <c r="AV66" s="45" t="inlineStr"/>
+      <c r="AW66" s="10" t="n"/>
+      <c r="AX66" s="11" t="n"/>
+      <c r="AY66" s="45" t="inlineStr"/>
+      <c r="AZ66" s="10" t="n"/>
+      <c r="BA66" s="11" t="n"/>
+      <c r="BB66" s="45" t="inlineStr"/>
+      <c r="BC66" s="10" t="n"/>
+      <c r="BD66" s="11" t="n"/>
+      <c r="BE66" s="45" t="inlineStr"/>
+      <c r="BF66" s="10" t="n"/>
+      <c r="BG66" s="11" t="n"/>
+      <c r="BH66" s="45" t="inlineStr"/>
+      <c r="BI66" s="10" t="n"/>
+      <c r="BJ66" s="11" t="n"/>
+      <c r="BK66" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL66" s="10" t="n"/>
+      <c r="BM66" s="10" t="n"/>
+      <c r="BN66" s="10" t="n"/>
+      <c r="BO66" s="10" t="n"/>
+      <c r="BP66" s="10" t="n"/>
+      <c r="BQ66" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="888">
+  <mergeCells count="905">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -18899,8 +19176,10 @@
     <mergeCell ref="AE64:AF64"/>
     <mergeCell ref="AS62:AU62"/>
     <mergeCell ref="AV63:AX63"/>
+    <mergeCell ref="AP66:AR66"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
+    <mergeCell ref="BK66:BQ66"/>
     <mergeCell ref="X16:AD16"/>
     <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="AE57:AF57"/>
@@ -18995,6 +19274,7 @@
     <mergeCell ref="AE58:AF58"/>
     <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="AM63:AO63"/>
+    <mergeCell ref="AG66:AI66"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
@@ -19077,6 +19357,7 @@
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
+    <mergeCell ref="AY66:BA66"/>
     <mergeCell ref="AV21:AX21"/>
     <mergeCell ref="BK24:BQ24"/>
     <mergeCell ref="X45:AD45"/>
@@ -19132,6 +19413,7 @@
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
     <mergeCell ref="Q60:W60"/>
+    <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
@@ -19167,6 +19449,7 @@
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
     <mergeCell ref="BB65:BD65"/>
+    <mergeCell ref="BE66:BG66"/>
     <mergeCell ref="E60:I60"/>
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="AV60:AX60"/>
@@ -19185,6 +19468,7 @@
     <mergeCell ref="AM42:AO42"/>
     <mergeCell ref="X62:AD62"/>
     <mergeCell ref="AE37:AF37"/>
+    <mergeCell ref="B66:D66"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="AM29:AO29"/>
     <mergeCell ref="AM23:AO23"/>
@@ -19244,6 +19528,7 @@
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="E66:I66"/>
     <mergeCell ref="AM48:AO48"/>
     <mergeCell ref="Q49:W49"/>
     <mergeCell ref="BK43:BQ43"/>
@@ -19290,6 +19575,7 @@
     <mergeCell ref="AG35:AI35"/>
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
+    <mergeCell ref="AV66:AX66"/>
     <mergeCell ref="AE60:AF60"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
@@ -19316,6 +19602,7 @@
     <mergeCell ref="AP51:AR51"/>
     <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK64:BQ64"/>
+    <mergeCell ref="J66:P66"/>
     <mergeCell ref="BK51:BQ51"/>
     <mergeCell ref="X60:AD60"/>
     <mergeCell ref="AM61:AO61"/>
@@ -19384,6 +19671,7 @@
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="AE66:AF66"/>
     <mergeCell ref="Q45:W45"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="BB31:BD31"/>
@@ -19393,6 +19681,7 @@
     <mergeCell ref="BE42:BG42"/>
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
+    <mergeCell ref="AS66:AU66"/>
     <mergeCell ref="BE52:BG52"/>
     <mergeCell ref="BK65:BQ65"/>
     <mergeCell ref="BK21:BQ21"/>
@@ -19491,6 +19780,7 @@
     <mergeCell ref="BE59:BG59"/>
     <mergeCell ref="AY62:BA62"/>
     <mergeCell ref="BB63:BD63"/>
+    <mergeCell ref="AJ66:AL66"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
@@ -19499,6 +19789,7 @@
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="AY64:BA64"/>
+    <mergeCell ref="Q66:W66"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="AY51:BA51"/>
     <mergeCell ref="X56:AD56"/>
@@ -19579,6 +19870,7 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="AY21:BA21"/>
     <mergeCell ref="E61:I61"/>
+    <mergeCell ref="BB66:BD66"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
@@ -19591,6 +19883,7 @@
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
     <mergeCell ref="X65:AD65"/>
+    <mergeCell ref="AM66:AO66"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F3:Q3"/>
@@ -19680,6 +19973,7 @@
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
     <mergeCell ref="BH64:BJ64"/>
+    <mergeCell ref="X66:AD66"/>
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AM33:AO33"/>
     <mergeCell ref="BK26:BQ26"/>
@@ -19705,13 +19999,13 @@
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE37 AE39:AE43 AE45:AE52 AE54:AE65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE37 AE39:AE43 AE45:AE52 AE54:AE66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG37 AG39:AG43 AG45:AG52 AG54:AG65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG37 AG39:AG43 AG45:AG52 AG54:AG66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV37 AV39:AV43 AV45:AV52 AV54:AV65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV37 AV39:AV43 AV45:AV52 AV54:AV66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
@@ -6346,7 +6346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ66"/>
+  <dimension ref="A1:BQ67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -16074,7 +16074,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>履歴一覧の並び順と各行の項目（rireki_no・tetsuzuki_shurui_label・saishin_data_flg）を確認</t>
+            <t>履歴一覧の並び順と各行の項目（rireki_no・tetsuzuki_shurui・saishin_data_flg）を確認</t>
           </r>
         </is>
       </c>
@@ -16134,7 +16134,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">履歴一覧が rireki_no の降順で表示されること、各行に手続種類ラベル（tetsuzuki_shurui_label）・最新データフラグ（saishin_data_flg）が表示されること
+            <t xml:space="preserve">履歴一覧が rireki_no の降順で表示されること、各行に手続種類（tetsuzuki_shurui の m_code ラベル）・最新データフラグ（saishin_data_flg）が表示されること
 </t>
           </r>
           <r>
@@ -19090,8 +19090,393 @@
       <c r="BP66" s="10" t="n"/>
       <c r="BQ66" s="11" t="n"/>
     </row>
+    <row r="67" ht="450" customHeight="1">
+      <c r="A67" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="B67" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-049</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="46" t="inlineStr">
+        <is>
+          <t>承認/否認前に支払方法・引落口座4項目を編集して保存（#56524）</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属、電子版取扱フラグあり）
+・購読種別=電子版 かつ denshi_shonin_status=0（承認待ち）の購読者（dokusya_id=200）が存在
+・支払方法=口座引落（shiharai_hoho=1）、自JAに金融機関支店（kinyu_shiten_flg=true）が2件以上存在</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="11" t="n"/>
+      <c r="Q67" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">承認待ちの購読者を編集モードで開き、各項目の活性状態を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支払方法=口座引落のまま引落口座支店を別の支店へ変更し、引落口座貯金種目=当座、引落口座番号=`9876543210`、引落口座名義=`ﾀﾅｶ ﾀﾛｳ` を入力して「承認・登録」ボタンを押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DBで保存結果を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT denshi_shonin_status, shiharai_hoho, bank_branch_code, bank_branch_name,
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">hikiotoshi_yokin_shubetsu, hikiotoshi_koza_no, hikiotoshi_koza_meigi
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya WHERE dokusya_id = 200;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">別の承認待ち購読者を開き、引落口座番号を空欄にして「承認・登録」ボタンを押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">別の承認待ち購読者を開き、引落口座名義を修正してから「承認しない」ボタンを押下し、確認ダイアログで「はい」を選択
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>別の承認待ち購読者（支払方法=現金集金・引落先未設定）を開き、支払方法を口座引落へ変更し、引落口座支店を未選択のまま「承認・登録」ボタンを押下</t>
+          </r>
+        </is>
+      </c>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="11" t="n"/>
+      <c r="X67" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支払方法・引落口座支店・引落口座貯金種目・引落口座番号・引落口座名義の5項目と新聞単価が**活性**であること。それ以外の項目（購読者氏名、メールアドレス、組合員コードなど）は**非活性**のままであること。支払方法の選択肢のうちクレジットカードは**非活性**であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「承認しました。」が表示され、購読者明細検索画面へ遷移すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`denshi_shonin_status=1` に加え、入力した4項目が保存されていること。`bank_branch_code` / `bank_branch_name` は選択した支店から逆引きされた値になっていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">承認APIが呼ばれず、引落口座番号の直下に「必須項目です。」が表示され、当該項目へフォーカスが移動すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「否認しました。」が表示され、`denshi_shonin_status=2` と修正後の引落口座名義がともに保存されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">承認APIが呼ばれず、引落口座支店の直下に「必須項目です。」が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・電子版申込の支払方法・口座情報は読者本人の自己申告のため誤りが多い。従来は承認画面で新聞単価しか直せず「承認 → 再編集」の2操作が必要だった（顧客要件 2026-08 / #56524）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・電子版はクレジットカードを選択できない（電子版読者管理システム連携専用）。APIへ直接 `shiharai_hoho=6` を送っても `VALIDATION_ERROR`（shiharai_hoho）となる
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・引落口座支店は自JAの金融機関支店のみ選択可。他JAの支店IDを直接APIへ送っても `VALIDATION_ERROR`（bank_shiten_id）となる
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・支払方法=口座引落以外の場合、4項目は任意（空欄のまま承認できる）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="11" t="n"/>
+      <c r="AE67" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF67" s="11" t="n"/>
+      <c r="AG67" s="45" t="inlineStr"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="11" t="n"/>
+      <c r="AJ67" s="45" t="inlineStr"/>
+      <c r="AK67" s="10" t="n"/>
+      <c r="AL67" s="11" t="n"/>
+      <c r="AM67" s="45" t="inlineStr"/>
+      <c r="AN67" s="10" t="n"/>
+      <c r="AO67" s="11" t="n"/>
+      <c r="AP67" s="45" t="inlineStr"/>
+      <c r="AQ67" s="10" t="n"/>
+      <c r="AR67" s="11" t="n"/>
+      <c r="AS67" s="45" t="inlineStr"/>
+      <c r="AT67" s="10" t="n"/>
+      <c r="AU67" s="11" t="n"/>
+      <c r="AV67" s="45" t="inlineStr"/>
+      <c r="AW67" s="10" t="n"/>
+      <c r="AX67" s="11" t="n"/>
+      <c r="AY67" s="45" t="inlineStr"/>
+      <c r="AZ67" s="10" t="n"/>
+      <c r="BA67" s="11" t="n"/>
+      <c r="BB67" s="45" t="inlineStr"/>
+      <c r="BC67" s="10" t="n"/>
+      <c r="BD67" s="11" t="n"/>
+      <c r="BE67" s="45" t="inlineStr"/>
+      <c r="BF67" s="10" t="n"/>
+      <c r="BG67" s="11" t="n"/>
+      <c r="BH67" s="45" t="inlineStr"/>
+      <c r="BI67" s="10" t="n"/>
+      <c r="BJ67" s="11" t="n"/>
+      <c r="BK67" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL67" s="10" t="n"/>
+      <c r="BM67" s="10" t="n"/>
+      <c r="BN67" s="10" t="n"/>
+      <c r="BO67" s="10" t="n"/>
+      <c r="BP67" s="10" t="n"/>
+      <c r="BQ67" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="905">
+  <mergeCells count="922">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -19158,6 +19543,7 @@
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="AG45:AI45"/>
+    <mergeCell ref="AS67:AU67"/>
     <mergeCell ref="AY29:BA29"/>
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="AJ33:AL33"/>
@@ -19194,6 +19580,7 @@
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
+    <mergeCell ref="AP67:AR67"/>
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="AY57:BA57"/>
@@ -19261,7 +19648,9 @@
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
     <mergeCell ref="BE54:BG54"/>
+    <mergeCell ref="AJ67:AL67"/>
     <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="BK67:BQ67"/>
     <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
@@ -19440,9 +19829,11 @@
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
     <mergeCell ref="AP40:AR40"/>
+    <mergeCell ref="BH67:BJ67"/>
     <mergeCell ref="J42:P42"/>
     <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="AY67:BA67"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="X36:AD36"/>
     <mergeCell ref="J52:P52"/>
@@ -19451,6 +19842,7 @@
     <mergeCell ref="BB65:BD65"/>
     <mergeCell ref="BE66:BG66"/>
     <mergeCell ref="E60:I60"/>
+    <mergeCell ref="X67:AD67"/>
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
@@ -19482,6 +19874,7 @@
     <mergeCell ref="AE26:AF26"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B67:D67"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
     <mergeCell ref="AV58:AX58"/>
@@ -19537,6 +19930,7 @@
     <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
+    <mergeCell ref="E67:I67"/>
     <mergeCell ref="AY14:BA14"/>
     <mergeCell ref="AJ18:AL18"/>
     <mergeCell ref="J51:P51"/>
@@ -19604,6 +19998,7 @@
     <mergeCell ref="BK64:BQ64"/>
     <mergeCell ref="J66:P66"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="AM67:AO67"/>
     <mergeCell ref="X60:AD60"/>
     <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
@@ -19666,6 +20061,7 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="AG49:AI49"/>
     <mergeCell ref="AE51:AF51"/>
+    <mergeCell ref="AV67:AX67"/>
     <mergeCell ref="BB29:BD29"/>
     <mergeCell ref="BB23:BD23"/>
     <mergeCell ref="E24:I24"/>
@@ -19684,9 +20080,11 @@
     <mergeCell ref="AS66:AU66"/>
     <mergeCell ref="BE52:BG52"/>
     <mergeCell ref="BK65:BQ65"/>
+    <mergeCell ref="J67:P67"/>
     <mergeCell ref="BK21:BQ21"/>
     <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AE61:AF61"/>
+    <mergeCell ref="AE67:AF67"/>
     <mergeCell ref="AV64:AX64"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
@@ -19852,6 +20250,7 @@
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
     <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="BE67:BG67"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="Q28:W28"/>
@@ -19871,6 +20270,7 @@
     <mergeCell ref="AY21:BA21"/>
     <mergeCell ref="E61:I61"/>
     <mergeCell ref="BB66:BD66"/>
+    <mergeCell ref="Q67:W67"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
@@ -19923,6 +20323,7 @@
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="Q18:W18"/>
     <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="AG67:AI67"/>
     <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AV54:AX54"/>
@@ -19951,6 +20352,7 @@
     <mergeCell ref="J54:P54"/>
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
+    <mergeCell ref="BB67:BD67"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
@@ -19999,13 +20401,13 @@
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE37 AE39:AE43 AE45:AE52 AE54:AE66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE37 AE39:AE43 AE45:AE52 AE54:AE67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG37 AG39:AG43 AG45:AG52 AG54:AG66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG37 AG39:AG43 AG45:AG52 AG54:AG67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV37 AV39:AV43 AV45:AV52 AV54:AV66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV37 AV39:AV43 AV45:AV52 AV54:AV67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1361,20 +1361,80 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>テストケース追加: TC-011-050 読者属性の従属4項目（かつJAグループ役職員 / 農業関係 / その他の内容 — 顧客DB設計 2026-08）、TC-011-051 電子版メールアドレス重複チェックの JA横断化（#56568）、TC-011-052 併読の配達先情報エリア表示（顧客要件 2026-08）。</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6346,7 +6406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ67"/>
+  <dimension ref="A1:BQ70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -19475,13 +19535,906 @@
       <c r="BP67" s="10" t="n"/>
       <c r="BQ67" s="11" t="n"/>
     </row>
+    <row r="68" ht="450" customHeight="1">
+      <c r="A68" s="44" t="n">
+        <v>51</v>
+      </c>
+      <c r="B68" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-050</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="46" t="inlineStr">
+        <is>
+          <t>読者属性の従属4項目（かつJAグループ役職員 / 農業関係 / その他の内容）</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100、電子版取扱フラグあり）
+・購読種別=電子版 の新規登録画面を開いている
+・読者属性（dokusyaso_bunrui）は単一選択（農業者 / JAグループ役職員 / 企業・団体 / 学生 / その他）</t>
+        </is>
+      </c>
+      <c r="K68" s="10" t="n"/>
+      <c r="L68" s="10" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="11" t="n"/>
+      <c r="Q68" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">読者属性で「農業者」を選択し、右側の「かつJAグループ役職員」チェックボックスの表示状態を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「かつJAグループ役職員」にチェックを入れ、主な生産物で「米」「野菜」を選択して登録
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DBで保存結果を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT dokusyaso_bunrui, ja_yakushokuin_flg, nogyo_kankei_flg,
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">nogyosya_bunrui, dokusyaso_bunrui_sonota, nogyosya_bunrui_sonota
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya WHERE dokusya_id = :作成したID;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">新規登録画面で読者属性「企業・団体」を選択し、「農業関係」チェックボックスの表示を確認してチェックを入れて登録
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">新規登録画面で読者属性「その他」を選択し、「その他の内容」欄に `自営業` を入力して登録
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">新規登録画面で読者属性「学生」を選択し、従属項目の表示状態を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>読者属性「農業者」＋主な生産物「その他」を選択し、「主な生産物（その他の内容）」欄に `きのこ` を入力して登録</t>
+          </r>
+        </is>
+      </c>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="10" t="n"/>
+      <c r="U68" s="10" t="n"/>
+      <c r="V68" s="10" t="n"/>
+      <c r="W68" s="11" t="n"/>
+      <c r="X68" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「かつJAグループ役職員」チェックボックスが表示・活性であること（読者属性=農業者のときのみ）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「登録しました。」が表示され、購読者明細検索画面へ遷移すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`dokusyaso_bunrui='0'`、`ja_yakushokuin_flg=true`、`nogyosya_bunrui='0,1'` が保存されていること。`nogyo_kankei_flg` は false、`dokusyaso_bunrui_sonota` / `nogyosya_bunrui_sonota` は空文字であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「農業関係」チェックボックスが表示・活性であり（読者属性=企業・団体のときのみ）、`nogyo_kankei_flg=true` が保存されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「その他の内容」欄が表示・活性であり（読者属性=その他のときのみ）、`dokusyaso_bunrui_sonota='自営業'` が保存されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「かつJAグループ役職員」「農業関係」「その他の内容」がいずれも非表示であること（学生は従属項目を持たない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>「主な生産物（その他の内容）」欄が表示・活性であり（主な生産物に「その他」を含むときのみ）、`nogyosya_bunrui_sonota='きのこ'` が保存されること</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y68" s="10" t="n"/>
+      <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="10" t="n"/>
+      <c r="AB68" s="10" t="n"/>
+      <c r="AC68" s="10" t="n"/>
+      <c r="AD68" s="11" t="n"/>
+      <c r="AE68" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF68" s="11" t="n"/>
+      <c r="AG68" s="45" t="inlineStr"/>
+      <c r="AH68" s="10" t="n"/>
+      <c r="AI68" s="11" t="n"/>
+      <c r="AJ68" s="45" t="inlineStr"/>
+      <c r="AK68" s="10" t="n"/>
+      <c r="AL68" s="11" t="n"/>
+      <c r="AM68" s="45" t="inlineStr"/>
+      <c r="AN68" s="10" t="n"/>
+      <c r="AO68" s="11" t="n"/>
+      <c r="AP68" s="45" t="inlineStr"/>
+      <c r="AQ68" s="10" t="n"/>
+      <c r="AR68" s="11" t="n"/>
+      <c r="AS68" s="45" t="inlineStr"/>
+      <c r="AT68" s="10" t="n"/>
+      <c r="AU68" s="11" t="n"/>
+      <c r="AV68" s="45" t="inlineStr"/>
+      <c r="AW68" s="10" t="n"/>
+      <c r="AX68" s="11" t="n"/>
+      <c r="AY68" s="45" t="inlineStr"/>
+      <c r="AZ68" s="10" t="n"/>
+      <c r="BA68" s="11" t="n"/>
+      <c r="BB68" s="45" t="inlineStr"/>
+      <c r="BC68" s="10" t="n"/>
+      <c r="BD68" s="11" t="n"/>
+      <c r="BE68" s="45" t="inlineStr"/>
+      <c r="BF68" s="10" t="n"/>
+      <c r="BG68" s="11" t="n"/>
+      <c r="BH68" s="45" t="inlineStr"/>
+      <c r="BI68" s="10" t="n"/>
+      <c r="BJ68" s="11" t="n"/>
+      <c r="BK68" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL68" s="10" t="n"/>
+      <c r="BM68" s="10" t="n"/>
+      <c r="BN68" s="10" t="n"/>
+      <c r="BO68" s="10" t="n"/>
+      <c r="BP68" s="10" t="n"/>
+      <c r="BQ68" s="11" t="n"/>
+    </row>
+    <row r="69" ht="368" customHeight="1">
+      <c r="A69" s="44" t="n">
+        <v>52</v>
+      </c>
+      <c r="B69" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-051</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="46" t="inlineStr">
+        <is>
+          <t>電子版メールアドレスの重複チェックがJA横断であること（#56568）</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100）
+・**別のJA**（ja_id=200）に 購読種別=電子版・メールアドレス `dup@example.com` の購読者が存在
+・自JA（ja_id=100）に 購読種別=紙版・メールアドレス `paper@example.com` の購読者が存在
+・別のJA（ja_id=200）に 購読種別=電子版・メールアドレス `deleted@example.com` の**論理削除済み**購読者が存在</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="11" t="n"/>
+      <c r="Q69" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">自JAで購読種別=電子版の新規登録を行い、メールアドレスに `dup@example.com` を入力して登録
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">自JAで購読種別=電子版の新規登録を行い、メールアドレスに `paper@example.com` を入力して登録
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">自JAで購読種別=電子版の新規登録を行い、メールアドレスに `deleted@example.com` を入力して登録
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>自JAで購読種別=**紙版**の新規登録を行い、メールアドレスに `paper@example.com` を入力して登録</t>
+          </r>
+        </is>
+      </c>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="11" t="n"/>
+      <c r="X69" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード400（`error_code: DUPLICATE_EMAIL`）が返却され、メールアドレス欄にエラーメッセージが表示されること。**他JAのレコードであっても重複と判定される**こと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">登録が成功すること（重複判定の対象は `dokusya_shubetsu IN (2,3)` のみ。紙版のメールとは衝突しない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">登録が成功すること（論理削除済みレコードは対象外。メールアドレスを再利用できる）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>登録が成功すること（紙版同士のメール重複は従来どおり許容）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="11" t="n"/>
+      <c r="AE69" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF69" s="11" t="n"/>
+      <c r="AG69" s="45" t="inlineStr"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="11" t="n"/>
+      <c r="AJ69" s="45" t="inlineStr"/>
+      <c r="AK69" s="10" t="n"/>
+      <c r="AL69" s="11" t="n"/>
+      <c r="AM69" s="45" t="inlineStr"/>
+      <c r="AN69" s="10" t="n"/>
+      <c r="AO69" s="11" t="n"/>
+      <c r="AP69" s="45" t="inlineStr"/>
+      <c r="AQ69" s="10" t="n"/>
+      <c r="AR69" s="11" t="n"/>
+      <c r="AS69" s="45" t="inlineStr"/>
+      <c r="AT69" s="10" t="n"/>
+      <c r="AU69" s="11" t="n"/>
+      <c r="AV69" s="45" t="inlineStr"/>
+      <c r="AW69" s="10" t="n"/>
+      <c r="AX69" s="11" t="n"/>
+      <c r="AY69" s="45" t="inlineStr"/>
+      <c r="AZ69" s="10" t="n"/>
+      <c r="BA69" s="11" t="n"/>
+      <c r="BB69" s="45" t="inlineStr"/>
+      <c r="BC69" s="10" t="n"/>
+      <c r="BD69" s="11" t="n"/>
+      <c r="BE69" s="45" t="inlineStr"/>
+      <c r="BF69" s="10" t="n"/>
+      <c r="BG69" s="11" t="n"/>
+      <c r="BH69" s="45" t="inlineStr"/>
+      <c r="BI69" s="10" t="n"/>
+      <c r="BJ69" s="11" t="n"/>
+      <c r="BK69" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL69" s="10" t="n"/>
+      <c r="BM69" s="10" t="n"/>
+      <c r="BN69" s="10" t="n"/>
+      <c r="BO69" s="10" t="n"/>
+      <c r="BP69" s="10" t="n"/>
+      <c r="BQ69" s="11" t="n"/>
+    </row>
+    <row r="70" ht="450" customHeight="1">
+      <c r="A70" s="44" t="n">
+        <v>53</v>
+      </c>
+      <c r="B70" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-052</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="11" t="n"/>
+      <c r="E70" s="46" t="inlineStr">
+        <is>
+          <t>併読の配達先情報エリアが表示されること（顧客要件 2026-08）</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100）
+・購読種別=**併読**（dokusya_shubetsu=3）の購読者が存在すること
+・当該購読者は読者同期バッチ経由で作成され、配達先が電子版の `paper_*` 由来で入っていること
+・購読種別=電子版（dokusya_shubetsu=2）の購読者も 1 件存在すること</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="11" t="n"/>
+      <c r="Q70" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">併読の購読者を詳細画面で開き、「配達先情報」エリアの表示有無を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">配達先の郵便番号・都道府県・市町村郡・丁目番地が、電子版側の `paper_zip` / `paper_pref_id` / `paper_addr` / `paper_city` と一致することを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT haitatsu_same_flg, haitatsu_yubin_no, haitatsu_todofuken_code,
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">haitatsu_shikuchoson, haitatsu_chome_banchi, haitatsu_tatemono_mei
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya WHERE dokusya_id = :併読のID;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">同じ画面で入力項目が編集できるかを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>電子版（dokusya_shubetsu=2）の購読者を開き、「配達先情報」エリアの表示有無を確認</t>
+          </r>
+        </is>
+      </c>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="11" t="n"/>
+      <c r="X70" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「配達先情報」エリアが**表示される**こと（従来は電子版と同じ扱いで非表示だった）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`haitatsu_same_flg=false` であり、配達先住所が購読者住所ではなく電子版の `paper_*` 由来の値と一致すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">併読レコードは電子版読者管理システムがバッチ連携で管理するため、全項目が**参照のみ**（更新APIは `DOKUSYA_READ_ONLY` 403）であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>電子版では「配達先情報」エリアが**表示されない**こと（配達が無いため）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="10" t="n"/>
+      <c r="AD70" s="11" t="n"/>
+      <c r="AE70" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF70" s="11" t="n"/>
+      <c r="AG70" s="45" t="inlineStr"/>
+      <c r="AH70" s="10" t="n"/>
+      <c r="AI70" s="11" t="n"/>
+      <c r="AJ70" s="45" t="inlineStr"/>
+      <c r="AK70" s="10" t="n"/>
+      <c r="AL70" s="11" t="n"/>
+      <c r="AM70" s="45" t="inlineStr"/>
+      <c r="AN70" s="10" t="n"/>
+      <c r="AO70" s="11" t="n"/>
+      <c r="AP70" s="45" t="inlineStr"/>
+      <c r="AQ70" s="10" t="n"/>
+      <c r="AR70" s="11" t="n"/>
+      <c r="AS70" s="45" t="inlineStr"/>
+      <c r="AT70" s="10" t="n"/>
+      <c r="AU70" s="11" t="n"/>
+      <c r="AV70" s="45" t="inlineStr"/>
+      <c r="AW70" s="10" t="n"/>
+      <c r="AX70" s="11" t="n"/>
+      <c r="AY70" s="45" t="inlineStr"/>
+      <c r="AZ70" s="10" t="n"/>
+      <c r="BA70" s="11" t="n"/>
+      <c r="BB70" s="45" t="inlineStr"/>
+      <c r="BC70" s="10" t="n"/>
+      <c r="BD70" s="11" t="n"/>
+      <c r="BE70" s="45" t="inlineStr"/>
+      <c r="BF70" s="10" t="n"/>
+      <c r="BG70" s="11" t="n"/>
+      <c r="BH70" s="45" t="inlineStr"/>
+      <c r="BI70" s="10" t="n"/>
+      <c r="BJ70" s="11" t="n"/>
+      <c r="BK70" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL70" s="10" t="n"/>
+      <c r="BM70" s="10" t="n"/>
+      <c r="BN70" s="10" t="n"/>
+      <c r="BO70" s="10" t="n"/>
+      <c r="BP70" s="10" t="n"/>
+      <c r="BQ70" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="922">
+  <mergeCells count="973">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
     <mergeCell ref="AS46:AU46"/>
     <mergeCell ref="BK58:BQ58"/>
+    <mergeCell ref="BB68:BD68"/>
     <mergeCell ref="AP50:AR50"/>
     <mergeCell ref="AE54:AF54"/>
     <mergeCell ref="BH33:BJ33"/>
@@ -19515,6 +20468,7 @@
     <mergeCell ref="W2:AH2"/>
     <mergeCell ref="X10:AD11"/>
     <mergeCell ref="AG42:AI42"/>
+    <mergeCell ref="BK70:BQ70"/>
     <mergeCell ref="AJ22:AL22"/>
     <mergeCell ref="AG26:AI26"/>
     <mergeCell ref="AP13:AR13"/>
@@ -19523,11 +20477,13 @@
     <mergeCell ref="AJ51:AL51"/>
     <mergeCell ref="BK47:BQ47"/>
     <mergeCell ref="E25:I25"/>
+    <mergeCell ref="X68:AD68"/>
     <mergeCell ref="Q40:W40"/>
     <mergeCell ref="AE36:AF36"/>
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
+    <mergeCell ref="AV70:AX70"/>
     <mergeCell ref="E58:I58"/>
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="BH21:BJ21"/>
@@ -19537,6 +20493,7 @@
     <mergeCell ref="AM49:AO49"/>
     <mergeCell ref="AE50:AF50"/>
     <mergeCell ref="AG52:AI52"/>
+    <mergeCell ref="X69:AD69"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="BB26:BD26"/>
@@ -19552,6 +20509,7 @@
     <mergeCell ref="X21:AD21"/>
     <mergeCell ref="AE62:AF62"/>
     <mergeCell ref="AG47:AI47"/>
+    <mergeCell ref="B68:D68"/>
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="AJ35:AL35"/>
@@ -19574,6 +20532,7 @@
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
     <mergeCell ref="AS64:AU64"/>
+    <mergeCell ref="AP68:AR68"/>
     <mergeCell ref="J65:P65"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
@@ -19630,6 +20589,7 @@
     <mergeCell ref="BH26:BJ26"/>
     <mergeCell ref="BE30:BG30"/>
     <mergeCell ref="AJ43:AL43"/>
+    <mergeCell ref="AY70:BA70"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="J55:P55"/>
@@ -19642,6 +20602,7 @@
     <mergeCell ref="AG40:AI40"/>
     <mergeCell ref="X24:AD24"/>
     <mergeCell ref="BB43:BD43"/>
+    <mergeCell ref="BK68:BQ68"/>
     <mergeCell ref="A44:BQ44"/>
     <mergeCell ref="AY47:BA47"/>
     <mergeCell ref="E21:I21"/>
@@ -19655,12 +20616,17 @@
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AP69:AR69"/>
     <mergeCell ref="E23:I23"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="BE56:BG56"/>
+    <mergeCell ref="AJ69:AL69"/>
+    <mergeCell ref="BK69:BQ69"/>
+    <mergeCell ref="AM70:AO70"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="AV68:AX68"/>
     <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="AG66:AI66"/>
@@ -19674,16 +20640,19 @@
     <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="BB48:BD48"/>
+    <mergeCell ref="AG68:AI68"/>
     <mergeCell ref="AG43:AI43"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E49:I49"/>
+    <mergeCell ref="J68:P68"/>
     <mergeCell ref="AY18:BA18"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
     <mergeCell ref="E36:I36"/>
     <mergeCell ref="Q64:W64"/>
     <mergeCell ref="Q51:W51"/>
+    <mergeCell ref="BH70:BJ70"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
@@ -19742,11 +20711,13 @@
     <mergeCell ref="BE65:BG65"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
+    <mergeCell ref="AE68:AF68"/>
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
     <mergeCell ref="AY66:BA66"/>
+    <mergeCell ref="AJ70:AL70"/>
     <mergeCell ref="AV21:AX21"/>
     <mergeCell ref="BK24:BQ24"/>
     <mergeCell ref="X45:AD45"/>
@@ -19761,6 +20732,7 @@
     <mergeCell ref="AP63:AR63"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="AY55:BA55"/>
+    <mergeCell ref="AY68:BA68"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="X46:AD46"/>
@@ -19774,6 +20746,7 @@
     <mergeCell ref="AM31:AO31"/>
     <mergeCell ref="BE39:BG39"/>
     <mergeCell ref="J29:P29"/>
+    <mergeCell ref="BE70:BG70"/>
     <mergeCell ref="X48:AD48"/>
     <mergeCell ref="AE23:AF23"/>
     <mergeCell ref="AC6:AE6"/>
@@ -19792,6 +20765,7 @@
     <mergeCell ref="AG51:AI51"/>
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E70:I70"/>
     <mergeCell ref="Q14:W14"/>
     <mergeCell ref="B59:D59"/>
     <mergeCell ref="E57:I57"/>
@@ -19815,6 +20789,7 @@
     <mergeCell ref="AV52:AX52"/>
     <mergeCell ref="AP55:AR55"/>
     <mergeCell ref="AS56:AU56"/>
+    <mergeCell ref="BH68:BJ68"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
     <mergeCell ref="AY63:BA63"/>
@@ -19841,6 +20816,7 @@
     <mergeCell ref="AV37:AX37"/>
     <mergeCell ref="BB65:BD65"/>
     <mergeCell ref="BE66:BG66"/>
+    <mergeCell ref="AY69:BA69"/>
     <mergeCell ref="E60:I60"/>
     <mergeCell ref="X67:AD67"/>
     <mergeCell ref="J37:P37"/>
@@ -19865,6 +20841,7 @@
     <mergeCell ref="AM29:AO29"/>
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
+    <mergeCell ref="J70:P70"/>
     <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
     <mergeCell ref="X64:AD64"/>
@@ -19885,6 +20862,7 @@
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
     <mergeCell ref="BB60:BD60"/>
+    <mergeCell ref="B69:D69"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
@@ -19912,6 +20890,7 @@
     <mergeCell ref="AP56:AR56"/>
     <mergeCell ref="AG20:AI20"/>
     <mergeCell ref="B16:D16"/>
+    <mergeCell ref="BE68:BG68"/>
     <mergeCell ref="AP43:AR43"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
@@ -19922,8 +20901,10 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="AJ23:AL23"/>
     <mergeCell ref="E66:I66"/>
+    <mergeCell ref="AE70:AF70"/>
     <mergeCell ref="AM48:AO48"/>
     <mergeCell ref="Q49:W49"/>
+    <mergeCell ref="E68:I68"/>
     <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
@@ -19944,11 +20925,13 @@
     <mergeCell ref="AJ34:AL34"/>
     <mergeCell ref="BK34:BQ34"/>
     <mergeCell ref="AY59:BA59"/>
+    <mergeCell ref="AS70:AU70"/>
     <mergeCell ref="J58:P58"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AJ49:AL49"/>
     <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="X70:AD70"/>
     <mergeCell ref="BB22:BD22"/>
     <mergeCell ref="BE23:BG23"/>
     <mergeCell ref="AJ36:AL36"/>
@@ -19985,6 +20968,7 @@
     <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
+    <mergeCell ref="B70:D70"/>
     <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="X58:AD58"/>
     <mergeCell ref="AS60:AU60"/>
@@ -20013,6 +20997,7 @@
     <mergeCell ref="Z8:AB8"/>
     <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
+    <mergeCell ref="AM69:AO69"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
@@ -20021,6 +21006,7 @@
     <mergeCell ref="AM35:AO35"/>
     <mergeCell ref="AJ26:AL26"/>
     <mergeCell ref="AS13:AU13"/>
+    <mergeCell ref="E69:I69"/>
     <mergeCell ref="AP17:AR17"/>
     <mergeCell ref="AY40:BA40"/>
     <mergeCell ref="Q42:W42"/>
@@ -20039,6 +21025,7 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="BE24:BG24"/>
     <mergeCell ref="BH25:BJ25"/>
+    <mergeCell ref="BH69:BJ69"/>
     <mergeCell ref="BB28:BD28"/>
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="BH35:BJ35"/>
@@ -20067,8 +21054,10 @@
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="Q70:W70"/>
     <mergeCell ref="AE66:AF66"/>
     <mergeCell ref="Q45:W45"/>
+    <mergeCell ref="AV69:AX69"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="BB31:BD31"/>
     <mergeCell ref="Q32:W32"/>
@@ -20089,9 +21078,11 @@
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
+    <mergeCell ref="AS68:AU68"/>
     <mergeCell ref="AJ32:AL32"/>
     <mergeCell ref="AJ63:AL63"/>
     <mergeCell ref="AP25:AR25"/>
+    <mergeCell ref="J69:P69"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="BB57:BD57"/>
@@ -20144,6 +21135,7 @@
     <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="AY34:BA34"/>
     <mergeCell ref="B33:D33"/>
+    <mergeCell ref="BB70:BD70"/>
     <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="AS34:AU34"/>
@@ -20158,6 +21150,7 @@
     <mergeCell ref="AS30:AU30"/>
     <mergeCell ref="BB47:BD47"/>
     <mergeCell ref="AG60:AI60"/>
+    <mergeCell ref="AE69:AF69"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="BH54:BJ54"/>
@@ -20169,6 +21162,7 @@
     <mergeCell ref="BH65:BJ65"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
+    <mergeCell ref="AS69:AU69"/>
     <mergeCell ref="BH56:BJ56"/>
     <mergeCell ref="X29:AD29"/>
     <mergeCell ref="AP35:AR35"/>
@@ -20180,6 +21174,7 @@
     <mergeCell ref="BB63:BD63"/>
     <mergeCell ref="AJ66:AL66"/>
     <mergeCell ref="BE46:BG46"/>
+    <mergeCell ref="AG70:AI70"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
     <mergeCell ref="BK20:BQ20"/>
@@ -20187,6 +21182,7 @@
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="AY64:BA64"/>
+    <mergeCell ref="AJ68:AL68"/>
     <mergeCell ref="Q66:W66"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="AY51:BA51"/>
@@ -20195,6 +21191,7 @@
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="X43:AD43"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="Q68:W68"/>
     <mergeCell ref="E40:I40"/>
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
@@ -20255,6 +21252,7 @@
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="Q28:W28"/>
     <mergeCell ref="E30:I30"/>
+    <mergeCell ref="BE69:BG69"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
@@ -20284,6 +21282,7 @@
     <mergeCell ref="J35:P35"/>
     <mergeCell ref="X65:AD65"/>
     <mergeCell ref="AM66:AO66"/>
+    <mergeCell ref="Q69:W69"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F3:Q3"/>
@@ -20300,6 +21299,7 @@
     <mergeCell ref="BK29:BQ29"/>
     <mergeCell ref="AS40:AU40"/>
     <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="AM68:AO68"/>
     <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="AE35:AF35"/>
@@ -20334,6 +21334,7 @@
     <mergeCell ref="AE13:AF13"/>
     <mergeCell ref="AS45:AU45"/>
     <mergeCell ref="BK57:BQ57"/>
+    <mergeCell ref="AG69:AI69"/>
     <mergeCell ref="AE40:AF40"/>
     <mergeCell ref="X47:AD47"/>
     <mergeCell ref="BH63:BJ63"/>
@@ -20360,6 +21361,7 @@
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="BB69:BD69"/>
     <mergeCell ref="AG16:AI16"/>
     <mergeCell ref="E64:I64"/>
     <mergeCell ref="E51:I51"/>
@@ -20367,6 +21369,7 @@
     <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="BE17:BG17"/>
     <mergeCell ref="B55:D55"/>
+    <mergeCell ref="AP70:AR70"/>
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
@@ -20401,13 +21404,13 @@
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE37 AE39:AE43 AE45:AE52 AE54:AE67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE37 AE39:AE43 AE45:AE52 AE54:AE70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG37 AG39:AG43 AG45:AG52 AG54:AG67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG37 AG39:AG43 AG45:AG52 AG54:AG70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV37 AV39:AV43 AV45:AV52 AV54:AV67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV37 AV39:AV43 AV45:AV52 AV54:AV70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
